--- a/workspaces/nasdaq_hourly_24hrs/macd/macd_12_26.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/macd/macd_12_26.xlsx
@@ -618,1641 +618,1641 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.01147</t>
+          <t>X ≈ -0.01146</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>18</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-3.649137178756099</v>
+        <v>-3.616124820723165</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>18.0935480765997</v>
+        <v>18.12713813209859</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>16.66769584348549</v>
+        <v>16.70295095824769</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>10.44011687620519</v>
+        <v>10.4761678340063</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.9678327727094143</v>
+        <v>-0.9025437282039093</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>4.743455908270654</v>
+        <v>4.808605295102751</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>3.975618884796681</v>
+        <v>4.041695164787555</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-1.829461472585628</v>
+        <v>-1.763058148617368</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-18.38085124701723</v>
+        <v>-18.31454426682365</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-13.62432352968428</v>
+        <v>-13.55705082714596</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-18.88876744096554</v>
+        <v>-18.82179304834604</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-19.1728326959043</v>
+        <v>-19.10548832965912</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-14.76208324906979</v>
+        <v>-14.69336938192725</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-14.98714392388472</v>
+        <v>-14.91812765040575</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-4.567186502755384</v>
+        <v>-4.497325366347212</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-3.974702764441062</v>
+        <v>-3.905488973925173</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-9.653273986940285</v>
+        <v>-9.583876552986872</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-15.3066371918632</v>
+        <v>-15.23708458292706</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-15.09539662490167</v>
+        <v>-15.02604839247864</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-14.91308843059439</v>
+        <v>-14.84391110335756</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-15.46012643883396</v>
+        <v>-15.39026990834244</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-15.54062917082296</v>
+        <v>-15.47063686378702</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-9.716615338024084</v>
+        <v>-9.64689453469942</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-9.795321637428167</v>
+        <v>-9.725467289720889</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.01068</t>
+          <t>X ≈ -0.01067</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>30</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-3.648776612640511</v>
+        <v>-3.615768463353689</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-10.60591962469602</v>
+        <v>-10.57255836658521</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-8.727931530680948</v>
+        <v>-8.692870069630473</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-2.813888671927955</v>
+        <v>-2.777935148333142</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-16.43435165789649</v>
+        <v>-16.36917523455279</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-9.623085629816899</v>
+        <v>-9.55803465561717</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-3.762647094356886</v>
+        <v>-3.69662292152578</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-4.040865394935423</v>
+        <v>-3.97447988792441</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-4.000534519644226</v>
+        <v>-3.934156094474048</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-1.452878951779951</v>
+        <v>-1.385550197652869</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-4.499899594457773</v>
+        <v>-4.432863332486264</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-1.458429331154278</v>
+        <v>-1.391013310722457</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-5.902013231146299</v>
+        <v>-5.833268762779973</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-6.124453234492954</v>
+        <v>-6.055409156733226</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-6.783204746628485</v>
+        <v>-6.713354059452691</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-6.191427647148757</v>
+        <v>-6.122223083050635</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-9.652985268311305</v>
+        <v>-9.583590674113871</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-9.760762276339342</v>
+        <v>-9.691200290798818</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-12.87621109561968</v>
+        <v>-12.80686111067237</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-9.36399909827059</v>
+        <v>-9.294815482196974</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-13.23972286435576</v>
+        <v>-13.16986529754127</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-13.31961981264841</v>
+        <v>-13.24962681421031</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-13.04889962431738</v>
+        <v>-12.97918044438871</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-13.12865497076024</v>
+        <v>-13.05880062305296</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.009881</t>
+          <t>X ≈ -0.009874</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>30</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>6.281903207622051</v>
+        <v>6.314990542406903</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>9.261820174312916</v>
+        <v>9.295336126507024</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>11.14555479331042</v>
+        <v>11.18076436744285</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>10.43874847400021</v>
+        <v>10.47479552902442</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>3.451924930647117</v>
+        <v>3.517230327673083</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3.638253967386717</v>
+        <v>3.703384625110878</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.869896034657081</v>
+        <v>2.935954943807211</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>9.227935783276294</v>
+        <v>9.294393304844789</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>9.272280554491232</v>
+        <v>9.33872653628741</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>8.504621937321282</v>
+        <v>8.571996925260606</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>8.780995910069592</v>
+        <v>8.848090633539705</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>8.505119063943738</v>
+        <v>8.572574764804017</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>10.70916548901717</v>
+        <v>10.77797279559952</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>13.81494546348419</v>
+        <v>13.88405901675065</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>16.48646518301346</v>
+        <v>16.55638943514871</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>20.41048022608293</v>
+        <v>20.4797602045783</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>16.9571403098754</v>
+        <v>17.02660057820474</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>13.530193588537</v>
+        <v>13.59980446232586</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>10.42188224238951</v>
+        <v>10.49127279318642</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>10.61178974948841</v>
+        <v>10.68100107624366</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>10.07245926405698</v>
+        <v>10.14234117890411</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>6.66831061151013</v>
+        <v>6.738317368798484</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>3.612746325721822</v>
+        <v>3.682471154816916</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>3.538011695906427</v>
+        <v>3.607866043613704</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.009085</t>
+          <t>X ≈ -0.009081</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>41</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-7.281080662224689</v>
+        <v>-7.248114679037329</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-5.193992395110506</v>
+        <v>-5.160598997503243</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-11.4732905397811</v>
+        <v>-11.43826267076147</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-7.338851198030113</v>
+        <v>-7.302940730780101</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.85291382412121</v>
+        <v>-2.787661453383365</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-2.668542991897183</v>
+        <v>-2.603462452773854</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-3.438743557685584</v>
+        <v>-3.372732280985112</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-8.57114841994445</v>
+        <v>-8.504804089490165</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-8.532223496610996</v>
+        <v>-8.465883693441285</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-4.448222315001743</v>
+        <v>-4.380920857070812</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.6827106279727033</v>
+        <v>0.7497611413202918</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.4044078033581968</v>
+        <v>0.4718226283311964</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.7161756015314467</v>
+        <v>-0.6474194143338394</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-10.66311183507839</v>
+        <v>-10.59409404066834</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-8.89103340218216</v>
+        <v>-8.821198114018621</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-13.16605396176367</v>
+        <v>-13.09687756695885</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-15.73707521332764</v>
+        <v>-15.6677036897912</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-18.28121787026269</v>
+        <v>-18.21168140098793</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-18.07097693392699</v>
+        <v>-18.00164231699144</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-20.32582108471914</v>
+        <v>-20.25665822725122</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-18.43786749503098</v>
+        <v>-18.36801920741343</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-18.51944721502943</v>
+        <v>-18.4494604524517</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-18.25043428428125</v>
+        <v>-18.18071822969224</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-15.89288261303665</v>
+        <v>-15.82302826532938</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.00829</t>
+          <t>X ≈ -0.008285</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>46</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.985959728760058</v>
+        <v>5.019025858410906</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-1.822894556938579</v>
+        <v>-1.789480927874024</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.094314087738539</v>
+        <v>-1.059212337624743</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-3.965416042813366</v>
+        <v>-3.929488342674809</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-6.489310855197552</v>
+        <v>-6.424097485885007</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-8.467850888292531</v>
+        <v>-8.402822359921785</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-2.752664795969871</v>
+        <v>-2.686659844314725</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-7.356624669036876</v>
+        <v>-7.290284722980523</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-13.80856877885967</v>
+        <v>-13.74227122774119</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-8.090266769351715</v>
+        <v>-8.022994716129624</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-3.489124348460038</v>
+        <v>-3.422102466455023</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-3.7687101659183</v>
+        <v>-3.70132184019679</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.608807064592639</v>
+        <v>1.677566615018335</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-2.945221479050915</v>
+        <v>-2.876181559529229</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-5.770888915943665</v>
+        <v>-5.701049687438591</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-7.347352858897473</v>
+        <v>-7.278165157022961</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-5.313670136332377</v>
+        <v>-5.244276495316662</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-7.589937973759305</v>
+        <v>-7.520382233519797</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-7.37650696340728</v>
+        <v>-7.307156248323068</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-9.363297794018997</v>
+        <v>-9.294121803373926</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-12.08071920107352</v>
+        <v>-12.01086640012387</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-12.16045833057942</v>
+        <v>-12.09046855896597</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-14.06283833429636</v>
+        <v>-13.99312161775126</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-18.49097381133995</v>
+        <v>-18.42111946363316</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.007494</t>
+          <t>X ≈ -0.00749</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-7.070500532948572</v>
+        <v>-7.820794346179646</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-14.25379036658302</v>
+        <v>-13.20480783271904</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-5.412918994115159</v>
+        <v>-4.536039803186853</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-6.124742596948508</v>
+        <v>-5.246751551574718</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-3.060573372576741</v>
+        <v>-3.89578321983668</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-8.019096855772048</v>
+        <v>-8.767625153702596</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-7.076550266126134</v>
+        <v>-7.853457965896368</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.4939892495581617</v>
+        <v>-1.387064206883515</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-2.168109560933374</v>
+        <v>-3.032421134884231</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-4.656217980104934</v>
+        <v>-5.490803592210277</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-7.818514372589448</v>
+        <v>-8.595469524632179</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-4.664397531617325</v>
+        <v>-5.499462487909447</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-5.786704346417629</v>
+        <v>-6.620711098865428</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-4.289973173769333</v>
+        <v>-5.1530914528485</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-8.386538046525111</v>
+        <v>-9.190876692356085</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-2.636170625645491</v>
+        <v>-3.528863772761646</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-2.770247720288289</v>
+        <v>-3.663048310052872</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-1.155028561097829</v>
+        <v>-2.077132795694602</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.7817533505673424</v>
+        <v>-0.1700474214974506</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.7532293806073866</v>
+        <v>-1.676346353523719</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-4.741052849437253</v>
+        <v>-5.605423360263941</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-1.372500279509211</v>
+        <v>-2.295440340574117</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-1.098322029194833</v>
+        <v>-2.02185482307133</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>3.997781810848565</v>
+        <v>2.986397117060427</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.0067</t>
+          <t>X ≈ -0.006696</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-7.463583475255945</v>
+        <v>-6.532256986358028</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-3.978862538766272</v>
+        <v>-4.919034118614817</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.3184734724956186</v>
+        <v>-0.5079244428134686</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-2.302082867669675</v>
+        <v>-3.16539132703992</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.7531838631376786</v>
+        <v>0.3989608511740101</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.344199783318764</v>
+        <v>2.534020311821259</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>6.312323189616095</v>
+        <v>7.615976259444686</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2.210837819512854</v>
+        <v>3.440194950636389</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>7.994900012213591</v>
+        <v>9.337229339891238</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.483666214649986</v>
+        <v>2.714690743821663</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-5.902399618866589</v>
+        <v>-4.821516650588912</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-4.267470920551879</v>
+        <v>-3.148325420614427</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.3591017778228363</v>
+        <v>1.592674003381028</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-3.694632763955838</v>
+        <v>-2.535577163220481</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>1.399990818201786</v>
+        <v>2.673016128037133</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-3.760340156273429</v>
+        <v>-2.600425385436111</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>1.86135034641439</v>
+        <v>3.134695578788758</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>3.676483538197914</v>
+        <v>4.988017753273311</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.05345736658451017</v>
+        <v>1.289879612475822</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.2402123738337352</v>
+        <v>1.476834139084289</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>5.461367679891545</v>
+        <v>6.812058517062248</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>5.387064942082837</v>
+        <v>6.738297003255674</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>3.740966718253752</v>
+        <v>5.054634951663317</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>1.743139901035072</v>
+        <v>3.019630749496059</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.005904</t>
+          <t>X ≈ -0.0059</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.086510046222386</v>
+        <v>-1.119405082975511</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.3955557093670379</v>
+        <v>-0.9051822042043369</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-3.874893080016051</v>
+        <v>-3.348874449736705</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2.582583824948742</v>
+        <v>3.036510871038679</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2.221780094641346</v>
+        <v>2.705125556621027</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>4.457462381668421</v>
+        <v>4.91987523795185</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.63856937155122</v>
+        <v>2.122956994340569</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3.413126352107142</v>
+        <v>3.877100545189137</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>5.50746104201486</v>
+        <v>5.950638326629502</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>4.739225589774748</v>
+        <v>5.183462431736729</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>6.041169349018055</v>
+        <v>6.474787214685698</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>3.710695265659425</v>
+        <v>4.165749148153317</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>2.591024767928772</v>
+        <v>3.047552807993661</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>4.426967346631109</v>
+        <v>4.862962024357969</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>3.771673734115161</v>
+        <v>4.20859818826775</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>8.479273241378273</v>
+        <v>8.873720144839908</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>5.263152475048983</v>
+        <v>5.689383877620529</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>5.160066089385069</v>
+        <v>5.586583318132213</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>12.58199893479658</v>
+        <v>12.93492644260979</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>13.80248492854142</v>
+        <v>14.14482751592568</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>13.26451797703574</v>
+        <v>13.60762601313224</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>12.16267928653897</v>
+        <v>12.51652167336429</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>11.41081464457381</v>
+        <v>11.77498982299362</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>9.276843311026703</v>
+        <v>9.662287812321189</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.005109</t>
+          <t>X ≈ -0.005105</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>102</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-13.36884892344368</v>
+        <v>-14.40018625016114</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-7.867852195171537</v>
+        <v>-8.898620430284367</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-8.328039726055522</v>
+        <v>-8.837190339735329</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-7.094633254979293</v>
+        <v>-7.058876069382194</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-11.35431178272039</v>
+        <v>-11.28930657261417</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-14.09616104037916</v>
+        <v>-14.03133406660817</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-15.84526592548359</v>
+        <v>-15.77949851225515</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-17.10277631383142</v>
+        <v>-17.03663781840447</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-11.21547607267397</v>
+        <v>-11.14929742334932</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-4.183954576804055</v>
+        <v>-4.116790072009962</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.9836728178965544</v>
+        <v>-0.9167601842933522</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.666394202641115</v>
+        <v>0.7573704314793304</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.5463480201339266</v>
+        <v>-0.36166134049558</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.303550763667396</v>
+        <v>0.3955138033649774</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>8.466104120467968</v>
+        <v>7.55856905283887</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>6.129263071092929</v>
+        <v>5.220740930141048</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>12.844434368349</v>
+        <v>11.9357952086991</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>14.70081217329889</v>
+        <v>13.79200825410632</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>14.92134277324448</v>
+        <v>14.0119963607843</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>10.21816307597093</v>
+        <v>9.308299625815366</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>10.65868410067427</v>
+        <v>9.749163269365816</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>9.606789525534843</v>
+        <v>8.697065727889928</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>10.86495443335141</v>
+        <v>9.9546195373958</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>11.77330581355371</v>
+        <v>10.86276800439803</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.004313</t>
+          <t>X ≈ -0.004309</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>93</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.9715274219355123</v>
+        <v>-1.522258073737262</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-3.439231790273524</v>
+        <v>-3.993954249521387</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.599576798900259</v>
+        <v>2.039224999707251</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.889137016007268</v>
+        <v>1.324923161313166</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.597519634792995</v>
+        <v>2.662574566238504</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.715417145664851</v>
+        <v>1.780301851306341</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.190797170913726</v>
+        <v>-1.124984353598087</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.739189403413299</v>
+        <v>1.805395274821343</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.7103381909085869</v>
+        <v>0.77654464400905</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.009484031239218</v>
+        <v>1.07664293852519</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>2.353323890155224</v>
+        <v>2.420224108079545</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>5.287154799211066</v>
+        <v>6.425253808776958</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.9556032075176972</v>
+        <v>2.095410996857176</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>2.878781937889379</v>
+        <v>4.019277446269875</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>1.150719633362513</v>
+        <v>2.292399932028694</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>4.961218758909958</v>
+        <v>6.10264433638352</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>4.829496821466165</v>
+        <v>5.971501566654553</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>6.872387459448987</v>
+        <v>8.014943667207888</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>1.72371371734306</v>
+        <v>2.866432787206783</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>1.91154907254527</v>
+        <v>3.054475822566516</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.2958743466843217</v>
+        <v>1.439858277632872</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>1.294757088965227</v>
+        <v>2.439257775314012</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-2.729423718319993</v>
+        <v>-1.584818103125457</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-3.881343142803495</v>
+        <v>-2.736219977891665</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.003518</t>
+          <t>X ≈ -0.003514</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2.011586826689182</v>
+        <v>2.689846899928447</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>2.300318606885284</v>
+        <v>3.508581504185955</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2.00985290257335</v>
+        <v>2.065642150285406</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.29941823987032</v>
+        <v>1.350930879103842</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.9397299186019907</v>
+        <v>-0.1432913009197776</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>3.409164268883281</v>
+        <v>3.009338034410398</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.3573301468899857</v>
+        <v>-0.0683121667481501</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>4.650545761244416</v>
+        <v>4.278284830576062</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>3.549347068467966</v>
+        <v>3.163631158603224</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.6507961922784986</v>
+        <v>-1.075648310992193</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>4.197581614682477</v>
+        <v>3.825526287553323</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-5.234949394795485</v>
+        <v>-5.713298198155883</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.777412290064504</v>
+        <v>-2.201334640994887</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.8530563865258856</v>
+        <v>-1.26352582529244</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-2.655999342573871</v>
+        <v>-3.079152309616191</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-8.940018829447695</v>
+        <v>-9.443969437209084</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-5.637374761485226</v>
+        <v>-6.101314931747147</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-6.891171624813296</v>
+        <v>-7.368466202464226</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-6.677774703153524</v>
+        <v>-7.155462096076512</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-5.345274041656012</v>
+        <v>-5.809973558727918</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-5.889376105684683</v>
+        <v>-6.353581870048423</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-4.818712271859795</v>
+        <v>-5.269610053500195</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-3.396537258630509</v>
+        <v>-3.834527891595314</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-1.174631982254226</v>
+        <v>-1.585932405998427</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.002723</t>
+          <t>X ≈ -0.002719</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.9636222523908415</v>
+        <v>0.4434427679111721</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.3913623404878024</v>
+        <v>-0.9027138031398252</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.823084239057309</v>
+        <v>-2.333660655851048</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.580544804430751</v>
+        <v>2.02291311021159</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>4.268635352258485</v>
+        <v>3.718975006906852</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>3.43129130909395</v>
+        <v>2.890267586823015</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.432142915171667</v>
+        <v>-1.930688948956927</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-5.809505752567205</v>
+        <v>-6.266099632820676</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.671343100186874</v>
+        <v>-2.169938496253984</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.442129564668754</v>
+        <v>-2.939998051601222</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-6.274127343844931</v>
+        <v>-6.730626087367554</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.449788005668744</v>
+        <v>-2.94797400567424</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.544035372789175</v>
+        <v>-3.051557430030215</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2.3696333169826</v>
+        <v>1.809825699888421</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.3409754913056844</v>
+        <v>-0.8792505464473805</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>1.280287521924087</v>
+        <v>1.747942016162789</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>3.203340027496075</v>
+        <v>3.6503792681251</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.01409493972293063</v>
+        <v>0.4929316683053884</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>1.258899158620245</v>
+        <v>1.727198270219141</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>4.534540315733736</v>
+        <v>3.952479728835996</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>3.994170064933094</v>
+        <v>3.412542568287101</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>0.8294858235967197</v>
+        <v>0.279281207955087</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>1.104705731058154</v>
+        <v>0.5539958535522942</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-4.12521854464363</v>
+        <v>-4.623426473393323</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.001927</t>
+          <t>X ≈ -0.001924</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>4.319366464999476</v>
+        <v>4.747763335287225</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.338693209654295</v>
+        <v>-0.9551885204520687</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.9227541682483604</v>
+        <v>0.9621157434247607</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-5.114799168330244</v>
+        <v>-5.119038779003176</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-4.144708846596416</v>
+        <v>-4.112656668874557</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-2.62891283977217</v>
+        <v>-2.583683296473829</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.06360243499879914</v>
+        <v>0.3851334228586438</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.9926156338562748</v>
+        <v>1.450897232331414</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.366325968007487</v>
+        <v>2.833797057707869</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.9301525935465307</v>
+        <v>1.394204313806362</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.870810811229134</v>
+        <v>2.339271016004773</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.9249404815654714</v>
+        <v>1.389414416200353</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.141958439666901</v>
+        <v>1.616974079057357</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2.258298115723498</v>
+        <v>2.742823540717986</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>2.271659700925042</v>
+        <v>2.761682430010715</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>1.528023693088954</v>
+        <v>1.33492244340016</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-2.620655981438063</v>
+        <v>-2.840795235813353</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>0.6213227651095679</v>
+        <v>0.4238838587746088</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.167545531850692</v>
+        <v>-0.03471741581829946</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.985516529775424</v>
+        <v>-0.5224637847176652</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-1.527852484703949</v>
+        <v>-1.063960395099599</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-1.604119395761764</v>
+        <v>-1.139929669212968</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-2.671581823066177</v>
+        <v>-2.216569972678656</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-1.406059892460455</v>
+        <v>-0.9416835059358419</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.001132</t>
+          <t>X ≈ -0.001129</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>150</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.9931571382546309</v>
+        <v>-0.9626061984746457</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-2.643387886502545</v>
+        <v>-2.615919773233792</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-3.414036311419132</v>
+        <v>-3.385341139762659</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-4.785673876281749</v>
+        <v>-4.756230791081428</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-3.825209023812597</v>
+        <v>-3.763710940812771</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.658422331059818</v>
+        <v>-1.594348984970772</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.764271089247949</v>
+        <v>-1.69858849057789</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.6054832277889943</v>
+        <v>0.6715785946150845</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.342910899131553</v>
+        <v>-1.276817234514688</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.200707585993555</v>
+        <v>1.267780076176678</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.8105652411259214</v>
+        <v>0.8773779385143428</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-3.446787991281511</v>
+        <v>-3.379629310322223</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.250182390697312</v>
+        <v>-1.181641410206126</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-4.790854301441115</v>
+        <v>-4.722018674952878</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-6.112990569452784</v>
+        <v>-6.043336380723858</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-2.200377935255226</v>
+        <v>-2.13132512344113</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-3.663741731118265</v>
+        <v>-3.594479411557899</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-2.440459826307027</v>
+        <v>-2.371004284877877</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-1.560497058740893</v>
+        <v>-1.491226013599658</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-2.705093527309302</v>
+        <v>-2.635981705777759</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>0.08092941306122725</v>
+        <v>0.1507420406743023</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-1.326854850524818</v>
+        <v>-1.256894063990707</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>1.61301595844786</v>
+        <v>1.68272105105514</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>1.538011695906427</v>
+        <v>1.607866043613704</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ -0.0003365</t>
+          <t>X ≈ -0.0003342</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-3.966377893438668</v>
+        <v>-3.680101075141941</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-4.307445949012092</v>
+        <v>-4.022262282130157</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-5.753969355226836</v>
+        <v>-5.468831699058349</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-4.610561363895293</v>
+        <v>-4.626879658622393</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-3.633946041130621</v>
+        <v>-3.927879805652744</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.108181816373744</v>
+        <v>-2.695629660710175</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-5.486082741039979</v>
+        <v>-6.075541425049359</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-6.812333138408711</v>
+        <v>-7.094433522327861</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-7.29931612384609</v>
+        <v>-7.27417650075548</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-7.549565614740615</v>
+        <v>-7.225345173336237</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-8.850178164886458</v>
+        <v>-8.517875554379152</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-8.084527936194185</v>
+        <v>-7.757182245043339</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-8.160947575149223</v>
+        <v>-7.837587842378831</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-7.337344443897976</v>
+        <v>-7.019015388700531</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-5.375883090258526</v>
+        <v>-5.070310197452073</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-3.7375459400659</v>
+        <v>-3.437958621297341</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-4.396632887093638</v>
+        <v>-4.093969793631715</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-3.454417311469271</v>
+        <v>-3.156940214154424</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-2.190335086791642</v>
+        <v>-1.898424145585345</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.9535047301565811</v>
+        <v>-0.6671351784548847</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.08078946012836496</v>
+        <v>0.3597092114445104</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>3.686041803451879</v>
+        <v>3.945951103334679</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>3.436562604622225</v>
+        <v>3.699061619350999</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>4.941520467836263</v>
+        <v>5.195998678866765</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.0004588</t>
+          <t>X ≈ 0.0004609</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.666486806849917</v>
+        <v>1.482438061687752</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>6.191234918559715</v>
+        <v>6.039859414318101</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.5972066413035932</v>
+        <v>-0.7867353021886245</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.77007679259772</v>
+        <v>-2.970135098238558</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-4.10837178511278</v>
+        <v>-4.287001370727396</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-4.406336856444895</v>
+        <v>-4.587069314685891</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.467198881738867</v>
+        <v>-2.915338192789307</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-4.89268650359184</v>
+        <v>-5.641400597989943</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-7.288762077743911</v>
+        <v>-8.046262760845046</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-8.062046042923726</v>
+        <v>-8.821347437304965</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-6.8200990298173</v>
+        <v>-7.282379959432184</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-8.562451803029624</v>
+        <v>-8.742877642353633</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-10.17403666943916</v>
+        <v>-10.3556097340679</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-10.88783993180306</v>
+        <v>-11.07159598607005</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-9.598175700080738</v>
+        <v>-9.771572278275649</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-9.98849871765848</v>
+        <v>-10.16741995926354</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-4.753752083483192</v>
+        <v>-4.906046259206086</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-4.373513537680417</v>
+        <v>-4.523293382882684</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-3.671839559596776</v>
+        <v>-3.819477461149212</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-3.486799293276299</v>
+        <v>-3.634675708033505</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-4.03059846277224</v>
+        <v>-4.177866066774918</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-4.598152832572154</v>
+        <v>-4.747765445392034</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-7.755082363671129</v>
+        <v>-7.921935316220825</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-7.834537323701404</v>
+        <v>-8.00132935868514</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.001254</t>
+          <t>X ≈ 0.001256</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>4.526048156873252</v>
+        <v>4.732297347919591</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.027070700475853</v>
+        <v>1.237495186104695</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.7403897591440511</v>
+        <v>0.9466084848181779</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.774833502560298</v>
+        <v>2.975898295444793</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.942156325811432</v>
+        <v>-1.706619158829902</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.2300759638906982</v>
+        <v>0.4640837383959493</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.743565640909686</v>
+        <v>-1.509144716052809</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-5.972051199437658</v>
+        <v>-5.731921058026202</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-4.513089723372339</v>
+        <v>-4.505814851034323</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-4.116599476271375</v>
+        <v>-4.110772247474841</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-4.629615502354667</v>
+        <v>-4.616045656105349</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-3.734563369992216</v>
+        <v>-3.722671593587037</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-4.878704895081412</v>
+        <v>-4.627941265084331</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-4.071823392403758</v>
+        <v>-4.067596186570064</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-6.470926721613296</v>
+        <v>-6.708251295548727</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-7.606431529157618</v>
+        <v>-8.074096905762083</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-5.525048685256095</v>
+        <v>-6.237089527645146</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-4.998058267593088</v>
+        <v>-5.70440394318036</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-5.973646572538101</v>
+        <v>-6.430931406334373</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-7.769887544977905</v>
+        <v>-7.983206551377599</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-8.316434677706326</v>
+        <v>-8.295080407139643</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-8.397357304537856</v>
+        <v>-8.13635454086068</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-9.713715110137478</v>
+        <v>-9.446545641459913</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-10.19214703425229</v>
+        <v>-9.923095748217648</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.00205</t>
+          <t>X ≈ 0.002051</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>277</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-2.817426456173841</v>
+        <v>-2.793421238218095</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.725072628074223</v>
+        <v>-1.699497085719365</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.745084795111367</v>
+        <v>-1.718950667376966</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.025317191948993</v>
+        <v>-0.9954072102209608</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.03211710688173497</v>
+        <v>0.0912660474802891</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-3.363715834958647</v>
+        <v>-3.311841979056744</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-3.430959920016321</v>
+        <v>-3.740454258441517</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.921936310958799</v>
+        <v>-2.228696338615023</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.236247056240046</v>
+        <v>-2.543020002406067</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-5.675166874766695</v>
+        <v>-6.207642293440436</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-5.542450190935313</v>
+        <v>-6.289393496984474</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-7.762213753072693</v>
+        <v>-8.735753382818274</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-7.586112871928698</v>
+        <v>-8.431773803975929</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-5.291088398649535</v>
+        <v>-5.908934746289816</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-4.868289335050584</v>
+        <v>-5.268577489870502</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-4.995774836611744</v>
+        <v>-5.168720564097583</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-7.288631081723665</v>
+        <v>-7.244407748677133</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-9.193192297328203</v>
+        <v>-9.152476305530023</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-11.14434817307913</v>
+        <v>-11.1003015387934</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-11.68555588470128</v>
+        <v>-11.63443325113728</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-11.8759937929586</v>
+        <v>-11.81553237797274</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-12.68237529852184</v>
+        <v>-12.61261721077783</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-11.33491255348898</v>
+        <v>-11.26531004802621</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-12.50290286486373</v>
+        <v>-12.43304851715645</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.002845</t>
+          <t>X ≈ 0.002847</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.670474955614495</v>
+        <v>-1.80859700891348</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.324610150769068</v>
+        <v>1.206950963509122</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.218942881249603</v>
+        <v>1.105407008909232</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.5054277814442898</v>
+        <v>0.3919258528494964</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.139538507943314</v>
+        <v>2.064010841650763</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.3373755429578225</v>
+        <v>-0.4295287859575794</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.887762607619536</v>
+        <v>2.147441603279091</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.3872049399521273</v>
+        <v>-0.1442680934038734</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.01324706094117545</v>
+        <v>0.233358552483665</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.4525076884156576</v>
+        <v>-0.207459040310205</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.4871988956561992</v>
+        <v>0.738000968769299</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.538272875413242</v>
+        <v>3.809752048299288</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.745603982437665</v>
+        <v>4.6955197160258</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2.526257726819239</v>
+        <v>2.463929695145609</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>3.865686883549699</v>
+        <v>3.81559469317601</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>4.459634079619789</v>
+        <v>4.412090161586896</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>3.659543903942861</v>
+        <v>3.608002643131613</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>2.55547302775966</v>
+        <v>2.498082079299337</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>2.979110805777488</v>
+        <v>2.714500596840622</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>2.833772783873947</v>
+        <v>2.56573407945271</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>3.626436415151836</v>
+        <v>3.362474401208424</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>2.215285605758503</v>
+        <v>1.945760540226608</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>0.8183030799575164</v>
+        <v>0.7555350220613306</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>2.077588061569756</v>
+        <v>2.019499153233397</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.00364</t>
+          <t>X ≈ 0.003641</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>246</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-4.6813980555782</v>
+        <v>-4.679982504785855</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-5.420932004487923</v>
+        <v>-5.422388379426508</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-2.813530169594017</v>
+        <v>-2.803616860551742</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.099752164063311</v>
+        <v>-1.078671501000699</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.390729565417111</v>
+        <v>3.4579617506893</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.150458165712465</v>
+        <v>1.206278550292758</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>3.210265969716808</v>
+        <v>3.275733280436533</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>5.764791178294267</v>
+        <v>5.836675227217349</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>4.187655752142554</v>
+        <v>4.254396171469701</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>4.628654622332355</v>
+        <v>4.694617626804558</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>4.497978925119526</v>
+        <v>4.564798230176038</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>6.241827294078149</v>
+        <v>6.31781914443124</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>5.522506345931667</v>
+        <v>5.597786108865485</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>4.896588141613144</v>
+        <v>4.97020316737823</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>2.619681941464243</v>
+        <v>2.684543594634974</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>2.404807368441979</v>
+        <v>2.470422431497106</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>1.461590887724682</v>
+        <v>1.523497164438332</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>2.974785391759795</v>
+        <v>3.045047724529702</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>1.977021415820204</v>
+        <v>2.042551921582223</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>2.417955264117175</v>
+        <v>2.228272720300104</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>3.496053546443491</v>
+        <v>3.309492789996483</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>3.421029913345656</v>
+        <v>3.232521817337279</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>4.914094493823676</v>
+        <v>4.725008709941136</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>2.806304378833211</v>
+        <v>2.876158726540581</v>
       </c>
     </row>
     <row r="26">
@@ -2262,161 +2262,161 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.051504707276372</v>
+        <v>1.085521045771983</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>2.209129738156314</v>
+        <v>2.243281560855067</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.7238672025647475</v>
+        <v>-0.6872748016088224</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.9399260192406729</v>
+        <v>-0.9027163832405876</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-4.291137847951781</v>
+        <v>-4.223581482653557</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.3746453714886115</v>
+        <v>0.440996643742352</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-3.384193799946821</v>
+        <v>-3.316026667013638</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.667775383541652</v>
+        <v>-2.599213236144863</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.626197327130214</v>
+        <v>-2.557726054230159</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.902825168187469</v>
+        <v>-2.833129292455695</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-3.623562945773529</v>
+        <v>-3.554094525915609</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-3.404922352731219</v>
+        <v>-3.335331491552722</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-5.027303046207699</v>
+        <v>-4.95600599621978</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-5.248690852936484</v>
+        <v>-5.17708487266637</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-6.90315307639699</v>
+        <v>-6.830253045868872</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-6.80542457926547</v>
+        <v>-6.733378561736764</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-7.934863283671184</v>
+        <v>-7.862320574336159</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-8.537333230728287</v>
+        <v>-8.46467371596826</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-8.818851577230411</v>
+        <v>-8.746294772854881</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-8.631900768693299</v>
+        <v>-8.559448962886883</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-6.869721578989861</v>
+        <v>-7.111945379609097</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-4.966714284009711</v>
+        <v>-5.197741589774431</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-3.207694378755122</v>
+        <v>-3.430729563859536</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-1.295321637426817</v>
+        <v>-1.51651206583908</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.005231</t>
+          <t>X ≈ 0.005232</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.78305266950769</v>
+        <v>1.846957764616853</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3.910177825644013</v>
+        <v>3.951205356510933</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3.678370976311051</v>
+        <v>3.732698502601856</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.355017164553061</v>
+        <v>2.40998838559814</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3.207264464890642</v>
+        <v>3.293710108172817</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.784868579332553</v>
+        <v>2.870920196709221</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>5.691820203420782</v>
+        <v>5.757508098184729</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>7.248362700669091</v>
+        <v>7.308564946114586</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>5.445158152316431</v>
+        <v>5.520783835346357</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>5.266448034199115</v>
+        <v>5.357624256870807</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>6.16319909402398</v>
+        <v>6.241439996593748</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>7.122473128895649</v>
+        <v>7.182202788267702</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>6.599522850133091</v>
+        <v>6.668796818972559</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>8.840466709879259</v>
+        <v>8.886742332769828</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>10.62940093570985</v>
+        <v>10.66762342543317</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>11.85487233688114</v>
+        <v>11.87176644493721</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>11.09838685002275</v>
+        <v>11.12809321039876</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>11.61579522663693</v>
+        <v>11.63300860413855</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>8.750433749614793</v>
+        <v>8.800119497257931</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>10.16461810120543</v>
+        <v>10.20647750234799</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>7.776697078832036</v>
+        <v>7.834663041698953</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>6.878685112490679</v>
+        <v>6.539304885167944</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>5.714442954597565</v>
+        <v>4.984511304967029</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>3.784925276153302</v>
+        <v>3.079410759060863</v>
       </c>
     </row>
     <row r="28">
@@ -2426,161 +2426,161 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>6.331115691944881</v>
+        <v>6.359152886567976</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>7.126677179776216</v>
+        <v>7.135487199329269</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>7.903221240542486</v>
+        <v>7.919690372520527</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3.825782907353165</v>
+        <v>3.873403019744451</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1.196658618425133</v>
+        <v>1.315390324974985</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.979821788564252</v>
+        <v>-1.830976822260965</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-6.132996433282543</v>
+        <v>-5.936258839484616</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-6.423453573563989</v>
+        <v>-6.214470284237727</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-3.013531490640027</v>
+        <v>-2.839649768989688</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.802044639249523</v>
+        <v>1.942990110529443</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-2.406075621344208</v>
+        <v>-2.22739469175314</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-4.918077542339553</v>
+        <v>-4.728366317423358</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>4.05074679811441</v>
+        <v>4.148471615720553</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.4657449670839355</v>
+        <v>0.5940594059406976</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>4.286912756803069</v>
+        <v>4.38036055280454</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>4.905777795950137</v>
+        <v>4.974747474747417</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>7.00697261827429</v>
+        <v>7.063052559992187</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>4.666700685705933</v>
+        <v>4.735989633948762</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>7.115731866158349</v>
+        <v>7.174103237095458</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>5.053204151590123</v>
+        <v>5.138726824841171</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>3.384027738021715</v>
+        <v>3.485069545764098</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>4.429287689044408</v>
+        <v>4.52033469546604</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>3.578086850956083</v>
+        <v>3.683698296837051</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>5.373217688415799</v>
+        <v>4.718977154724818</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.006821</t>
+          <t>X ≈ 0.006822</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>68</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>9.561172711896262</v>
+        <v>9.594447004215091</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-1.068120449806884</v>
+        <v>-1.034447441193542</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.4333555566952541</v>
+        <v>0.4687099803637409</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.2804377564979035</v>
+        <v>-0.2442440390789997</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.766057164360355</v>
+        <v>3.831730194256032</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>12.77675118913184</v>
+        <v>12.84222579211811</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>19.35682623354837</v>
+        <v>19.42321828469832</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>19.07827158802989</v>
+        <v>19.14500683994532</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>16.17861118246429</v>
+        <v>16.2453175512718</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>15.40477577169487</v>
+        <v>15.47240187523531</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>15.67913503881016</v>
+        <v>15.74646151739719</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>13.92945290004114</v>
+        <v>13.99712387865507</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>9.863785210965709</v>
+        <v>9.932785341210668</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>3.760075458754891</v>
+        <v>3.829353523587613</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>0.1599677491294358</v>
+        <v>0.2300337554189014</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-6.597913377719763</v>
+        <v>-6.528520499108687</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-3.790830601280454</v>
+        <v>-3.721261165497928</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-2.425225782081661</v>
+        <v>-2.355513634025037</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>2.202662086732509</v>
+        <v>2.272142452781644</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>2.389705882352942</v>
+        <v>2.458988262749671</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>1.84650547335503</v>
+        <v>1.916442094783683</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>4.71172688830061</v>
+        <v>4.781772603962771</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>3.515913819488624</v>
+        <v>3.585659081150709</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>6.381148950808388</v>
+        <v>6.451003298515666</v>
       </c>
     </row>
     <row r="30">
@@ -2593,76 +2593,76 @@
         <v>62</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.4483149541378992</v>
+        <v>-0.4150406618190701</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-5.622200146201571</v>
+        <v>-5.58852713758823</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.002615518744555</v>
+        <v>1.037969942413042</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3.514628657164295</v>
+        <v>3.550822374583198</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.689350805279055</v>
+        <v>-1.623677775383378</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.502186192272376</v>
+        <v>-1.436711589286105</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>4.176560578899505</v>
+        <v>4.242952630049452</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>10.34961883660665</v>
+        <v>10.41635408852208</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>15.22984457904865</v>
+        <v>15.29655094785615</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>20.90762207150502</v>
+        <v>20.97524817504546</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>17.95617488700745</v>
+        <v>18.02350136559448</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>14.45127453191969</v>
+        <v>14.51894551053363</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>8.488073636013191</v>
+        <v>8.557073766258149</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>8.266716824978836</v>
+        <v>8.335994889811559</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>9.220688811747941</v>
+        <v>9.290754818037406</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>8.202845635562916</v>
+        <v>8.272238514173992</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>8.068751941413993</v>
+        <v>8.138321377196519</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>4.737962073705816</v>
+        <v>4.80767422176244</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>6.566988462444037</v>
+        <v>6.636468828493172</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>5.141129032258064</v>
+        <v>5.210411412654793</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>7.823735074872964</v>
+        <v>7.893671696301617</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>4.521973567617501</v>
+        <v>4.592019283279662</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>1.570942282486726</v>
+        <v>1.640687544148811</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.1179022825881475</v>
+        <v>-0.04804793488087</v>
       </c>
     </row>
     <row r="31">
@@ -2675,76 +2675,76 @@
         <v>62</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>4.390394723281467</v>
+        <v>4.423669015600296</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>8.893928886056493</v>
+        <v>8.927601894669834</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>7.454228421970328</v>
+        <v>7.489582845638814</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-4.549887471867969</v>
+        <v>-4.513693754449065</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.536455646333756</v>
+        <v>1.602128676229434</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.1107170335341792</v>
+        <v>0.1761916365204499</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.6621490985199685</v>
+        <v>-0.5957570473700216</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-2.553606969844914</v>
+        <v>-2.486871717929482</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>3.939521998403528</v>
+        <v>4.00622836721103</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>8.004396265053451</v>
+        <v>8.072022368593892</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>6.665852306362353</v>
+        <v>6.733178784949381</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>3.160951951274512</v>
+        <v>3.228622929888445</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>2.03646073278739</v>
+        <v>2.105460863032349</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>1.815103921753035</v>
+        <v>1.884381986585758</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>7.607785585941535</v>
+        <v>7.677851592231001</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>6.589942409756425</v>
+        <v>6.659335288367501</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>8.068751941413993</v>
+        <v>8.138321377196519</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>1.512155622092912</v>
+        <v>1.581867770149536</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>1.728278785024727</v>
+        <v>1.797759151073862</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>9.979838709677423</v>
+        <v>10.04912109007415</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>11.04954152648592</v>
+        <v>11.11947814791457</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>9.36068324503686</v>
+        <v>9.430728960699021</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>12.86126486313189</v>
+        <v>12.93101012479397</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>9.559517072250465</v>
+        <v>9.629371419957742</v>
       </c>
     </row>
     <row r="32">
@@ -2757,76 +2757,76 @@
         <v>52</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>11.71049397886459</v>
+        <v>11.74376827118342</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>15.2214723103741</v>
+        <v>15.25514531898745</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>9.935618000134184</v>
+        <v>9.970972423802671</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>14.99105545617174</v>
+        <v>15.02724917359065</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>10.77963182499384</v>
+        <v>10.84530485488952</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>9.043719514923708</v>
+        <v>9.109194117909979</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>6.347776459792811</v>
+        <v>6.414168510942758</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>4.146144891197274</v>
+        <v>4.212880143112706</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-3.504646736087757</v>
+        <v>-3.437940367280255</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-11.97078983916491</v>
+        <v>-11.90316373562447</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-9.773353648972616</v>
+        <v>-9.706027170385589</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-4.283216783216751</v>
+        <v>-4.215545804602819</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-1.561554155550084</v>
+        <v>-1.492554025305125</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>2.063242879569415</v>
+        <v>2.132520944402138</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>3.327388563609034</v>
+        <v>3.3974545698985</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>1.999371690153495</v>
+        <v>2.068764568764571</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-3.903952773226194</v>
+        <v>-3.834383337443668</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-2.085859266244562</v>
+        <v>-2.016147118187938</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-1.869736103312746</v>
+        <v>-1.800255737263612</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-5.528846153846153</v>
+        <v>-5.459563773449425</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-9.918200408997954</v>
+        <v>-9.848263787569302</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-9.994155464640542</v>
+        <v>-9.924109748978381</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-11.64245722123535</v>
+        <v>-11.57271195957327</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-5.949167791273055</v>
+        <v>-5.879313443565778</v>
       </c>
     </row>
     <row r="33">
@@ -2839,76 +2839,76 @@
         <v>31</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-2.061218179944305</v>
+        <v>-2.027943887625476</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>7.281025660250037</v>
+        <v>7.314698668863379</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>9.067131647776804</v>
+        <v>9.102486071445291</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>11.57914478619654</v>
+        <v>11.61533850361545</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>7.9880685495596</v>
+        <v>8.053741579455277</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.723620259340585</v>
+        <v>1.789094862326856</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>7.402367030512316</v>
+        <v>7.468759081662263</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>7.123812384993798</v>
+        <v>7.19054763690923</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>3.939521998403528</v>
+        <v>4.00622836721103</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.06011986397879809</v>
+        <v>0.007506239561642758</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.2142394031365811</v>
+        <v>0.2815658817236084</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>6.386758402887438</v>
+        <v>6.45442938150137</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>8.488073636013247</v>
+        <v>8.557073766258206</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>5.040910373365982</v>
+        <v>5.110188438198705</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>1.156172682715734</v>
+        <v>1.2262386890052</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-4.700380170888693</v>
+        <v>-4.630987292277617</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>1.617139038188242</v>
+        <v>1.686708473970768</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>1.512155622092912</v>
+        <v>1.581867770149536</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>1.728278785024727</v>
+        <v>1.797759151073862</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>1.91532258064516</v>
+        <v>1.984604961041889</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>1.372122171647206</v>
+        <v>1.442058793075859</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>1.296167116004554</v>
+        <v>1.366212831666715</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>8.022555185712527</v>
+        <v>8.092300447374612</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>7.946613846444059</v>
+        <v>8.016468194151336</v>
       </c>
     </row>
     <row r="34">
@@ -2921,76 +2921,76 @@
         <v>38</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>4.220615436354421</v>
+        <v>4.253889728673251</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-6.640875867763548</v>
+        <v>-6.607202859150206</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>2.445739457623986</v>
+        <v>2.481093881292473</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.8996328029375675</v>
+        <v>-0.8634390855186638</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>9.261413201512042</v>
+        <v>9.327086231407719</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.553840972413589</v>
+        <v>1.61931557539986</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>6.044132735096397</v>
+        <v>6.110524786246344</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>3.133999142209397</v>
+        <v>3.200734394124829</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>3.175515207232017</v>
+        <v>3.242221576039519</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>10.29641663856787</v>
+        <v>10.36404274210831</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>2.676039063577925</v>
+        <v>2.743365542164952</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-2.866212734633777</v>
+        <v>-2.798541756019844</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-6.622282900489388</v>
+        <v>-6.553282770244429</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>1.051097130581525</v>
+        <v>1.120375195414248</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-2.239413055824159</v>
+        <v>-2.169347049534693</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>0.9872259411656401</v>
+        <v>1.056618819776716</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>3.484711194385099</v>
+        <v>3.554280630167625</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-1.883430116446981</v>
+        <v>-1.813717968390357</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-4.298885900883583</v>
+        <v>-4.229405534834449</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>3.782894736842103</v>
+        <v>3.852177117238831</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>0.6081153804757307</v>
+        <v>0.6780520019043834</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>0.5321603248331215</v>
+        <v>0.6022060404952825</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-4.456222403421584</v>
+        <v>-4.386477141759499</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-4.532163742690052</v>
+        <v>-4.462309394982775</v>
       </c>
     </row>
   </sheetData>
@@ -3180,83 +3180,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.01187</t>
+          <t>X &gt; -0.01186</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3351</v>
+        <v>3355</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.02859680586934843</v>
+        <v>-0.02924261372799464</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.007898454641939168</v>
+        <v>0.0072010808152001</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.08126310215622823</v>
+        <v>-0.08188940631040253</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.1853359364759655</v>
+        <v>-0.1858562395147771</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.148238524241485</v>
+        <v>-0.1494058286178443</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.2114806129389351</v>
+        <v>-0.2125692062251261</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.2847833794179166</v>
+        <v>-0.2858041142968233</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.3088595638071894</v>
+        <v>-0.3098590577635534</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.3692200712493516</v>
+        <v>-0.3701476258970402</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.3237444625504438</v>
+        <v>-0.3247451224774522</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.2700151325544624</v>
+        <v>-0.2710737627481308</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.3833105639528469</v>
+        <v>-0.3842419732990194</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.4198344831938812</v>
+        <v>-0.4207500123246319</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.4451680787076597</v>
+        <v>-0.4460594647874814</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.3424832312627615</v>
+        <v>-0.343513142531755</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.2952672820680888</v>
+        <v>-0.29633984807937</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.1734813387642973</v>
+        <v>-0.174702744390089</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.2607406850938077</v>
+        <v>-0.2618615346848543</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.2950592902569014</v>
+        <v>-0.2961348581427288</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.3586065573770512</v>
+        <v>-0.3596027044499479</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.3177233666604451</v>
+        <v>-0.3187819531440468</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.4057271914523781</v>
+        <v>-0.4066834755199622</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.5010032098529464</v>
+        <v>-0.5018400424558251</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.5592726968121653</v>
+        <v>-0.5600425505244004</v>
       </c>
     </row>
     <row r="7">
@@ -3266,1719 +3266,1719 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3333</v>
+        <v>3337</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.009043932568431501</v>
+        <v>-0.009894732479587276</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.08977382054415983</v>
+        <v>-0.09053906510121834</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.1717165258050528</v>
+        <v>-0.1724279518788876</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.2427191199827945</v>
+        <v>-0.2433679066779106</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1438122726745945</v>
+        <v>-0.1453433526836037</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.2382399460867859</v>
+        <v>-0.2396537555280602</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.3077918524919809</v>
+        <v>-0.3091469333029693</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.300647492292633</v>
+        <v>-0.302020405190774</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.2719475356466532</v>
+        <v>-0.2733543566322254</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.2519141525569282</v>
+        <v>-0.2533691852032405</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.1694638149572825</v>
+        <v>-0.1710099488012418</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.2818369970836301</v>
+        <v>-0.2832583249878127</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.3423785942692561</v>
+        <v>-0.3437625539329972</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.3666335556914078</v>
+        <v>-0.3679961662135653</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.3196675520287684</v>
+        <v>-0.3211072030565774</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.2753963433694011</v>
+        <v>-0.2768718575893416</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.1222853388641525</v>
+        <v>-0.1239490349041006</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.1794847183605768</v>
+        <v>-0.1810841853086629</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.2151294756683626</v>
+        <v>-0.2166807246042097</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.2800044950554437</v>
+        <v>-0.2814733813512476</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.2359462123552731</v>
+        <v>-0.2374853444555285</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.3239905470993421</v>
+        <v>-0.3254275087867313</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.4512339274325825</v>
+        <v>-0.4525110101332572</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.5093930445676165</v>
+        <v>-0.5106036397346045</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.01028</t>
+          <t>X &gt; -0.01027</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3303</v>
+        <v>3307</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.02401449322695726</v>
+        <v>0.02281655023169549</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.005740673589833989</v>
+        <v>0.004550314712659542</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.0940034013284361</v>
+        <v>-0.09513334542815954</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.2193660813638516</v>
+        <v>-0.220375158794738</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.004149029643492952</v>
+        <v>0.001833834028239778</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.1530006574062241</v>
+        <v>-0.155120514825704</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.2764126041553396</v>
+        <v>-0.2784168820037038</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.2666763941759811</v>
+        <v>-0.2687050787674252</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.2380820771180581</v>
+        <v>-0.240144785378746</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.2410062070598968</v>
+        <v>-0.2430984170225656</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.1301319731816193</v>
+        <v>-0.1323478376701459</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.2711504182092312</v>
+        <v>-0.2732091415671789</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.2918823668680233</v>
+        <v>-0.2939635862083563</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.3143372824961119</v>
+        <v>-0.3164018542342575</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.2609614921323171</v>
+        <v>-0.2631188735458707</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.2216630890208151</v>
+        <v>-0.2238447826683085</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.03572130680741736</v>
+        <v>-0.03813432393454974</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.09246130729809465</v>
+        <v>-0.09481158683127688</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.1001332756688029</v>
+        <v>-0.1024668112138087</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.1974977320834626</v>
+        <v>-0.1997073508023064</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.117837432591422</v>
+        <v>-0.1201671108321349</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.2059557672124299</v>
+        <v>-0.2081834872679167</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.3368137122020158</v>
+        <v>-0.338873246895389</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.3947766782988396</v>
+        <v>-0.3967705857583326</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.009483</t>
+          <t>X &gt; -0.009478</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3273</v>
+        <v>3277</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.033344706721671</v>
+        <v>-0.03478650737136491</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.07909965180634515</v>
+        <v>-0.08050417852927438</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.1970240997210908</v>
+        <v>-0.1983609717284764</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.3170573238511594</v>
+        <v>-0.3182863948748604</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.02745294928412534</v>
+        <v>-0.03034861785133103</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.1877509289441903</v>
+        <v>-0.1904440284656559</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.3052513634478373</v>
+        <v>-0.3078435389382008</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.3537030869115725</v>
+        <v>-0.3562525159075989</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.3252531369861558</v>
+        <v>-0.3278366192664492</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.3211677849185719</v>
+        <v>-0.3237980997410546</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.2118105055670583</v>
+        <v>-0.2145611895579407</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.351592851592855</v>
+        <v>-0.3541897693337717</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.3927169026689796</v>
+        <v>-0.3953240047174305</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.4438449153648634</v>
+        <v>-0.446403021805061</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.4144667778806763</v>
+        <v>-0.4170966731372232</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.4107753100575096</v>
+        <v>-0.4133803791338053</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.1914762253837949</v>
+        <v>-0.1943571030203586</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.2173252385156559</v>
+        <v>-0.220181889386879</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.1965770476033484</v>
+        <v>-0.1994494746657551</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.2965746109246297</v>
+        <v>-0.2993171319470633</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.2112407020382463</v>
+        <v>-0.2141174461058881</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.2689646249459088</v>
+        <v>-0.2717767206160957</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.3730149957760247</v>
+        <v>-0.3756875075152664</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.4308242344327056</v>
+        <v>-0.4334318914895334</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.008688</t>
+          <t>X &gt; -0.008683</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3232</v>
+        <v>3236</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.05859748825841393</v>
+        <v>0.05660609307309983</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.0142139455948751</v>
+        <v>-0.01613956555711127</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.05397740292577424</v>
+        <v>-0.05595183400896531</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.2279813495809364</v>
+        <v>-0.2297910834496122</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.008389840279086513</v>
+        <v>0.004586433525929579</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1562804850762873</v>
+        <v>-0.1598711745111885</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.2655009983600465</v>
+        <v>-0.2690115122311738</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.2494595044071275</v>
+        <v>-0.2530106696415757</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.2211424362607204</v>
+        <v>-0.224727864618373</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.2688134421792725</v>
+        <v>-0.2723945048552281</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.2231580818279255</v>
+        <v>-0.2267791177303735</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.3611832064359817</v>
+        <v>-0.3646553157813273</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.3886136209074209</v>
+        <v>-0.3921299652259975</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.3142069377323509</v>
+        <v>-0.3178321529010546</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.3069360750352601</v>
+        <v>-0.310617019529019</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.248966391517925</v>
+        <v>-0.2526809401038719</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.005729702371681356</v>
+        <v>0.001689624438725446</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.01182686479549488</v>
+        <v>0.007769742249600142</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.03017121828133185</v>
+        <v>0.02610364849103064</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.04249072929543019</v>
+        <v>-0.04645836034401896</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.0199757888382166</v>
+        <v>0.01589181601204359</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.03744550793061308</v>
+        <v>-0.04146614181347985</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.1462284268314917</v>
+        <v>-0.1500984285260074</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.2346780730704694</v>
+        <v>-0.2384462761225947</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.007892</t>
+          <t>X &gt; -0.007888</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3186</v>
+        <v>3190</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.01254459054356261</v>
+        <v>-0.01495231106657258</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.0119000870861683</v>
+        <v>0.009432128068780798</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.03895684815446998</v>
+        <v>-0.04148475464647561</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.1740196434011807</v>
+        <v>-0.1764412170156433</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.1022047279099567</v>
+        <v>0.09728845869612002</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.03627664372413619</v>
+        <v>-0.04100730161812294</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.2295909121422071</v>
+        <v>-0.2341488717058269</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.1468450670019266</v>
+        <v>-0.1515327365840164</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.02496490589048506</v>
+        <v>-0.02980404182726204</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.1558859930110614</v>
+        <v>-0.1606303638776083</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.1760035155174791</v>
+        <v>-0.1807023547080107</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.3119847632042791</v>
+        <v>-0.3165403753038518</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.4174527142950524</v>
+        <v>-0.4219751196746628</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.2762199104565752</v>
+        <v>-0.2809405940593948</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.2280466115444426</v>
+        <v>-0.2328866424996079</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.1464787024094889</v>
+        <v>-0.1513730172266747</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.08253208547914426</v>
+        <v>0.07733678478630424</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.1215824148813383</v>
+        <v>0.1163261657246437</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.1371100746396721</v>
+        <v>0.1318497159686061</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.09208463949843804</v>
+        <v>0.08689352629528457</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>0.1946876436831388</v>
+        <v>0.1893184235174488</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>0.1375885755100086</v>
+        <v>0.1322812284652031</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>0.054701910815524</v>
+        <v>0.04951883376375577</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>0.02890937324478671</v>
+        <v>0.02374901122082207</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.007097</t>
+          <t>X &gt; -0.007093</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3128</v>
+        <v>3131</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.118325436521495</v>
+        <v>0.1321395701444388</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.2764173653191619</v>
+        <v>0.2584388855540851</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.06068822999952772</v>
+        <v>0.0432098310654041</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.06368015129577032</v>
+        <v>-0.08089720240721476</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.1608495903870093</v>
+        <v>0.1725331821178528</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.1117424011284101</v>
+        <v>0.1234355132247344</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.1026332259110418</v>
+        <v>-0.09057198363261421</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.1404082503177051</v>
+        <v>-0.1282506041190956</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.01477370983600679</v>
+        <v>0.0267767338004532</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.07243993954192973</v>
+        <v>-0.0601895397090999</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.03429455461269271</v>
+        <v>-0.02213599794482946</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.2312814573961077</v>
+        <v>-0.2188743246351521</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.3178949794283383</v>
+        <v>-0.3051672554867793</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.2017960967506411</v>
+        <v>-0.1891306609170869</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.07677023583188003</v>
+        <v>-0.0640838916399602</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.1003143381039635</v>
+        <v>-0.08772818983077002</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.1354288977344211</v>
+        <v>0.1478199277423897</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.1452535902671457</v>
+        <v>0.1576593112767739</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.1251569704185087</v>
+        <v>0.1375386112450272</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.1077586206896584</v>
+        <v>0.1201197009708892</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>0.2862071285299947</v>
+        <v>0.2985134938601846</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>0.1655889443051279</v>
+        <v>0.1780287763966371</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>0.07608151072619762</v>
+        <v>0.08855142582804376</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.04468225123763858</v>
+        <v>-0.03207859601154439</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.006302</t>
+          <t>X &gt; -0.006298</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3076</v>
+        <v>3080</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.2464981489442621</v>
+        <v>0.2424915910475676</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.3483531764415488</v>
+        <v>0.3441697697140285</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.05633035203796055</v>
+        <v>0.05233575573027593</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.02583979328164787</v>
+        <v>-0.02982278670712901</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.1763013912918439</v>
+        <v>0.1687838927925682</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.09090762093534011</v>
+        <v>0.08351998571550467</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.2110785229225556</v>
+        <v>-0.2181804123329201</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.1801562332927276</v>
+        <v>-0.1873385012919897</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.1201308960559331</v>
+        <v>-0.1273898515601388</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.09874602537351507</v>
+        <v>-0.1061372327156036</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.06490618119394043</v>
+        <v>0.05733426610869685</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.1630493858473159</v>
+        <v>-0.1703671798640656</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.3293396580294612</v>
+        <v>-0.3365925490589419</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.1427494430787704</v>
+        <v>-0.150277163638691</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.1017349870704223</v>
+        <v>-0.1094060023553993</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.03844133987743703</v>
+        <v>-0.04612184016328769</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.1062520722040787</v>
+        <v>0.09836192183220049</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.08555789543866865</v>
+        <v>0.07767610330865438</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.1263690573493861</v>
+        <v>0.1184576401207593</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>0.1055194805194759</v>
+        <v>0.09765462423590066</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.1987206692742163</v>
+        <v>0.1906593392552125</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>0.0773195191151288</v>
+        <v>0.06940095835449256</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>0.0141263641750129</v>
+        <v>0.00632082199116013</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.07490551258945288</v>
+        <v>-0.08261014686248558</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.005506</t>
+          <t>X &gt; -0.005503</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2979</v>
+        <v>2982</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.2899025782598628</v>
+        <v>0.287248758738464</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.3725757887018446</v>
+        <v>0.3852282852887967</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.1843359488520733</v>
+        <v>0.1641126169428091</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.1107733585613815</v>
+        <v>-0.1305943153654354</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.1096980229719762</v>
+        <v>0.08542994139914839</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.05127291340205886</v>
+        <v>-0.07542126670540483</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.2713053929339537</v>
+        <v>-0.2951192003456669</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.2971580496014923</v>
+        <v>-0.3209116154956035</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.3033723925288783</v>
+        <v>-0.3271372564771724</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.2562764874981909</v>
+        <v>-0.2799738414065303</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.1296884906016089</v>
+        <v>-0.153567943468957</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.2891834010189029</v>
+        <v>-0.3128686554327089</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.4244304097306824</v>
+        <v>-0.4478085936569158</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.2915451895043688</v>
+        <v>-0.3150315031503084</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.227858063926746</v>
+        <v>-0.2513122433617951</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.3157888774342652</v>
+        <v>-0.3392621870882735</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.06166311378986222</v>
+        <v>-0.08538058375707891</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.07967449624069189</v>
+        <v>-0.1033677957700547</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.279201972564131</v>
+        <v>-0.302740865125358</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.3404710023466322</v>
+        <v>-0.3639895553031991</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.2267181823044595</v>
+        <v>-0.2502738378205578</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.3161950486727605</v>
+        <v>-0.3396593468336278</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.3569641907758765</v>
+        <v>-0.3804429479948368</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.379410257769301</v>
+        <v>-0.4028650093708634</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.004711</t>
+          <t>X &gt; -0.004707</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2877</v>
+        <v>2880</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.7741544563181648</v>
+        <v>0.807428748636994</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.6647286056483424</v>
+        <v>0.7140312606320194</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.4861302897768525</v>
+        <v>0.4829087633251632</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.1368295991844022</v>
+        <v>0.1147823300893194</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.5161384123291555</v>
+        <v>0.4882851929371199</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.4466688971477026</v>
+        <v>0.4188506449578142</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.2808475352273447</v>
+        <v>0.2532859002844603</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.2986615760333535</v>
+        <v>0.2711036875240893</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.08350093919681711</v>
+        <v>0.05614758276621501</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.1170261694206047</v>
+        <v>-0.1440865999059966</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.09941167399261275</v>
+        <v>-0.1265382182730903</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.3585156622539785</v>
+        <v>-0.3507729564275124</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.4588479974422555</v>
+        <v>-0.4508596422063817</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.3480970793978457</v>
+        <v>-0.3401966494227295</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.5360902998698336</v>
+        <v>-0.5279122059355643</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.5442891550671405</v>
+        <v>-0.5361789641568038</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.519230699183737</v>
+        <v>-0.5111305597399038</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.6036959214381312</v>
+        <v>-0.5954956975365064</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.8181159677231449</v>
+        <v>-0.8097211418763308</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.7148125650815658</v>
+        <v>-0.7065497971344854</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.6126448534423972</v>
+        <v>-0.6044205687000712</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.6680005497395527</v>
+        <v>-0.6597100265634168</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.7548215768241775</v>
+        <v>-0.7464764110190814</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.8102677618620859</v>
+        <v>-0.8018561786085172</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.003916</t>
+          <t>X &gt; -0.003912</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2784</v>
+        <v>2787</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.8324692604408739</v>
+        <v>0.8851685672522791</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.8018221102534895</v>
+        <v>0.8711330376123811</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.4155302447522473</v>
+        <v>0.4309757134566468</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.07829346780346924</v>
+        <v>0.07440088146936574</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.4466095137339252</v>
+        <v>0.4157308650874469</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.4042861431562841</v>
+        <v>0.3734200880183067</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.3300080803678256</v>
+        <v>0.2992776956239283</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.2505404955928725</v>
+        <v>0.2199055828887708</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.06256133272799502</v>
+        <v>0.03210849891419087</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.1546574368995479</v>
+        <v>-0.1848213853649412</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.1813457283984121</v>
+        <v>-0.2115216758801211</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.5471102574106794</v>
+        <v>-0.5768836450403612</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.5060979838148327</v>
+        <v>-0.535826692594938</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.455891529328774</v>
+        <v>-0.4856688743597246</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.5924384765187583</v>
+        <v>-0.6220238058030461</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.728201596159046</v>
+        <v>-0.7577112809670936</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.6979058642054454</v>
+        <v>-0.7274508998025766</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.8534357757565516</v>
+        <v>-0.8828192931307868</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.9030262265992803</v>
+        <v>-0.9323915098005244</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.8025466284074625</v>
+        <v>-0.8320522666831707</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.6429940939638641</v>
+        <v>-0.672636547425931</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.7335668070669783</v>
+        <v>-0.7631201469705147</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.688859651838861</v>
+        <v>-0.7185016075149946</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.7076779592659861</v>
+        <v>-0.7373079786324297</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.00312</t>
+          <t>X &gt; -0.003117</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2697</v>
+        <v>2701</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.7944332099167255</v>
+        <v>0.8277075022355547</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.753483513587959</v>
+        <v>0.7871565222013004</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.3641004815967364</v>
+        <v>0.378927837274766</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.03890234612389065</v>
+        <v>0.03375609072647023</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.430702403899474</v>
+        <v>0.4335301639680864</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.30735459071348</v>
+        <v>0.2894923044604596</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.3291267233832542</v>
+        <v>0.3109817786168918</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.1086048418621672</v>
+        <v>0.09068654723489544</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.04991562648942249</v>
+        <v>-0.06759936807331002</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.138652960919579</v>
+        <v>-0.1564574032827721</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.3226014491429581</v>
+        <v>-0.3400615221797381</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.3958896400756871</v>
+        <v>-0.4133399014017343</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.4650878449035574</v>
+        <v>-0.4827968208576507</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.4430797597417708</v>
+        <v>-0.4609018629638655</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.525871996968597</v>
+        <v>-0.5437886886879255</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.4633042660529654</v>
+        <v>-0.4811403067216986</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.5385681578415813</v>
+        <v>-0.556346750692164</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.6586701032063402</v>
+        <v>-0.6763159113452701</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.7167440176781739</v>
+        <v>-0.7342485736954742</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.6560070344316955</v>
+        <v>-0.673554957865754</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.4737559645535114</v>
+        <v>-0.4917549118296591</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.6017879211059238</v>
+        <v>-0.6196332413942329</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.6015152129101011</v>
+        <v>-0.619287146044833</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.6926149262663586</v>
+        <v>-0.7102877265948635</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.002325</t>
+          <t>X &gt; -0.002322</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2600</v>
+        <v>2603</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.7881211571782671</v>
+        <v>0.842174633992677</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.796195070451553</v>
+        <v>0.8507782248073141</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.4456992961749791</v>
+        <v>0.4810537198434659</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.05592046866678402</v>
+        <v>-0.04113341673014048</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.287517982364534</v>
+        <v>0.3098368890514607</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.1908077208354371</v>
+        <v>0.1915760625582266</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.3948356291293393</v>
+        <v>0.3953781410072992</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.3293958909620329</v>
+        <v>0.3300123427191295</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.01057609079852284</v>
+        <v>0.0115513175055213</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.052715564548933</v>
+        <v>-0.05166025248169603</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.1005637523021576</v>
+        <v>-0.0994640087765859</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.3192634318208647</v>
+        <v>-0.3179137998962744</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.387527110209362</v>
+        <v>-0.3860858951185477</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.5480155937580236</v>
+        <v>-0.5463921822721787</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.5327700589106357</v>
+        <v>-0.5311589299247998</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.5283536519890291</v>
+        <v>-0.5650627299420847</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.678170117063793</v>
+        <v>-0.7147252177855492</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.6837694144233168</v>
+        <v>-0.7203367576017925</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.790450705409306</v>
+        <v>-0.8269192577921558</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.8496543778801851</v>
+        <v>-0.847719921099241</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.6404439741151293</v>
+        <v>-0.6387472871855735</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.6551854415813736</v>
+        <v>-0.653476351665546</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.6651703788966117</v>
+        <v>-0.6634599212889754</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.5645524066576684</v>
+        <v>-0.5629624875682637</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.00153</t>
+          <t>X &gt; -0.001527</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2451</v>
+        <v>2455</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.5734514097831891</v>
+        <v>0.6067257021020183</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.9259781605110291</v>
+        <v>0.9596511691243705</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.4166984083989931</v>
+        <v>0.4520528320674799</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.2516164249480042</v>
+        <v>0.2649887802622928</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.5569597602165075</v>
+        <v>0.576447498653522</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.3622228018352516</v>
+        <v>0.3588829404143397</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.4227047729706612</v>
+        <v>0.3959957451971192</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.289077758897065</v>
+        <v>0.2624396487628573</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.1326335100599607</v>
+        <v>-0.1585881405596297</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.1124656076155262</v>
+        <v>-0.1388243892681089</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.2204065960255974</v>
+        <v>-0.2464834725923311</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.3949004710271424</v>
+        <v>-0.4208403074247116</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.4805068519195075</v>
+        <v>-0.5068406308326061</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.7186156519843649</v>
+        <v>-0.744682987568531</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.7032555889863303</v>
+        <v>-0.7296683072243724</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.6533639434686762</v>
+        <v>-0.6796035876425606</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.5600834610900023</v>
+        <v>-0.5865548052934528</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.7631079434932388</v>
+        <v>-0.7893162489352861</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.8486887467604944</v>
+        <v>-0.8746772507095102</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.8413951120162935</v>
+        <v>-0.867328030339344</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.5864970675146637</v>
+        <v>-0.6131132586840309</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.5974983101358831</v>
+        <v>-0.6241504490190977</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.5431975901649579</v>
+        <v>-0.5698304762357651</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.513395892832861</v>
+        <v>-0.5401312408397914</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.0007342</t>
+          <t>X &gt; -0.0007318</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2301</v>
+        <v>2305</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.6755771299942523</v>
+        <v>0.7088514223130815</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.158661735935631</v>
+        <v>1.192334744548972</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.6664203588434674</v>
+        <v>0.7017747825119542</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.579992585393228</v>
+        <v>0.591749272974468</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.8426291724739485</v>
+        <v>0.8588873103324488</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.493946734879259</v>
+        <v>0.4859913086606582</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.565271647952315</v>
+        <v>0.5323027453560059</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.2684515875220939</v>
+        <v>0.2358145546727073</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.05373667896011369</v>
+        <v>-0.08581835136516247</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.1980701182810449</v>
+        <v>-0.2303604716180914</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.2876146688516457</v>
+        <v>-0.3196197900179243</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.1959508282465379</v>
+        <v>-0.2282943853272528</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.4303324360930603</v>
+        <v>-0.4629273480100409</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.453150290220556</v>
+        <v>-0.4858542009708486</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.3506001143796453</v>
+        <v>-0.3838764586235399</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.5525155737303038</v>
+        <v>-0.5851314703454733</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.3577589324049768</v>
+        <v>-0.3908113385083496</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.6537629706892218</v>
+        <v>-0.6863864418240553</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.8022866403732465</v>
+        <v>-0.8345547715626438</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.7199023861171341</v>
+        <v>-0.7522312618726517</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.6300059645535114</v>
+        <v>-0.6628218464947793</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.5499522514403878</v>
+        <v>-0.5829740749428609</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.6837590992009979</v>
+        <v>-0.7164173435214991</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.647125201094866</v>
+        <v>-0.679914144383396</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 6.112e-05</t>
+          <t>X &gt; 6.337e-05</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2111</v>
+        <v>2114</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.093375071468564</v>
+        <v>1.10539348807179</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.650637321032775</v>
+        <v>1.663473832579115</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.244285847082857</v>
+        <v>1.259289370014294</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.047167028957801</v>
+        <v>1.063252643804638</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.245542147644414</v>
+        <v>1.291371945693456</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.7281506310128805</v>
+        <v>0.7734509137457195</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.10992220878061</v>
+        <v>1.129321778727544</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.9057557551804933</v>
+        <v>0.8981028151774808</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.598399794051879</v>
+        <v>0.5636501474681239</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.4635993011065906</v>
+        <v>0.4016367270707306</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.4830566074376108</v>
+        <v>0.4210930060998592</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.514058480379731</v>
+        <v>0.451940988942269</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.2654595470526928</v>
+        <v>0.2033735765048306</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.1664597946675173</v>
+        <v>0.1044172213831587</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.1016991586743501</v>
+        <v>0.03954305136522152</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.2658477529800649</v>
+        <v>-0.3273784023077155</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.005758856032173298</v>
+        <v>-0.05623079691488897</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.4016908130633468</v>
+        <v>-0.4631717916277012</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.6773557048831975</v>
+        <v>-0.738434123294752</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.6988770685579269</v>
+        <v>-0.7599196970348032</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.6939809198777951</v>
+        <v>-0.7552075759490791</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.9312117826718023</v>
+        <v>-0.9921626790351112</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-1.054607570885707</v>
+        <v>-1.11535607668548</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-1.150129785224152</v>
+        <v>-1.210803145916408</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.0008565</t>
+          <t>X &gt; 0.0008585</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1907</v>
+        <v>1911</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.032066841779098</v>
+        <v>1.065341134097928</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.164910047883602</v>
+        <v>1.198583056496943</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.441278226543183</v>
+        <v>1.47663265021167</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.45551403451487</v>
+        <v>1.491707751933774</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.818273370655675</v>
+        <v>1.883946400551352</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.277408862497609</v>
+        <v>1.342883465483879</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.492582252024441</v>
+        <v>1.558974303174388</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.526040087005107</v>
+        <v>1.592775338920539</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.442123455219345</v>
+        <v>1.478256280585633</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.375624288092531</v>
+        <v>1.381367645630782</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.264306607437611</v>
+        <v>1.23941064712708</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.485011861510046</v>
+        <v>1.428679964427914</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.382217401360165</v>
+        <v>1.325023818287285</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.348985827284189</v>
+        <v>1.291612763566832</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>1.139336532133207</v>
+        <v>1.081749441693376</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.7742260785849098</v>
+        <v>0.7179007374421715</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.5149042318377042</v>
+        <v>0.4589510653797859</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>0.02319216324598017</v>
+        <v>-0.03187682405848591</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.3570228751183393</v>
+        <v>-0.4111438053541718</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.400641025641022</v>
+        <v>-0.4545426848774241</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-0.3370485765372209</v>
+        <v>-0.3916284688650151</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.5389433116808959</v>
+        <v>-0.5932158650264938</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.3378289354749953</v>
+        <v>-0.3923128607641289</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.4350699331793919</v>
+        <v>-0.4894651965746775</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.001652</t>
+          <t>X &gt; 0.001654</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1655</v>
+        <v>1658</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.5000527684233731</v>
+        <v>0.5057875019526463</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.185898274800067</v>
+        <v>1.192645318987445</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.547999612515738</v>
+        <v>1.557510885341074</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.254626719743001</v>
+        <v>1.265229942821414</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2.390858436220455</v>
+        <v>2.431843316427987</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.436881908086093</v>
+        <v>1.476982579448439</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.985337097353387</v>
+        <v>2.027149280173468</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.667743412795794</v>
+        <v>2.710476296958852</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.348899117458075</v>
+        <v>2.391386555796643</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.211902468527398</v>
+        <v>2.219432418221693</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>2.16174973231233</v>
+        <v>2.132915137306689</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>2.279774978330934</v>
+        <v>2.21474265693562</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.335542125652168</v>
+        <v>2.233407513156415</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.174390010584098</v>
+        <v>2.109393140155873</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>2.2981198191085</v>
+        <v>2.27045281112779</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>2.050314125201893</v>
+        <v>2.059502307846678</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>1.434582863322682</v>
+        <v>1.480723242723144</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>0.7877571835308359</v>
+        <v>0.833713864203169</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.498197168234995</v>
+        <v>0.5074365704287018</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.7214436407474452</v>
+        <v>0.6942823803967286</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>0.8779395186256806</v>
+        <v>0.8143868148403399</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>0.6576248612495945</v>
+        <v>0.5578179618649699</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>1.08979844580292</v>
+        <v>0.9893040834554228</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>1.050599812724151</v>
+        <v>0.9500453761428602</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.002447</t>
+          <t>X &gt; 0.002449</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1378</v>
+        <v>1381</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.166919056676953</v>
+        <v>1.167540449836288</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.77104990041412</v>
+        <v>1.772749190170494</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2.209962153090991</v>
+        <v>2.21470121850755</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.712931845678185</v>
+        <v>1.718666938761118</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.865003101116564</v>
+        <v>2.901314644088025</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2.401878696782312</v>
+        <v>2.437521611096471</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>3.074099269930599</v>
+        <v>3.184011105080309</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3.590342312273307</v>
+        <v>3.701172039213709</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>3.270586700995359</v>
+        <v>3.381126321634554</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>3.797329324908006</v>
+        <v>3.909729083775943</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.710416915722774</v>
+        <v>3.822255826444021</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>4.298375035369261</v>
+        <v>4.411185381781266</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.329953181043969</v>
+        <v>4.372622013406712</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.67507035844892</v>
+        <v>3.717703657567498</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>3.738682472012776</v>
+        <v>3.782626158974651</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>3.466690498512762</v>
+        <v>3.50933412213238</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>3.188088133843607</v>
+        <v>3.230803825357377</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>2.794087376707864</v>
+        <v>2.836736801941107</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>2.838534657018755</v>
+        <v>2.835708443169118</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>3.215448625180898</v>
+        <v>3.167167412934688</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>3.441683732928183</v>
+        <v>3.34768704395637</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>3.339177868692765</v>
+        <v>3.199534502648497</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>3.587363719245481</v>
+        <v>3.447325889697574</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>3.775070234851761</v>
+        <v>3.634416852206513</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.003243</t>
+          <t>X &gt; 0.003244</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.953184867311933</v>
+        <v>1.986459159630762</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.894762120195281</v>
+        <v>1.928435128808623</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.484581951312101</v>
+        <v>2.519936374980588</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>2.047541405646619</v>
+        <v>2.083735123065523</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.066035458260949</v>
+        <v>3.131708488156626</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>3.160949148758505</v>
+        <v>3.226423751744775</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>3.402843164305956</v>
+        <v>3.469235215455903</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>4.692554201444217</v>
+        <v>4.759289453359649</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>4.180564731411508</v>
+        <v>4.24727110021901</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>4.974995003298901</v>
+        <v>5.042621106839341</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>4.603597812849664</v>
+        <v>4.670924291436691</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>4.509005754393215</v>
+        <v>4.576676733007147</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.21477283848909</v>
+        <v>4.283772968734048</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>3.993416027454735</v>
+        <v>4.062694092287458</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>3.703488478454339</v>
+        <v>3.773554484743805</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>3.191537457965026</v>
+        <v>3.260930336576102</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>3.057443763816103</v>
+        <v>3.127013199598629</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>2.860209425211593</v>
+        <v>2.929921573268217</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>2.799579820615726</v>
+        <v>2.869060186664861</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>3.321214219759923</v>
+        <v>3.33265876416057</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>3.390487206528853</v>
+        <v>3.34361813124989</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>3.650617893361286</v>
+        <v>3.544524937368458</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>4.354693775915642</v>
+        <v>4.188003339887416</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>4.245456861182923</v>
+        <v>4.078780171037536</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.004038</t>
+          <t>X &gt; 0.004039</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.912497471190655</v>
+        <v>3.945771763509484</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>4.055219208637141</v>
+        <v>4.088892217250482</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>4.049210500823392</v>
+        <v>4.084564924491879</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.976994248562143</v>
+        <v>3.013187965981047</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>2.970147402606187</v>
+        <v>3.035820432501865</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>3.754683580726478</v>
+        <v>3.820158183712749</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>3.459714700763264</v>
+        <v>3.526106751913211</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>4.375903185471692</v>
+        <v>4.442638437387124</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>4.178470624448927</v>
+        <v>4.245176993256429</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>5.0772755959973</v>
+        <v>5.144901699537741</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>4.634788984976446</v>
+        <v>4.702115463563473</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>3.997272142433438</v>
+        <v>4.064943121047371</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>3.828575428127891</v>
+        <v>3.89757555837285</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3.726692930116236</v>
+        <v>3.795970994948959</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>4.023556195260532</v>
+        <v>4.093622201549998</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>3.423873114654917</v>
+        <v>3.493265993265993</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>3.528728046551393</v>
+        <v>3.598297482333919</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>2.826373065342615</v>
+        <v>2.896085213399239</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>3.04249622827443</v>
+        <v>3.111976594323565</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>3.587962962962962</v>
+        <v>3.657245343359691</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>3.359311552724535</v>
+        <v>3.35364780143906</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>3.718419385658834</v>
+        <v>3.636224779098065</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>4.189492603520229</v>
+        <v>4.030173804602811</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>4.670464677098913</v>
+        <v>4.432238803470334</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.004833</t>
+          <t>X &gt; 0.004834</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4.81644463198505</v>
+        <v>4.849718924303879</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>4.638501821743247</v>
+        <v>4.672174830356589</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>5.557291923694841</v>
+        <v>5.592646347363328</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>4.214567792891621</v>
+        <v>4.250761510310525</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>5.264392347490215</v>
+        <v>5.330065377385893</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>4.822626142886939</v>
+        <v>4.88810074587321</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>5.622087054858071</v>
+        <v>5.688479106008018</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>6.601394044559633</v>
+        <v>6.668129296475065</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>6.32844470077724</v>
+        <v>6.395151069584742</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>7.598634447240507</v>
+        <v>7.666260550780947</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>7.244062896745788</v>
+        <v>7.311389375332816</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>6.336038175660818</v>
+        <v>6.40370915427475</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>6.626641296796315</v>
+        <v>6.695641427041274</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>6.562517190164478</v>
+        <v>6.631795254997201</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>7.475912995152335</v>
+        <v>7.5459790014418</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>6.655878705151075</v>
+        <v>6.725271583762151</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>7.150715828612221</v>
+        <v>7.220285264394747</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>6.416801594906872</v>
+        <v>6.486513742963496</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>6.790157462241204</v>
+        <v>6.859637828290339</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>7.448899371069189</v>
+        <v>7.518181751465917</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>6.5912335532662</v>
+        <v>6.661170174694853</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>6.462537448745259</v>
+        <v>6.428091508883234</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>6.526676484175944</v>
+        <v>6.388100812560253</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>6.555389263047026</v>
+        <v>6.312268559336978</v>
       </c>
     </row>
     <row r="28">
@@ -4988,79 +4988,79 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>5.859776899333944</v>
+        <v>5.893051191652773</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>4.889008164350635</v>
+        <v>4.922681172963976</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>6.203544988400097</v>
+        <v>6.238899412068584</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>4.854158454867957</v>
+        <v>4.89035217228686</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>5.971939517301536</v>
+        <v>6.037612547197213</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>5.523510909969339</v>
+        <v>5.58898551295561</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>5.598102405033956</v>
+        <v>5.664494456183903</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>6.378869793413699</v>
+        <v>6.445605045329131</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>6.632250265215994</v>
+        <v>6.698956634023496</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>8.400787735802503</v>
+        <v>8.468413839342944</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>7.615824969019528</v>
+        <v>7.683151447606555</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>6.065544624866661</v>
+        <v>6.133215603480593</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>6.635968660616804</v>
+        <v>6.704968790861763</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>5.779018629243474</v>
+        <v>5.848296694076197</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>6.391273830884138</v>
+        <v>6.461339837173604</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>4.867689812708896</v>
+        <v>4.937082691319972</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>5.792918152458284</v>
+        <v>5.862487588240811</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>4.628612702464693</v>
+        <v>4.698324850521317</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>6.115922306074488</v>
+        <v>6.185402672123622</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>6.514830508474574</v>
+        <v>6.584112888871303</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>6.183494506256288</v>
+        <v>6.253431127684941</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>6.319403857393333</v>
+        <v>6.389449573055494</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>6.80604343065513</v>
+        <v>6.875788692317215</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>7.508287704399002</v>
+        <v>7.435549659432915</v>
       </c>
     </row>
     <row r="29">
@@ -5073,158 +5073,158 @@
         <v>382</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>5.749962363882709</v>
+        <v>5.783236656201538</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>4.367666430390216</v>
+        <v>4.401339439003557</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.807547118136547</v>
+        <v>5.842901541805034</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5.09375380494339</v>
+        <v>5.129947522362293</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>7.084504962327713</v>
+        <v>7.150177992223391</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>7.271669575334499</v>
+        <v>7.33714417832077</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>8.33126417626476</v>
+        <v>8.397656227414707</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>9.361610054306411</v>
+        <v>9.428345306221843</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>8.879565909904969</v>
+        <v>8.94627227871247</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>9.938191232119827</v>
+        <v>10.00581733566027</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>9.950770394523119</v>
+        <v>10.01809687311015</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>8.62455607220005</v>
+        <v>8.692227050813983</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>7.238284749000861</v>
+        <v>7.30728487924582</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>7.016927937966507</v>
+        <v>7.08620600279923</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>6.881556908353296</v>
+        <v>6.951622914642762</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>4.858815910854254</v>
+        <v>4.92820878946533</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>5.510062530841466</v>
+        <v>5.579631966623992</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>4.619738800610051</v>
+        <v>4.689450948666675</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>5.882982382390033</v>
+        <v>5.952462748439167</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>6.855366492146601</v>
+        <v>6.92464887254333</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>6.835726292572723</v>
+        <v>6.905662914001375</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>6.759771236930114</v>
+        <v>6.829816952592275</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>7.558106612836333</v>
+        <v>7.627851874498418</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>8.005725482991942</v>
+        <v>8.075579830699219</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.007219</t>
+          <t>X &gt; 0.00722</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>314</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>4.924604708898883</v>
+        <v>4.957879001217712</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>5.544843206993413</v>
+        <v>5.578516215606754</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>6.971384781123831</v>
+        <v>7.006739204792318</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>6.257591467930673</v>
+        <v>6.293785185349577</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>7.803149708384339</v>
+        <v>7.868822738280016</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>6.079486295913412</v>
+        <v>6.144960898899683</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.943562839018625</v>
+        <v>6.009954890168572</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>7.257364881398146</v>
+        <v>7.324100133313578</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>7.29888094642078</v>
+        <v>7.365587315228282</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>8.754344898708673</v>
+        <v>8.821971002249114</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>8.710232828244401</v>
+        <v>8.777559306831428</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>7.475724912030643</v>
+        <v>7.543395890644575</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>6.669705031123122</v>
+        <v>6.738705161368081</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>7.722233570407234</v>
+        <v>7.791511635239956</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>8.337187681688398</v>
+        <v>8.407253687977864</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>7.33989104341169</v>
+        <v>7.409283922022766</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>7.52426868684239</v>
+        <v>7.593838122624916</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>6.145399920428645</v>
+        <v>6.215112068485269</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>6.679994420940069</v>
+        <v>6.749474786989204</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>7.822452229299358</v>
+        <v>7.891734609696087</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>7.916194495460637</v>
+        <v>7.98613111688929</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>7.203296764658795</v>
+        <v>7.273342480320956</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>8.433485943879781</v>
+        <v>8.503231205541866</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>8.357544604611313</v>
+        <v>8.42739895231859</v>
       </c>
     </row>
     <row r="31">
@@ -5237,76 +5237,76 @@
         <v>252</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>6.246513514884121</v>
+        <v>6.27978780720295</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>8.292290381192181</v>
+        <v>8.325963389805523</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>8.439891504407626</v>
+        <v>8.475245928076113</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>6.932447397563678</v>
+        <v>6.968641114982582</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>10.13860618396819</v>
+        <v>10.20427921386387</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>7.944818416022613</v>
+        <v>8.010293019008884</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>6.378301490317781</v>
+        <v>6.444693541467728</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>6.496572241624619</v>
+        <v>6.563307493540051</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>5.347612116171064</v>
+        <v>5.414318484978565</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>5.764252895877824</v>
+        <v>5.831878999418265</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>6.435437559818567</v>
+        <v>6.502764038405594</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>5.759518259518259</v>
+        <v>5.827189238132192</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>6.222328628332711</v>
+        <v>6.29132875857767</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>7.588273404599938</v>
+        <v>7.657551469432661</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>8.119818356038827</v>
+        <v>8.189884362328293</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>7.127576818358612</v>
+        <v>7.196969696969688</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>7.390308521035095</v>
+        <v>7.459877956817621</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>6.491674311289017</v>
+        <v>6.561386459345641</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>6.707797474220833</v>
+        <v>6.777277840269967</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>8.482142857142861</v>
+        <v>8.55142523753959</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>7.938942448144907</v>
+        <v>8.00887906957356</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>7.862987392502298</v>
+        <v>7.933033108164459</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>10.1218895431114</v>
+        <v>10.19163480477349</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>10.44277360066832</v>
+        <v>10.5126279483756</v>
       </c>
     </row>
     <row r="32">
@@ -5319,76 +5319,76 @@
         <v>190</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>6.852194383722889</v>
+        <v>6.885468676041718</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>8.095966237499617</v>
+        <v>8.129639246112959</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>8.76152893130822</v>
+        <v>8.796883354976707</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>10.67931456548347</v>
+        <v>10.71550828290238</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>12.94562372782785</v>
+        <v>13.01129675772353</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>10.50120939346621</v>
+        <v>10.56668399645248</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>8.675711682464829</v>
+        <v>8.742103733614776</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>9.449788615893624</v>
+        <v>9.516523867809056</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>5.80709415460047</v>
+        <v>5.873800523407972</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>5.033258743831041</v>
+        <v>5.100884847371482</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>6.360249589893755</v>
+        <v>6.427576068480782</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>6.607471475892538</v>
+        <v>6.675142454506471</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>7.58824341530012</v>
+        <v>7.657243545545079</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>9.472149762160505</v>
+        <v>9.541427826993228</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>8.286902733649519</v>
+        <v>8.356968739938985</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>7.303015414849845</v>
+        <v>7.372408293460921</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>7.168921720700922</v>
+        <v>7.238491156483448</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>8.116569883553012</v>
+        <v>8.186282031609636</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>8.332693046484827</v>
+        <v>8.402173412533962</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>7.993421052631575</v>
+        <v>8.062703433028304</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>6.923904854159936</v>
+        <v>6.993841475588589</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>7.374265587991012</v>
+        <v>7.444311303653173</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>9.227988122894196</v>
+        <v>9.297733384556281</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>10.73099415204678</v>
+        <v>10.80084849975406</v>
       </c>
     </row>
     <row r="33">
@@ -5401,76 +5401,76 @@
         <v>138</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>5.021530768162251</v>
+        <v>5.05480506048108</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>5.410992934677338</v>
+        <v>5.44466594329068</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>8.319118557547718</v>
+        <v>8.354472981216205</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>9.054600606673411</v>
+        <v>9.090794324092315</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>13.7617945897653</v>
+        <v>13.82746761966098</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>11.05040847813441</v>
+        <v>11.11588308112069</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>9.552904664920952</v>
+        <v>9.619296716070899</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>11.44826306288066</v>
+        <v>11.51499831479609</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>9.315866084425025</v>
+        <v>9.382572453232527</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>11.44058139829328</v>
+        <v>11.50820750183372</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>12.43957834656804</v>
+        <v>12.50690482515507</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>10.7112090807743</v>
+        <v>10.77888005938823</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>11.035993224606</v>
+        <v>11.10499335485095</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>12.26391177589048</v>
+        <v>12.33318984072321</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>10.15570517453434</v>
+        <v>10.22577118082381</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>9.301489861836878</v>
+        <v>9.370882740447954</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>11.34130921116622</v>
+        <v>11.41087864694875</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>11.96096347623036</v>
+        <v>12.03067562428699</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>12.17708663916218</v>
+        <v>12.24656700521131</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>13.08876811594203</v>
+        <v>13.15805049633876</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>13.2702053881035</v>
+        <v>13.34014200953215</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>13.9188880136203</v>
+        <v>13.98893372928246</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>17.09221390474011</v>
+        <v>17.1619591664022</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>17.01627256547165</v>
+        <v>17.08612691317892</v>
       </c>
     </row>
     <row r="34">
@@ -5483,76 +5483,76 @@
         <v>107</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>7.073542145651068</v>
+        <v>7.106816437969897</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>4.869207752502071</v>
+        <v>4.902880761115412</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>8.102404484677614</v>
+        <v>8.1377589083461</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>8.323190610736795</v>
+        <v>8.359384328155699</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>15.43455633973144</v>
+        <v>15.50022936962712</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>13.75256207423355</v>
+        <v>13.81803667721982</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>10.17595762442252</v>
+        <v>10.24234967557246</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>12.70114129666096</v>
+        <v>12.7678765485764</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>10.87349848317892</v>
+        <v>10.94020485198642</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>14.77256026867118</v>
+        <v>14.84018637221162</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>15.98149897503885</v>
+        <v>16.04882545362587</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>11.9640873145546</v>
+        <v>12.03175829316854</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>11.77417553531979</v>
+        <v>11.84317566556475</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>14.35655704204245</v>
+        <v>14.42583510687517</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>12.76304636375281</v>
+        <v>12.83311237004228</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>13.35810641337419</v>
+        <v>13.42749929198527</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>14.1585921584776</v>
+        <v>14.22816159426013</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>14.98818818163467</v>
+        <v>15.05790032969129</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>15.20431134456648</v>
+        <v>15.27379171061562</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>16.32593457943925</v>
+        <v>16.39521695983598</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>16.71731360969363</v>
+        <v>16.78725023112228</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>17.57593799330336</v>
+        <v>17.64598370896552</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>19.71987203829016</v>
+        <v>19.78961729995224</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>19.64393069902169</v>
+        <v>19.71378504672897</v>
       </c>
     </row>
     <row r="35">
@@ -5565,76 +5565,76 @@
         <v>69</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>8.644719173959345</v>
+        <v>8.677993466278174</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>11.20809438395271</v>
+        <v>11.24176739256605</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>11.2176692821854</v>
+        <v>11.25302370585388</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>13.40242669362993</v>
+        <v>13.43862041104883</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>18.83425835788125</v>
+        <v>18.89993138777693</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>20.47069833320687</v>
+        <v>20.53617293619314</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>12.45145538955864</v>
+        <v>12.51784744070859</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>17.97000219331545</v>
+        <v>18.03673744523088</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>15.1129675337004</v>
+        <v>15.1796739025079</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>17.23768284756866</v>
+        <v>17.3053089511091</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>23.30914356395935</v>
+        <v>23.37647004254638</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>20.13149893584676</v>
+        <v>20.1991699144607</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>21.90555844199731</v>
+        <v>21.97455857224227</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>21.68420163096295</v>
+        <v>21.75347969579568</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>21.02527039192565</v>
+        <v>21.09533639821512</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>20.17105507922819</v>
+        <v>20.24044795783927</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>20.03696138507927</v>
+        <v>20.10653082086179</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>24.2798040559405</v>
+        <v>24.34951620399713</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>25.94520258119116</v>
+        <v>26.0146829472403</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>23.23369565217391</v>
+        <v>23.30297803257064</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>25.58904596781364</v>
+        <v>25.65898258924229</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>26.96236627448987</v>
+        <v>27.03241199015203</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>33.03424289024736</v>
+        <v>33.10398815190945</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>32.9583015509789</v>
+        <v>33.02815589868617</v>
       </c>
     </row>
   </sheetData>
@@ -5824,83 +5824,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.01187</t>
+          <t>X &lt; -0.01186</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>69</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1.398342362365149</v>
+        <v>1.431616654683978</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.3861085145980141</v>
+        <v>-0.3524355059846727</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>3.971292470591202</v>
+        <v>4.006646894259688</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>9.054600606673411</v>
+        <v>9.090794324092315</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>7.240055459330513</v>
+        <v>7.30572848922619</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>10.32577079697498</v>
+        <v>10.39124539996125</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>13.90073075187748</v>
+        <v>13.96712280302743</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>15.07145146867776</v>
+        <v>15.1381867205932</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>18.01151825833809</v>
+        <v>18.07822462714559</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>15.7884074852498</v>
+        <v>15.85603358879024</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>13.16421602772746</v>
+        <v>13.23154250631449</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>18.68222357352792</v>
+        <v>18.74989455214185</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>20.45628307967846</v>
+        <v>20.52528320992342</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>21.68420163096295</v>
+        <v>21.75347969579568</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>16.67744430496912</v>
+        <v>16.74751031125859</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>14.37395362995282</v>
+        <v>14.44334650856389</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>8.442758486528547</v>
+        <v>8.512327922311073</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>12.68560115738978</v>
+        <v>12.75531330544641</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>14.35099968264043</v>
+        <v>14.42048004868956</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>17.43659420289855</v>
+        <v>17.50587658329528</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>15.44411843158176</v>
+        <v>15.51405505301042</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>19.71598946289567</v>
+        <v>19.78603517855783</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>24.33859071633432</v>
+        <v>24.4083359779964</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>27.16120010170354</v>
+        <v>27.23105444941081</v>
       </c>
     </row>
     <row r="7">
@@ -5913,1716 +5913,1716 @@
         <v>87</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.3488670999963333</v>
+        <v>0.3821413923151624</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3.461967447420967</v>
+        <v>3.495640456034309</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>6.619968132760121</v>
+        <v>6.655322556428608</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>9.354450681635932</v>
+        <v>9.390644399054835</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>5.540905034542916</v>
+        <v>5.606578064438594</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>9.17634550961867</v>
+        <v>9.241820112604941</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>11.85175523963361</v>
+        <v>11.91814729078356</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>11.57320059411505</v>
+        <v>11.63993584603048</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>10.46529137178135</v>
+        <v>10.53199774058885</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>9.691455961011918</v>
+        <v>9.759082064552359</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>6.517539366058301</v>
+        <v>6.584865844645329</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>10.83614661200869</v>
+        <v>10.90381759062262</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>13.1599312555905</v>
+        <v>13.22893138583546</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>14.08799973191247</v>
+        <v>14.15727779674519</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>12.27964320551884</v>
+        <v>12.34970921180831</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>10.57585268042759</v>
+        <v>10.64524555903867</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>4.694632549497058</v>
+        <v>4.764201985279584</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>6.888499708114409</v>
+        <v>6.958211856171033</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>8.254048158402547</v>
+        <v>8.323528524451682</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>10.73994252873564</v>
+        <v>10.80922490913237</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>9.047316832381362</v>
+        <v>9.117253453810015</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>12.41963763880771</v>
+        <v>12.48968335446987</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>17.29211395471513</v>
+        <v>17.36185921637721</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>19.5150231901593</v>
+        <v>19.58487753786658</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.01028</t>
+          <t>X &lt; -0.01027</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>117</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.682668414297801</v>
+        <v>-0.6493941219789718</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.1631430742412761</v>
+        <v>-0.1294700656279346</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2.670660735176867</v>
+        <v>2.706015158845354</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>6.230371695487975</v>
+        <v>6.266565412906878</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1178040724420555</v>
+        <v>-0.05213104254637813</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4.342864814069003</v>
+        <v>4.408339417055274</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>7.843502955519249</v>
+        <v>7.909895006669196</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>7.564948310000688</v>
+        <v>7.63168356191612</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>6.75176352032247</v>
+        <v>6.818469889129972</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>6.832628964253892</v>
+        <v>6.900255067794333</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>3.688184812565815</v>
+        <v>3.755511291152843</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>7.682595182595179</v>
+        <v>7.750266161209112</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>8.267505673509753</v>
+        <v>8.336505803754712</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>8.90084971717625</v>
+        <v>8.970127782008973</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>7.387217623438097</v>
+        <v>7.457283629727563</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>6.272875963657761</v>
+        <v>6.342268842268837</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>1.010577141303713</v>
+        <v>1.080146577086239</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>2.614995434610144</v>
+        <v>2.684707582666768</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>2.831118597541959</v>
+        <v>2.900598963591094</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>5.582264957264954</v>
+        <v>5.651547337661682</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>3.329662838865289</v>
+        <v>3.399599460293942</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>5.817810347325242</v>
+        <v>5.887856062987403</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>9.511388932610792</v>
+        <v>9.581134194272877</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>11.14484930274404</v>
+        <v>11.21470365045132</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.009483</t>
+          <t>X &lt; -0.009478</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>147</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.7476473017322007</v>
+        <v>0.7809215940510299</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1.773016004774938</v>
+        <v>1.806689013388279</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4.414948193750035</v>
+        <v>4.450302617418522</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>7.102515424774566</v>
+        <v>7.13870914219347</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.6147966601586745</v>
+        <v>0.6804696900543519</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>4.203321817383156</v>
+        <v>4.268796420369426</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>6.831816229546817</v>
+        <v>6.898208280696764</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>7.913805801715327</v>
+        <v>7.980541053630759</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>7.275049757894422</v>
+        <v>7.341756126701924</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>7.181486455968532</v>
+        <v>7.249112559508973</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>4.734757287709719</v>
+        <v>4.802083766296747</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>7.857023928452492</v>
+        <v>7.924694907066424</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>8.773349036495965</v>
+        <v>8.842349166740924</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>9.912536443148689</v>
+        <v>9.981814507981412</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>9.253605204111388</v>
+        <v>9.323671210400853</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>9.16839314488923</v>
+        <v>9.237786023500306</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>4.272394688835554</v>
+        <v>4.34196412461808</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>4.847683381583806</v>
+        <v>4.91739552964043</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>4.38353443567209</v>
+        <v>4.453014801721224</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>6.611394557823118</v>
+        <v>6.680676938219847</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>4.7076499311381</v>
+        <v>4.777586552566753</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>5.992239093182555</v>
+        <v>6.062284808844716</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>8.307830586195301</v>
+        <v>8.377575847857386</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>9.592433464613912</v>
+        <v>9.662287812321189</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.008688</t>
+          <t>X &lt; -0.008683</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>188</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-1.014546937665692</v>
+        <v>-0.9812726453468628</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.2460222285410438</v>
+        <v>0.2796952371543853</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.9339813389229903</v>
+        <v>0.9693357625914771</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3.943592281048986</v>
+        <v>3.979785998467889</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.1450817592942144</v>
+        <v>-0.07940872939853705</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2.70165732179769</v>
+        <v>2.767131924783961</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4.58836565782876</v>
+        <v>4.654757708978707</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>4.309811012310199</v>
+        <v>4.376546264225631</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>3.819412183715812</v>
+        <v>3.886118552523314</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>4.641321453797445</v>
+        <v>4.708947557337886</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>3.85185093367874</v>
+        <v>3.919177412265768</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>6.232331498288943</v>
+        <v>6.300002476902876</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>6.703584960652869</v>
+        <v>6.772585090897827</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>5.418398362384472</v>
+        <v>5.487676427217195</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>5.291382016964199</v>
+        <v>5.361448023253665</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>4.290697385734511</v>
+        <v>4.360090264345587</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.09871545735058618</v>
+        <v>-0.02914602156806012</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.203698873445866</v>
+        <v>-0.1339867253892422</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.5194906041310645</v>
+        <v>-0.45001023808193</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.7313829787234027</v>
+        <v>0.8006653591201314</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.3437323238915724</v>
+        <v>-0.2737957024629196</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>0.6441424076998672</v>
+        <v>0.7141881233620282</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>2.514662255033059</v>
+        <v>2.584407516695144</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>4.034465596615654</v>
+        <v>4.104319944322931</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.007892</t>
+          <t>X &lt; -0.007888</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>234</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.1720324404030507</v>
+        <v>0.2053067327218798</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.1631430742412761</v>
+        <v>-0.1294700656279346</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.5339085984247234</v>
+        <v>0.5692630220932102</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.384217849334135</v>
+        <v>2.420411566753039</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.399855354493333</v>
+        <v>-1.334182324597656</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.4967109679151562</v>
+        <v>0.562185570901427</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.14264825466455</v>
+        <v>3.209040305814497</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2.009392754445138</v>
+        <v>2.07612800636057</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.3415071100660541</v>
+        <v>0.4082134788735559</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2.131774263399194</v>
+        <v>2.199400366939635</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>2.406133530514531</v>
+        <v>2.473460009101558</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>4.263791763791765</v>
+        <v>4.331462742405698</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>5.703403109407184</v>
+        <v>5.772403239652142</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>3.772644588971119</v>
+        <v>3.841922653803842</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>3.113713349933818</v>
+        <v>3.183779356223283</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>1.999371690153495</v>
+        <v>2.068764568764571</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-1.126174995448416</v>
+        <v>-1.05660555966589</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-1.658508838894122</v>
+        <v>-1.588796690837498</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-1.869736103312746</v>
+        <v>-1.800255737263612</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-1.255341880341874</v>
+        <v>-1.186059499945145</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-2.653243144040694</v>
+        <v>-2.583306522612041</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-1.874497344982437</v>
+        <v>-1.804451629320276</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.7450213237994561</v>
+        <v>-0.675276062137371</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.393612235717498</v>
+        <v>-0.3237578880102205</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.007097</t>
+          <t>X &lt; -0.007093</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.276861131778197</v>
+        <v>-1.422417079302271</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.981899660121144</v>
+        <v>-2.781084662635031</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.6544768365360554</v>
+        <v>-0.4648375000619254</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.6865243708187379</v>
+        <v>0.8699900504612117</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.73353993475326</v>
+        <v>-1.854878920379576</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.203909568321819</v>
+        <v>-1.32661580595456</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.105416080446076</v>
+        <v>0.9731078651038985</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.511792941776832</v>
+        <v>1.37749027700611</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.1590197603238295</v>
+        <v>-0.2875071827174054</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.7794735960300372</v>
+        <v>0.646061782884324</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.3689013562960568</v>
+        <v>0.2375275683909592</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.487067726793754</v>
+        <v>2.347856663236477</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>3.417371028854554</v>
+        <v>3.27247616634623</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>2.168616957546234</v>
+        <v>2.027506504916708</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.8247542116596165</v>
+        <v>0.6867693506808621</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>1.077348507856335</v>
+        <v>0.9398593442962024</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-1.454005460265186</v>
+        <v>-1.583136290974785</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-1.558988876360466</v>
+        <v>-1.687976994795967</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-1.342865713428651</v>
+        <v>-1.472085613871641</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-1.155821917808218</v>
+        <v>-1.285239803903615</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-3.068885340504799</v>
+        <v>-3.192973685180228</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-1.774977382448782</v>
+        <v>-1.903631933278746</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.8152707091173355</v>
+        <v>-0.9465633641414044</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>0.4786509653128235</v>
+        <v>0.3427920959459101</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.006302</t>
+          <t>X &lt; -0.006298</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>344</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-2.220633033657769</v>
+        <v>-2.18735874133894</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-3.137203897139308</v>
+        <v>-3.103530888525967</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.5071369193649815</v>
+        <v>-0.4717824956964947</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.2325581395348877</v>
+        <v>0.2687518569537914</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.586200017582186</v>
+        <v>-1.520526987686509</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.8176400557381882</v>
+        <v>-0.7521654527519175</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.897865905231043</v>
+        <v>1.96425795638099</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.619311259712482</v>
+        <v>1.686046511627914</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1.079431975897904</v>
+        <v>1.146138344705406</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.8869919139656872</v>
+        <v>0.9546180175061281</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.5828348654306055</v>
+        <v>-0.5155083868435781</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>1.46365262644332</v>
+        <v>1.531323605057253</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>2.955440477723627</v>
+        <v>3.024440607968586</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>1.280595294596246</v>
+        <v>1.349873359428969</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.9123617299775475</v>
+        <v>0.9824277362670131</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.3446310819245113</v>
+        <v>0.4140239605355873</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.952253309898822</v>
+        <v>-0.8826838741162959</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.7665390515754993</v>
+        <v>-0.6968269035188754</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-1.131811237480896</v>
+        <v>-1.062330871431762</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.9447674418604635</v>
+        <v>-0.8754850614637348</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-1.77866552527702</v>
+        <v>-1.708728903848368</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.6918298832452123</v>
+        <v>-0.6217841675830513</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.1263570423444875</v>
+        <v>-0.05661178068240247</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>0.6697946416428593</v>
+        <v>0.7396489893501368</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.005506</t>
+          <t>X &lt; -0.005503</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.973441133641948</v>
+        <v>-1.947844856095628</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.535374017900793</v>
+        <v>-2.61815784843337</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.253986046612781</v>
+        <v>-1.115000426876122</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.7533090755682181</v>
+        <v>0.8869776803779672</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.7457475575284036</v>
+        <v>-0.5800345116263159</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.3484465339364391</v>
+        <v>0.511909050036671</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.843154098027533</v>
+        <v>2.002403805060354</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>2.018114191738007</v>
+        <v>2.176681048090082</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2.059630256760641</v>
+        <v>2.218168230004785</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.739309585220234</v>
+        <v>1.897741241751099</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.8798820042630098</v>
+        <v>1.040579164456013</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.961332318475179</v>
+        <v>2.119295824356428</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>2.877657426518645</v>
+        <v>3.032332852522934</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.976028506640759</v>
+        <v>2.132520944402138</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>1.543854637217962</v>
+        <v>1.700621990712982</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>2.138914686839342</v>
+        <v>2.295008912655973</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.4175194053888376</v>
+        <v>0.5773813684386795</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.5392933589080684</v>
+        <v>0.6987850085088994</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>1.889203369912451</v>
+        <v>2.045898108890242</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>2.303004535147387</v>
+        <v>2.458988262749671</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>1.53304675653493</v>
+        <v>1.690197750892239</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>2.137363809735852</v>
+        <v>2.293084821157343</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>2.412138976217982</v>
+        <v>2.567559533639397</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>2.562955006564025</v>
+        <v>2.717971624307523</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.004711</t>
+          <t>X &lt; -0.004707</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-4.134526562288549</v>
+        <v>-4.280700861146777</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-3.548891763857362</v>
+        <v>-3.792473728631599</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.59448541394719</v>
+        <v>-2.569606263565063</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.7300098505289228</v>
+        <v>-0.6118910979025713</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.752738199088895</v>
+        <v>-2.602093335155729</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-2.381411523467008</v>
+        <v>-2.231303619646589</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.496819091985117</v>
+        <v>-1.348840538831048</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.591211674888577</v>
+        <v>-1.443228454172363</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.4447232341753349</v>
+        <v>-0.2988000957870725</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.6230619812062557</v>
+        <v>0.7665195222940895</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.5290971230913755</v>
+        <v>0.6729321056324835</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.907461783152399</v>
+        <v>1.864770937478596</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>2.44042912820116</v>
+        <v>2.39602063532837</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.850748191936603</v>
+        <v>1.80729470005825</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>2.849275516435206</v>
+        <v>2.803563167183569</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>2.89184937821129</v>
+        <v>2.84647950089127</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>2.757755684062367</v>
+        <v>2.712562363913797</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>3.205258455812384</v>
+        <v>3.159192248327905</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>4.34219193181972</v>
+        <v>4.29420127631105</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>3.792587476979747</v>
+        <v>3.745752968632019</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>3.249387067981793</v>
+        <v>3.203206800665988</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>3.541756137569386</v>
+        <v>3.495007898080416</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>4.000693366666617</v>
+        <v>3.953306139974238</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>4.293076152628352</v>
+        <v>4.245120945574492</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.003916</t>
+          <t>X &lt; -0.003912</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-3.674121405750796</v>
+        <v>-3.874856473806382</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-3.537598807187571</v>
+        <v>-3.819373911781781</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.832645183223391</v>
+        <v>-1.892516200249396</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.3451806347813289</v>
+        <v>-0.3272239395031562</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.968312055025507</v>
+        <v>-1.831304250291012</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.781147442018721</v>
+        <v>-1.644338064193633</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.453384643255141</v>
+        <v>-1.317385649182889</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.103008471163641</v>
+        <v>-0.9676536088496164</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.2753288841284203</v>
+        <v>-0.1412370705769916</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.6803954535298189</v>
+        <v>0.8126918373739613</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.7975220162426453</v>
+        <v>0.9297656082642973</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2.405220565597929</v>
+        <v>2.534846660075331</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>2.224125573525882</v>
+        <v>2.353599820848729</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2.002768762491527</v>
+        <v>2.132520944402138</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>2.60169915867435</v>
+        <v>2.730264616994262</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>3.196759208295731</v>
+        <v>3.324651538937253</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>3.062665514146808</v>
+        <v>3.19073440195978</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>3.7438456200641</v>
+        <v>3.870823054496519</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>3.959968782995915</v>
+        <v>4.086714435420845</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>3.518081761006286</v>
+        <v>3.645616760302538</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>2.817648647605822</v>
+        <v>2.946084721064921</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>3.213391705170757</v>
+        <v>3.341196373470581</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>3.016468758445342</v>
+        <v>3.144713472137873</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>3.097760123579384</v>
+        <v>3.225867090186185</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.00312</t>
+          <t>X &lt; -0.003117</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>723</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.98351367094417</v>
+        <v>-3.091396563981419</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.833639935609511</v>
+        <v>-2.943987047957847</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.368776084342947</v>
+        <v>-1.419152602686047</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.1461931873009732</v>
+        <v>-0.1265969802555063</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.617963663887949</v>
+        <v>-1.628133309156375</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.154173877990431</v>
+        <v>-1.08869927500416</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.235477077817627</v>
+        <v>-1.16908502666768</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.4075310317732601</v>
+        <v>-0.3407957798578281</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.1872353790308381</v>
+        <v>0.2539417478383399</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.5199006598243514</v>
+        <v>0.5875267633647923</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.209197686275786</v>
+        <v>1.276524164862813</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.483354128582349</v>
+        <v>1.551025107196281</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.741988774548872</v>
+        <v>1.810988904793831</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.658944549959884</v>
+        <v>1.728222614792607</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>1.968201416040145</v>
+        <v>2.038267422329611</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>1.73338594698933</v>
+        <v>1.802778825600406</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>2.014230012176505</v>
+        <v>2.083799447959031</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>2.462496941862689</v>
+        <v>2.532209089919313</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>2.678620104794504</v>
+        <v>2.748100470843639</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>2.450726141078839</v>
+        <v>2.520008521475567</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>1.769213145635518</v>
+        <v>1.839149767064171</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>2.246508435774373</v>
+        <v>2.316554151436534</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>2.244658429365771</v>
+        <v>2.314403691027856</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>2.583654849433401</v>
+        <v>2.653509197140679</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.002325</t>
+          <t>X &lt; -0.002322</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.516995948990754</v>
+        <v>-2.67232411101066</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.545882286248776</v>
+        <v>-2.702896639054515</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.424607140578814</v>
+        <v>-1.530147815181707</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.1786727169597242</v>
+        <v>0.1309971874237092</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.9183043851374819</v>
+        <v>-0.9879348980582634</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.6091885526185052</v>
+        <v>-0.6115966625641178</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.260103465160334</v>
+        <v>-1.261742666795513</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.050853232630125</v>
+        <v>-1.052743392912781</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.03372741150992908</v>
+        <v>-0.03683477372645427</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.1680469338182036</v>
+        <v>0.1646709875086785</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.3204549814213422</v>
+        <v>0.316927950011646</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.016970834044002</v>
+        <v>1.012599983835273</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.233943030191007</v>
+        <v>1.22926739322763</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.744293536229826</v>
+        <v>1.739004594734752</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>1.6951183947535</v>
+        <v>1.689874695448957</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>1.680422346813906</v>
+        <v>1.79705089875614</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>2.156084750225958</v>
+        <v>2.272147160073423</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>2.173052553642876</v>
+        <v>2.289109135911197</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>2.511126936086882</v>
+        <v>2.626803196494478</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>2.698170731707314</v>
+        <v>2.69184632680355</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>2.033019103197169</v>
+        <v>2.027497479178564</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>2.079015267066751</v>
+        <v>2.073454197428418</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>2.109887994524492</v>
+        <v>2.104323550592568</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>1.790044216231635</v>
+        <v>1.784885938051382</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.00153</t>
+          <t>X &lt; -0.001527</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>969</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.459909253330615</v>
+        <v>-1.538283010867872</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-2.35981238431264</v>
+        <v>-2.435582844019969</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.063032472200554</v>
+        <v>-1.148483659682242</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.6416348669210592</v>
+        <v>-0.6739220831361763</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.419701349571525</v>
+        <v>-1.467536783389811</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.9229392133449323</v>
+        <v>-0.9145965244373642</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.076610298959324</v>
+        <v>-1.010218247809377</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.7359698980382632</v>
+        <v>-0.6692346461228311</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.3375379110504255</v>
+        <v>0.4042442798579273</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.2860967211272296</v>
+        <v>0.3537228246676705</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.5604559882425661</v>
+        <v>0.6277824668295935</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.003756305613898</v>
+        <v>1.071427284227831</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.220854354412616</v>
+        <v>1.289854484657575</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.825090938631092</v>
+        <v>1.894369003463815</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>1.785354746033427</v>
+        <v>1.855420752322892</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>1.658020574808575</v>
+        <v>1.727413453419651</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>1.420727706253039</v>
+        <v>1.490297142035566</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>1.934939336597388</v>
+        <v>2.004651484654012</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>2.151062499529203</v>
+        <v>2.220542865578338</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>2.131707946336427</v>
+        <v>2.200990326733155</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>1.485308362931875</v>
+        <v>1.555244984360527</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>1.512552481695863</v>
+        <v>1.582598197358024</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>1.374530950551573</v>
+        <v>1.444276212213659</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>1.298589611283106</v>
+        <v>1.368443958990383</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.0007342</t>
+          <t>X &lt; -0.0007318</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1119</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.399366722432326</v>
+        <v>-1.46306933565419</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.402154063252262</v>
+        <v>-2.463168395767546</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.382866910844086</v>
+        <v>-1.451042782718382</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.203005174886208</v>
+        <v>-1.224636195941784</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.747005969740471</v>
+        <v>-1.779068987147127</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.023648327243066</v>
+        <v>-1.007564123848262</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.170955924891373</v>
+        <v>-1.104563873741427</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.5558555212588985</v>
+        <v>-0.4891202693434664</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.111219078169448</v>
+        <v>0.1779254469769498</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.4097697263812492</v>
+        <v>0.4773958299216901</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.5947634885814779</v>
+        <v>0.6620899671685052</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.4050350900216841</v>
+        <v>0.4727060686356168</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.8891229600063966</v>
+        <v>0.9581230902513553</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.9358626637173444</v>
+        <v>1.005140728550067</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.7237589492555543</v>
+        <v>0.7938249555450199</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>1.140087989046734</v>
+        <v>1.20948086765781</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.7378977801525011</v>
+        <v>0.8074672159350271</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>1.347838403378042</v>
+        <v>1.417550551434665</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>1.653327071224965</v>
+        <v>1.722807437274099</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>1.48290884718498</v>
+        <v>1.552191227581709</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>1.297170457847443</v>
+        <v>1.367107079276096</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>1.131849897289726</v>
+        <v>1.201895612951887</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>1.406625063771855</v>
+        <v>1.47637032543394</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>1.330683724503388</v>
+        <v>1.400538072210665</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 6.112e-05</t>
+          <t>X &lt; 6.337e-05</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.771533886724917</v>
+        <v>-1.783379334811798</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.676471330143791</v>
+        <v>-2.685790831356897</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.019119335700772</v>
+        <v>-2.034751540919082</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.700548134745354</v>
+        <v>-1.719302147428763</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.024243688805328</v>
+        <v>-2.089763878658303</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.184287771907115</v>
+        <v>-1.252590216477088</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.804365515878622</v>
+        <v>-1.830309783040541</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.471766609067174</v>
+        <v>-1.456678956324438</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.9718853797970226</v>
+        <v>-0.9149103842960713</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.7525962680301532</v>
+        <v>-0.6524297367988652</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.7838137770798355</v>
+        <v>-0.6837136060873235</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.8337250984309748</v>
+        <v>-0.7334553759475355</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.4303324360930603</v>
+        <v>-0.3298998855517397</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.2697182769211608</v>
+        <v>-0.1692993726853587</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.1647075755459255</v>
+        <v>-0.0640838916399602</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.4303524740754554</v>
+        <v>0.5303030303030312</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.009317996238479509</v>
+        <v>0.09104238187516955</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.6496405280787627</v>
+        <v>0.7495604566799443</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>1.094946273134347</v>
+        <v>1.194459471192054</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>1.129201680672267</v>
+        <v>1.228633525434894</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>1.12076062996308</v>
+        <v>1.220438502507037</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>1.503170738567995</v>
+        <v>1.602607808273504</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>1.701551711008875</v>
+        <v>1.80074664289296</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>1.854792953864155</v>
+        <v>1.953922023257469</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.0008565</t>
+          <t>X &lt; 0.0008585</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1513</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.305700353119221</v>
+        <v>-1.344259186922784</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.474734708413564</v>
+        <v>-1.513378343823803</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.825808978684151</v>
+        <v>-1.86567975450528</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.845058331161567</v>
+        <v>-1.885965816547426</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.306424598793448</v>
+        <v>-2.383440084381739</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.621423922496959</v>
+        <v>-1.700042728193232</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.895796347848744</v>
+        <v>-1.974906182479813</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.939573752353489</v>
+        <v>-2.019055357115484</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.831963834059209</v>
+        <v>-1.87512323718083</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.746579152297251</v>
+        <v>-1.753379526434315</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.604407591725199</v>
+        <v>-1.574231621152826</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.8835014952001</v>
+        <v>-1.815830516586168</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.752209501525982</v>
+        <v>-1.683209371281023</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.709190899473754</v>
+        <v>-1.639912834641031</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-1.442808192708014</v>
+        <v>-1.372742186418549</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-0.9799358496299178</v>
+        <v>-0.9105429710188417</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-0.6513725708773208</v>
+        <v>-0.5818031350947948</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-0.02932360098449749</v>
+        <v>0.04038854707212636</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.4511749750339007</v>
+        <v>0.5206553410830352</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.5060310641110348</v>
+        <v>0.5753134445077634</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.4254876280146007</v>
+        <v>0.4954242494432535</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>0.6800018387302273</v>
+        <v>0.7500475543923883</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>0.4260261790391837</v>
+        <v>0.4957714407012688</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>0.5483663995856531</v>
+        <v>0.6182207472929306</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.001652</t>
+          <t>X &lt; 0.001654</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.4682721369093983</v>
+        <v>-0.4720305121980957</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.111153982859946</v>
+        <v>-1.113671049828916</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.451249636733507</v>
+        <v>-1.4551926519975</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.176875204716666</v>
+        <v>-1.182776755536416</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.243956762292598</v>
+        <v>-2.274641528125997</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.34935610657832</v>
+        <v>-1.382282909000125</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.865455004003039</v>
+        <v>-1.898242207208028</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.508070458670254</v>
+        <v>-2.539545359312797</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.209557644388525</v>
+        <v>-2.24184069230737</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.079438252898065</v>
+        <v>-2.081812595220342</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.031067686347704</v>
+        <v>-2.001788374776275</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.140670064398876</v>
+        <v>-2.079758341501616</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.191714955202407</v>
+        <v>-2.098469848612247</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.041640366071327</v>
+        <v>-1.980757081919371</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-2.159036775757478</v>
+        <v>-2.13071291479072</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-1.927318484414442</v>
+        <v>-1.931582909843783</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-1.349287732717443</v>
+        <v>-1.387916760542311</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-0.7413397630848237</v>
+        <v>-0.7819011381792365</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.4685593763569784</v>
+        <v>-0.4761699869483493</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.6781161473087849</v>
+        <v>-0.6518714657571181</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.8247159897345</v>
+        <v>-0.7650719369750689</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.6173849263969373</v>
+        <v>-0.5243362495446533</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-1.022496445467219</v>
+        <v>-0.9293632358168438</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.9851233371436123</v>
+        <v>-0.8919452059144106</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.002447</t>
+          <t>X &lt; 0.002449</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.7843690988056835</v>
+        <v>-0.7823199816490174</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.191026755186186</v>
+        <v>-1.188420809503548</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.48691668443265</v>
+        <v>-1.485417936564474</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.153063071215271</v>
+        <v>-1.153283054976527</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.929520336713068</v>
+        <v>-1.947824346006669</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.618403172515443</v>
+        <v>-1.637247395894342</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.072359176611762</v>
+        <v>-2.139692593938811</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.421556413346138</v>
+        <v>-2.488439927191322</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.206968305303555</v>
+        <v>-2.274366586974985</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.563660383254962</v>
+        <v>-2.63121913521271</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.50620644771125</v>
+        <v>-2.573602632897789</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.904761254370626</v>
+        <v>-2.971587619582806</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.92753063144351</v>
+        <v>-2.947044953480258</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.485971347064165</v>
+        <v>-2.506866971436295</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-2.53023791748933</v>
+        <v>-2.551888769688745</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-2.347309026390242</v>
+        <v>-2.368672079506638</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-2.159722945295933</v>
+        <v>-2.181739106674442</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-1.893739926231</v>
+        <v>-1.916564238927478</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-1.922474745669398</v>
+        <v>-1.91680585381372</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-2.176175318315373</v>
+        <v>-2.141903438674177</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-2.327602955520966</v>
+        <v>-2.265093533166173</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-2.256643221741449</v>
+        <v>-2.165911021616679</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-2.42261242352572</v>
+        <v>-2.331964943495855</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-2.547525359268235</v>
+        <v>-2.456744822759269</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.003243</t>
+          <t>X &lt; 0.003244</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>2341</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.8975211514057335</v>
+        <v>-0.9112660723824533</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.8710441638217574</v>
+        <v>-0.88502272634571</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.14267578923306</v>
+        <v>-1.156972058652677</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.9420776246693308</v>
+        <v>-0.9571054548317832</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.411287658919271</v>
+        <v>-1.439072488835002</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.455594255418106</v>
+        <v>-1.483224489775807</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.567650654529388</v>
+        <v>-1.595524384197795</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.162724810529575</v>
+        <v>-2.189757965807239</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.927576422309691</v>
+        <v>-1.955007164601859</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.294848758968513</v>
+        <v>-2.322090603149462</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.124435942583673</v>
+        <v>-2.151841025039246</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.081670459012877</v>
+        <v>-2.109318698375738</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.946661166136423</v>
+        <v>-1.975163716762104</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.845210133742931</v>
+        <v>-1.874025700442381</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-1.711975057844143</v>
+        <v>-1.741393385041413</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-1.47594991656743</v>
+        <v>-1.505472097465287</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-1.41454077677195</v>
+        <v>-1.444261741953525</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-1.323854405179063</v>
+        <v>-1.353808604187009</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-1.296345376141581</v>
+        <v>-1.326252128931635</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-1.536469457496793</v>
+        <v>-1.541212500149349</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-1.567068414123973</v>
+        <v>-1.546940697513826</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-1.68574025746414</v>
+        <v>-1.640591388602651</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-2.009000118747927</v>
+        <v>-1.939254857085842</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-1.956791094923695</v>
+        <v>-1.886936747216417</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.004038</t>
+          <t>X &lt; 0.004039</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>2587</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.25662332440006</v>
+        <v>-1.265368186228898</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.302962947266529</v>
+        <v>-1.311768028301522</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.301531946693238</v>
+        <v>-1.310882224616449</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.9572586193033032</v>
+        <v>-0.96741017549909</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.9554240491857868</v>
+        <v>-0.9750505379908176</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.20825457788083</v>
+        <v>-1.227436621791782</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.113762001745698</v>
+        <v>-1.133391455972109</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.409246235567451</v>
+        <v>-1.428539520588942</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.346181644597287</v>
+        <v>-1.365570001289626</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.63638031338072</v>
+        <v>-1.65562580642564</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.494344522505891</v>
+        <v>-1.513719478077924</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.289293558079684</v>
+        <v>-1.309102498005636</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.235357607302646</v>
+        <v>-1.255685428159389</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.202947158699295</v>
+        <v>-1.223422303724398</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-1.299273354719546</v>
+        <v>-1.319862011824867</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-1.106052411025146</v>
+        <v>-1.12672972499562</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-1.140365009638437</v>
+        <v>-1.161054353397653</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.9137405390852749</v>
+        <v>-0.9348335224123261</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.9839912453885944</v>
+        <v>-1.004909108583639</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-1.160852338616159</v>
+        <v>-1.181441278422255</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-1.085575747227558</v>
+        <v>-1.083785023090535</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.200185615394332</v>
+        <v>-1.175558184667857</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-1.350613386677956</v>
+        <v>-1.30342174437888</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-1.503864350994746</v>
+        <v>-1.434010003287469</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.004833</t>
+          <t>X &lt; 0.004834</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2787</v>
+        <v>2788</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.091292763071785</v>
+        <v>-1.097268315851032</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.051349664514866</v>
+        <v>-1.057474445589612</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.260049077885895</v>
+        <v>-1.266259550346419</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.9559433367614361</v>
+        <v>-0.9627793164378531</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.194489308956037</v>
+        <v>-1.207667110800649</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.094643193032155</v>
+        <v>-1.10792304860135</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.276561002102717</v>
+        <v>-1.289794193019993</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.49945950440712</v>
+        <v>-1.512457286932289</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.437974572952605</v>
+        <v>-1.451058180612151</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.727209259630079</v>
+        <v>-1.740093401247918</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.647202002978311</v>
+        <v>-1.66013696633761</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.441244735236147</v>
+        <v>-1.45455679361384</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.507886892580494</v>
+        <v>-1.521410485029747</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.493829968842022</v>
+        <v>-1.507441666253825</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-1.702356127789784</v>
+        <v>-1.715853644947067</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-1.516167212204898</v>
+        <v>-1.529782806606832</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-1.629471611249514</v>
+        <v>-1.642970099518806</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-1.462754772172318</v>
+        <v>-1.476529255735421</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-1.548418840439368</v>
+        <v>-1.56202279226374</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-1.69924677187948</v>
+        <v>-1.712594410434221</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-1.504135105804558</v>
+        <v>-1.517916241886752</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-1.472447534967081</v>
+        <v>-1.46532838697123</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-1.484719372431847</v>
+        <v>-1.456734355248585</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-1.488898960713591</v>
+        <v>-1.439957964038129</v>
       </c>
     </row>
     <row r="28">
@@ -7632,79 +7632,79 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2949</v>
+        <v>2952</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.9309372926575605</v>
+        <v>-0.9349647604907858</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.7769736880718909</v>
+        <v>-0.7812728694146003</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.9862153029723402</v>
+        <v>-0.9905013530092148</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.7719551181595889</v>
+        <v>-0.7766642750065174</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.9500355416805988</v>
+        <v>-0.9591898762292388</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.8789943187813591</v>
+        <v>-0.8882158795000237</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.8911650371588564</v>
+        <v>-0.9005191590834656</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.015798428640785</v>
+        <v>-1.025042311790877</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.056504260945644</v>
+        <v>-1.065691786740501</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.33868055749452</v>
+        <v>-1.347636996685729</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.214005196007179</v>
+        <v>-1.223085154559961</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.967208467208458</v>
+        <v>-0.976679407841722</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.058525585607008</v>
+        <v>-1.068088177282064</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.9221422559171444</v>
+        <v>-0.9319365427427257</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-1.020183039627092</v>
+        <v>-1.029973793700073</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.7772495235448531</v>
+        <v>-0.7872645372645408</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.9252986016786267</v>
+        <v>-0.9351450292834329</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.7395752185387039</v>
+        <v>-0.7496988943360563</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.977553446822597</v>
+        <v>-0.9873216304505661</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-1.041666666666664</v>
+        <v>-1.051319784691231</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.9890238586760276</v>
+        <v>-0.9988560041513637</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-1.01110461718293</v>
+        <v>-1.020927623047463</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-1.089336215418527</v>
+        <v>-1.099008554952164</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-1.19918735461917</v>
+        <v>-1.188881923865971</v>
       </c>
     </row>
     <row r="29">
@@ -7714,161 +7714,161 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3038</v>
+        <v>3042</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.7175712587400156</v>
+        <v>-0.720781860577155</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.5452446328134215</v>
+        <v>-0.5487309613901346</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.7252314479006756</v>
+        <v>-0.7286935647957904</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.6363027970857971</v>
+        <v>-0.6399869214704026</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.8852734365748134</v>
+        <v>-0.8923123139592732</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.9089586969168053</v>
+        <v>-0.9159441425223989</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.041748908456022</v>
+        <v>-1.048677567464019</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.170967596838594</v>
+        <v>-1.177772369841968</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.11103641584792</v>
+        <v>-1.11791822390191</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.243902048056931</v>
+        <v>-1.250727166957532</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.245884723273633</v>
+        <v>-1.252672014902799</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.080190301501773</v>
+        <v>-1.087239925805804</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.9068628317869241</v>
+        <v>-0.914308163731377</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.879418133957742</v>
+        <v>-0.8869366622114327</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.8627353918578891</v>
+        <v>-0.8703769103223635</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.6093459218471153</v>
+        <v>-0.6172379533035226</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.6912459398297131</v>
+        <v>-0.6990552349132031</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.5797438310883862</v>
+        <v>-0.5877199023591402</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.7385143838557227</v>
+        <v>-0.7462555857905357</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.860864562787647</v>
+        <v>-0.868422806733939</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.8586805142264922</v>
+        <v>-0.8663261849420465</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.8494186225353033</v>
+        <v>-0.8570926661925924</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.9500482810475503</v>
+        <v>-0.9575548524674318</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-1.006644876399911</v>
+        <v>-1.014093193730147</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.007219</t>
+          <t>X &lt; 0.00722</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3106</v>
+        <v>3110</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.4941917157539848</v>
+        <v>-0.496895629231517</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.5566114984002368</v>
+        <v>-0.559276529917156</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.7000367193069721</v>
+        <v>-0.7026879943483877</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.6285616509693668</v>
+        <v>-0.6313893125238863</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.7840604826984574</v>
+        <v>-0.7896485585873876</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.6110623229567267</v>
+        <v>-0.6168534917693478</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.5975916527223291</v>
+        <v>-0.6034940311841765</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.7299207472001967</v>
+        <v>-0.7356901605439674</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.7343315018186942</v>
+        <v>-0.7400942134341264</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.881046249421324</v>
+        <v>-0.8867153952324571</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.876887819194863</v>
+        <v>-0.8825339808981951</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.7528472169267602</v>
+        <v>-0.7586887603018511</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.671892005060208</v>
+        <v>-0.6779728999261678</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.7781711621013727</v>
+        <v>-0.7841457222645261</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.8404099300321519</v>
+        <v>-0.8463859115181265</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.7401174655206404</v>
+        <v>-0.7461562384589939</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.7589528967775578</v>
+        <v>-0.7649872218492888</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.6200692721769272</v>
+        <v>-0.6262981994558317</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.6742263735696383</v>
+        <v>-0.6803643926531677</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.7897909967845678</v>
+        <v>-0.7957625778563155</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.7995127280716119</v>
+        <v>-0.805539727177397</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.7277461982312943</v>
+        <v>-0.7338783865105327</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.8523059499125409</v>
+        <v>-0.8582496298746847</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.8449030926748122</v>
+        <v>-0.8508692189800797</v>
       </c>
     </row>
     <row r="31">
@@ -7878,79 +7878,79 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3168</v>
+        <v>3172</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.4933003465217212</v>
+        <v>-0.4953072073286791</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.6550649454734909</v>
+        <v>-0.6569013068976233</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.6669340417405891</v>
+        <v>-0.6688888111102926</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.5479851769717783</v>
+        <v>-0.550155877498625</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.8016720296077864</v>
+        <v>-0.8058534509224984</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.6284037165215537</v>
+        <v>-0.6327880378652893</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.5046568212119595</v>
+        <v>-0.5092702328158936</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.5141759437466789</v>
+        <v>-0.5188059875696567</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.4233736265394654</v>
+        <v>-0.4281168052132358</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.4565027434824671</v>
+        <v>-0.4612785649257347</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.5098177507306829</v>
+        <v>-0.5145044074342806</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.4564146545278618</v>
+        <v>-0.4611971381938815</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.4932453017740954</v>
+        <v>-0.4980882334783416</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.601713309615846</v>
+        <v>-0.606443422469205</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.6440649120937394</v>
+        <v>-0.6488056772419668</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.5655382110284464</v>
+        <v>-0.5703259005145753</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.58656936922862</v>
+        <v>-0.5913460978666407</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.5154070341666142</v>
+        <v>-0.5202861509613257</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.5327339941706981</v>
+        <v>-0.5375744462537071</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.6738650693568715</v>
+        <v>-0.6785135893765712</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.6309093336274145</v>
+        <v>-0.6356653623724497</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.6250702911389823</v>
+        <v>-0.6298438384554004</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.8048962337848167</v>
+        <v>-0.8094207282706947</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.8306751727804382</v>
+        <v>-0.8351772518886094</v>
       </c>
     </row>
     <row r="32">
@@ -7960,79 +7960,79 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3230</v>
+        <v>3234</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.4002203913025966</v>
+        <v>-0.4016699565391164</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.4730115575414899</v>
+        <v>-0.4743954105532779</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.5120549052440992</v>
+        <v>-0.5134893509817502</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.6243291592128841</v>
+        <v>-0.6256750380305576</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.7570540191712212</v>
+        <v>-0.7599589252897161</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.6142948844700058</v>
+        <v>-0.6173646861396023</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.5076640651888837</v>
+        <v>-0.5109196276182075</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.5531299559518814</v>
+        <v>-0.5563506261180606</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.3400147578964905</v>
+        <v>-0.3434971066320358</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.2947962889420097</v>
+        <v>-0.2983891998154462</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.3726325692506478</v>
+        <v>-0.3761131669268067</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.3872361444847527</v>
+        <v>-0.3907199834738861</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.4448522829086841</v>
+        <v>-0.4483439980442441</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.5554655724723645</v>
+        <v>-0.5588382512727179</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.4861103795595625</v>
+        <v>-0.4896158065335783</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.42852777295289</v>
+        <v>-0.4320658777783919</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.4207893503037425</v>
+        <v>-0.4243484479271373</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.4765600364261644</v>
+        <v>-0.4800597487672249</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.4894008280779332</v>
+        <v>-0.4928721668358875</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.4696196660482386</v>
+        <v>-0.4731048956996275</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.4069105853047859</v>
+        <v>-0.4105127835532443</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.433511900284131</v>
+        <v>-0.4370887353813728</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.5426548261683379</v>
+        <v>-0.5460801678719278</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.631234950120394</v>
+        <v>-0.6345581988105309</v>
       </c>
     </row>
     <row r="33">
@@ -8042,79 +8042,79 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3282</v>
+        <v>3286</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.2096735993967869</v>
+        <v>-0.2108078266383728</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.2260039421868925</v>
+        <v>-0.2271353990852916</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.3475744356468695</v>
+        <v>-0.3486293533135267</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.3784175904666682</v>
+        <v>-0.3794705434739001</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.5753188892419416</v>
+        <v>-0.5773647599132232</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.462107990903796</v>
+        <v>-0.4642832521775588</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.3996061969563698</v>
+        <v>-0.4018961389094144</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.4790358710362526</v>
+        <v>-0.4812446297522328</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.389927060858561</v>
+        <v>-0.392243259177846</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.4790049250498924</v>
+        <v>-0.4812523137130427</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.5209899277166699</v>
+        <v>-0.5231745577057865</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.4487391782473722</v>
+        <v>-0.4510265155232247</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.4624862025495418</v>
+        <v>-0.464813188647085</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.5141007974097462</v>
+        <v>-0.5163774872632843</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.4258545469722748</v>
+        <v>-0.4282720555246371</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.390153678095281</v>
+        <v>-0.3925870729149352</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.4758591277412449</v>
+        <v>-0.4781965542905979</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.5020112407906865</v>
+        <v>-0.5043235832781292</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.5112375893533212</v>
+        <v>-0.5135297012212519</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.5496804625684675</v>
+        <v>-0.5519182275060075</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.5574698153906539</v>
+        <v>-0.5597262381621846</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.58489846098648</v>
+        <v>-0.5871267806085712</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.7184664998032773</v>
+        <v>-0.7205203422462745</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.7154922650929549</v>
+        <v>-0.7175549342722647</v>
       </c>
     </row>
     <row r="34">
@@ -8124,79 +8124,79 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3313</v>
+        <v>3317</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.2268791995157855</v>
+        <v>-0.2276734607373569</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.1562234571267567</v>
+        <v>-0.1571153762921114</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.26003517692277</v>
+        <v>-0.2608568613520106</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.2672011387185265</v>
+        <v>-0.2680413914032442</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.4956475175123884</v>
+        <v>-0.4971596350569882</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.4417664791182787</v>
+        <v>-0.4433373086844128</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.3269752149589138</v>
+        <v>-0.3287136818495071</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.4082373441702387</v>
+        <v>-0.4098898261919217</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.3495986591647053</v>
+        <v>-0.3513211041904327</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.4751018781929019</v>
+        <v>-0.4767036751205822</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.5141372189805082</v>
+        <v>-0.5156829800414329</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.3850097271149835</v>
+        <v>-0.3867221800447638</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.3790122690370694</v>
+        <v>-0.3807751791512715</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.4622785445376323</v>
+        <v>-0.4639508134762949</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.4110914993743435</v>
+        <v>-0.4128511796736305</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.4303876501749571</v>
+        <v>-0.4321029847345557</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.4563160725774509</v>
+        <v>-0.458006405110055</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.4831985945872006</v>
+        <v>-0.4848616717655574</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.4903138378145258</v>
+        <v>-0.4919613826116347</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.5266430509496516</v>
+        <v>-0.5282409559477443</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.5394308070679159</v>
+        <v>-0.5410348719066533</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.5673078024987817</v>
+        <v>-0.5688822708223356</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.6367007568186693</v>
+        <v>-0.6381823541575855</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.634440261030889</v>
+        <v>-0.63592854989448</v>
       </c>
     </row>
     <row r="35">
@@ -8206,79 +8206,79 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3351</v>
+        <v>3355</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.1767888627750978</v>
+        <v>-0.1772591915847244</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.2292791320761225</v>
+        <v>-0.229695573019562</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.2295430547066388</v>
+        <v>-0.2299936717132525</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.2743303001662625</v>
+        <v>-0.2747451284036586</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.3856272482771033</v>
+        <v>-0.3865131196670433</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.4192574013034331</v>
+        <v>-0.4200995946034212</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.255092168016489</v>
+        <v>-0.256148123786744</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.368259623207237</v>
+        <v>-0.36918863355708</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.3098023647728212</v>
+        <v>-0.3108004448881374</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.353462144571246</v>
+        <v>-0.3544275208152357</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.4781007449206953</v>
+        <v>-0.4789122425581098</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.4130459192903473</v>
+        <v>-0.4139420029990504</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.449578683074904</v>
+        <v>-0.4504588655628936</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.4451680787076597</v>
+        <v>-0.4460594647874814</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.4317689455484768</v>
+        <v>-0.4326926906887181</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.4143503425027433</v>
+        <v>-0.4152812694293573</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.4117183846249333</v>
+        <v>-0.4126563434382717</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.4990486982007454</v>
+        <v>-0.4998859321855917</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.5334383129029092</v>
+        <v>-0.5342300962379625</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.4778315946348712</v>
+        <v>-0.4786857648846023</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.5264293893199579</v>
+        <v>-0.5272393682721059</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.5548473823262157</v>
+        <v>-0.5556259837117921</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.6800008232181014</v>
+        <v>-0.6806243094403328</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.6786400498411069</v>
+        <v>-0.6792675877822134</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/nasdaq_hourly_24hrs/macd/macd_12_26.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/macd/macd_12_26.xlsx
@@ -618,1395 +618,1395 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.01146</t>
+          <t>X ≈ -0.01141</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-3.616124820723165</v>
+        <v>-5.883586627650253</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>18.12713813209859</v>
+        <v>17.52515444451127</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>16.70295095824769</v>
+        <v>16.28287696969767</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>10.4761678340063</v>
+        <v>10.96449684011542</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.9025437282039093</v>
+        <v>-3.511344113126846</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>4.808605295102751</v>
+        <v>6.116463269019512</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4.041695164787555</v>
+        <v>5.326905168102677</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-1.763058148617368</v>
+        <v>0.2856670025247681</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-18.31454426682365</v>
+        <v>-13.80911825132768</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-13.55705082714596</v>
+        <v>-5.121394188149239</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-18.82179304834604</v>
+        <v>-9.59496991534381</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-19.10548832965912</v>
+        <v>-9.873736083383029</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-14.69336938192725</v>
+        <v>-6.241568313468534</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-14.91812765040575</v>
+        <v>-6.490869094439745</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-4.497325366347212</v>
+        <v>-7.17280324252274</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-3.905488973925173</v>
+        <v>-6.614743866973285</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-9.583876552986872</v>
+        <v>-16.2240278313426</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-15.23708458292706</v>
+        <v>-21.11500439350743</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-15.02604839247864</v>
+        <v>-20.90710661061758</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-14.84391110335756</v>
+        <v>-20.69897601072699</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-15.39026990834244</v>
+        <v>-21.27192300412935</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-15.47063686378702</v>
+        <v>-21.35332308121438</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-9.64689453469942</v>
+        <v>-16.35553243589338</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-9.725467289720889</v>
+        <v>-16.52238744149443</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.01067</t>
+          <t>X ≈ -0.01062</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-3.615768463353689</v>
+        <v>-1.80606715489381</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-10.57255836658521</v>
+        <v>-8.902904037723509</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-8.692870069630473</v>
+        <v>-6.726225358001606</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-2.777935148333142</v>
+        <v>-0.4621065681250229</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-16.36917523455279</v>
+        <v>-14.45026937081342</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-9.55803465561717</v>
+        <v>-10.86938080330096</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-3.69662292152578</v>
+        <v>-4.802420362331887</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-3.97447988792441</v>
+        <v>-1.67539505296957</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-3.934156094474048</v>
+        <v>1.884616985643959</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-1.385550197652869</v>
+        <v>1.09251159390589</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-4.432863332486264</v>
+        <v>-2.070444978786959</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-1.391013310722457</v>
+        <v>1.088898897798131</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-5.833268762779973</v>
+        <v>-3.45901444185548</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-6.055409156733226</v>
+        <v>-3.707497846997953</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-6.713354059452691</v>
+        <v>-0.949616318697899</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-6.122223083050635</v>
+        <v>-0.3897406546351334</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-9.583590674113871</v>
+        <v>-0.4930572309585841</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-9.691200290798818</v>
+        <v>-0.6259220875068792</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-12.80686111067237</v>
+        <v>-3.855081738551789</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-9.294815482196974</v>
+        <v>-0.1977943497497776</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-13.16986529754127</v>
+        <v>-4.209842269855116</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-13.24962681421031</v>
+        <v>-4.286213766036994</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-12.97918044438871</v>
+        <v>-4.043888968513741</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-13.05880062305296</v>
+        <v>-4.207116505533051</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.009874</t>
+          <t>X ≈ -0.009832</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>6.314990542406903</v>
+        <v>3.575370917256571</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>9.295336126507024</v>
+        <v>3.33182898328046</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>11.18076436744285</v>
+        <v>5.634274776498664</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>10.47479552902442</v>
+        <v>5.046409678038685</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>3.517230327673083</v>
+        <v>1.224465464357863</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3.703384625110878</v>
+        <v>1.380084318946338</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.935954943807211</v>
+        <v>0.5889269767061478</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>9.294393304844789</v>
+        <v>3.839855700205604</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>9.33872653628741</v>
+        <v>3.968575110440476</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>8.571996925260606</v>
+        <v>3.177166215234877</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>8.848090633539705</v>
+        <v>3.44981286492515</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>8.572574764804017</v>
+        <v>3.174824621189188</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>10.77797279559952</v>
+        <v>5.624193822350712</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>13.88405901675065</v>
+        <v>8.939091483338323</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>16.55638943514871</v>
+        <v>11.82346969008764</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>20.4797602045783</v>
+        <v>15.94997496553532</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>17.02660057820474</v>
+        <v>12.2877364242654</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>13.59980446232586</v>
+        <v>8.593787859381067</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>10.49127279318642</v>
+        <v>5.244530777433766</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>10.68100107624366</v>
+        <v>5.460372847473963</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>10.14234117890411</v>
+        <v>4.895245665007096</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>6.738317368798484</v>
+        <v>1.252343881845185</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>3.682471154816916</v>
+        <v>-2.074023570428572</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>3.607866043613704</v>
+        <v>-2.236673155780956</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.009081</t>
+          <t>X ≈ -0.009038</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-7.248114679037329</v>
+        <v>-8.246493559416741</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-5.160598997503243</v>
+        <v>-6.128600721015303</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-11.43826267076147</v>
+        <v>-9.743615342692102</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-7.302940730780101</v>
+        <v>-7.969643443156471</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.787661453383365</v>
+        <v>-1.142840230182095</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-2.603462452773854</v>
+        <v>-0.9879718602687575</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-3.372732280985112</v>
+        <v>0.588828819541618</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-8.504804089490165</v>
+        <v>-4.453196346974586</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-8.465883693441285</v>
+        <v>-4.326993038457118</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-4.380920857070812</v>
+        <v>-0.3793010986765637</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.7497611413202918</v>
+        <v>4.635252631144013</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.4718226283311964</v>
+        <v>4.360660902089911</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.6474194143338394</v>
+        <v>3.250824725359969</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-10.59409404066834</v>
+        <v>-6.490360544489739</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-8.821198114018621</v>
+        <v>-4.798006228678773</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-13.09687756695885</v>
+        <v>-8.989649322159977</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-15.6677036897912</v>
+        <v>-11.47131921327454</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-18.21168140098793</v>
+        <v>-13.98403398430122</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-18.00164231699144</v>
+        <v>-16.15139041328193</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-20.25665822725122</v>
+        <v>-18.32011219153247</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-18.36801920741343</v>
+        <v>-18.89247980095081</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-18.4494604524517</v>
+        <v>-18.97335881792287</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-18.18071822969224</v>
+        <v>-18.73556679904664</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-15.82302826532938</v>
+        <v>-16.52238744149443</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.008285</t>
+          <t>X ≈ -0.008246</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>5.019025858410906</v>
+        <v>6.412012588654626</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-1.789480927874024</v>
+        <v>2.196449613574565</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.059212337624743</v>
+        <v>0.9500725683797953</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-3.929488342674809</v>
+        <v>-3.614488732630555</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-6.424097485885007</v>
+        <v>-3.888304797652538</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-8.402822359921785</v>
+        <v>-7.712034341062882</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-2.686659844314725</v>
+        <v>-4.527060897562365</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-7.290284722980523</v>
+        <v>-4.831685104449448</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-13.74227122774119</v>
+        <v>-14.65912238031786</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-8.022994716129624</v>
+        <v>-9.482437375806072</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-3.422102466455023</v>
+        <v>-5.230098864334913</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-3.70132184019679</v>
+        <v>-3.515147672172581</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.677566615018335</v>
+        <v>3.345385510714628</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-2.876181559529229</v>
+        <v>1.105547953730657</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-5.701049687438591</v>
+        <v>-1.568621378949189</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-7.278165157022961</v>
+        <v>-3.003967963393762</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-5.244276495316662</v>
+        <v>-1.112269428272008</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-7.520382233519797</v>
+        <v>-3.24148857315469</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-7.307156248323068</v>
+        <v>-1.031390416396434</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-9.294121803373926</v>
+        <v>-2.814995651547314</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-12.01086640012387</v>
+        <v>-3.382677024788158</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-12.09046855896597</v>
+        <v>-3.458889618455139</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-13.99312161775126</v>
+        <v>-5.215808826278881</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-18.42111946363316</v>
+        <v>-9.379530298637285</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.00749</t>
+          <t>X ≈ -0.007454</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-7.820794346179646</v>
+        <v>-7.335232176384572</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-13.20480783271904</v>
+        <v>-12.16514351898258</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-4.536039803186853</v>
+        <v>-5.774487308884538</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-5.246751551574718</v>
+        <v>-7.89418322859138</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-3.89578321983668</v>
+        <v>-9.698509073185107</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-8.767625153702596</v>
+        <v>-14.13525433361649</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-7.853457965896368</v>
+        <v>-11.87115108585812</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.387064206883515</v>
+        <v>-6.055401152015776</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-3.032421134884231</v>
+        <v>-5.929084337155821</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-5.490803592210277</v>
+        <v>-6.724028612088567</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-8.595469524632179</v>
+        <v>-9.519322613428301</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-5.499462487909447</v>
+        <v>-6.733210698210399</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-6.620711098865428</v>
+        <v>-7.846701018804367</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-5.1530914528485</v>
+        <v>-6.562538389233602</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-9.190876692356085</v>
+        <v>-8.778627443638044</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-3.528863772761646</v>
+        <v>-2.082988151734746</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-3.663048310052872</v>
+        <v>-2.186715653205383</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-2.077132795694602</v>
+        <v>-0.7844204802692403</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.1700474214974506</v>
+        <v>0.9654929438521904</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-1.676346353523719</v>
+        <v>-0.3564598887549764</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-5.605423360263941</v>
+        <v>-3.997358566839651</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-2.295440340574117</v>
+        <v>-0.9988379392555586</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-2.02185482307133</v>
+        <v>-0.7556311130659026</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>2.986397117060427</v>
+        <v>3.697392778285788</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.006696</t>
+          <t>X ≈ -0.006662</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-6.532256986358028</v>
+        <v>-3.515413192090435</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-4.919034118614817</v>
+        <v>-5.472072655591752</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.5079244428134686</v>
+        <v>-5.008952515723905</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-3.16539132703992</v>
+        <v>-7.312440505978962</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.3989608511740101</v>
+        <v>-2.446384592921554</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.534020311821259</v>
+        <v>1.136966204966306</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>7.615976259444686</v>
+        <v>5.489298527552464</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>3.440194950636389</v>
+        <v>1.756734885630095</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>9.337229339891238</v>
+        <v>7.03290104389275</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>2.714690743821663</v>
+        <v>1.093127481205194</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-4.821516650588912</v>
+        <v>-5.502876871769224</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.148325420614427</v>
+        <v>-4.063578612768943</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>1.592674003381028</v>
+        <v>-1.740123062053421</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.535577163220481</v>
+        <v>-5.424859339560861</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>2.673016128037133</v>
+        <v>-0.9490402334592076</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-2.600425385436111</v>
+        <v>-5.548620219969806</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>3.134695578788758</v>
+        <v>-0.4927544005816387</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>4.988017753273311</v>
+        <v>4.536858657558795</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>1.289879612475822</v>
+        <v>3.031051940712203</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>1.476834139084289</v>
+        <v>3.246314093467412</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>6.812058517062248</v>
+        <v>7.848045078578167</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>6.738297003255674</v>
+        <v>7.775342350330654</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>5.054634951663317</v>
+        <v>8.02137443671544</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>3.019630749496059</v>
+        <v>7.861849011707541</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.0059</t>
+          <t>X ≈ -0.00587</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.119405082975511</v>
+        <v>-2.577756257484211</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.9051822042043369</v>
+        <v>-0.9489042650951234</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-3.348874449736705</v>
+        <v>-2.196695471822295</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>3.036510871038679</v>
+        <v>4.710966497973047</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2.705125556621027</v>
+        <v>2.564864237230417</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>4.91987523795185</v>
+        <v>4.596582569270403</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2.122956994340569</v>
+        <v>1.929537211617536</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3.877100545189137</v>
+        <v>3.503491451505802</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>5.950638326629502</v>
+        <v>6.448422539307288</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>5.183462431736729</v>
+        <v>5.658252873729076</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>6.474787214685698</v>
+        <v>7.810519151973523</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>4.165749148153317</v>
+        <v>5.657366403763469</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>3.047552807993661</v>
+        <v>3.608006808217361</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>4.862962024357969</v>
+        <v>7.12341236871962</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>4.20859818826775</v>
+        <v>6.445797871014484</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>8.873720144839908</v>
+        <v>10.77137245131034</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>5.689383877620529</v>
+        <v>6.906972582778899</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>5.586583318132213</v>
+        <v>7.717999254771954</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>12.93492644260979</v>
+        <v>13.58561673131192</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>14.14482751592568</v>
+        <v>14.74658469357423</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>13.60762601313224</v>
+        <v>14.18478101052037</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>12.51652167336429</v>
+        <v>14.11433855796096</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>11.77498982299362</v>
+        <v>12.47646950155966</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>9.662287812321189</v>
+        <v>12.31858290891011</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.005105</t>
+          <t>X ≈ -0.005078</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-14.40018625016114</v>
+        <v>-14.58862090801837</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-8.898620430284367</v>
+        <v>-9.056217511021984</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-8.837190339735329</v>
+        <v>-9.342469975396384</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-7.058876069382194</v>
+        <v>-7.043225938121914</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-11.28930657261417</v>
+        <v>-10.21131302438365</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-14.03133406660817</v>
+        <v>-13.91928492133695</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-15.77949851225515</v>
+        <v>-15.68111900765068</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-17.03663781840447</v>
+        <v>-16.95568576338527</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-11.14929742334932</v>
+        <v>-12.00510065368372</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-4.116790072009962</v>
+        <v>-5.071850448226655</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.9167601842933522</v>
+        <v>-2.869078049451403</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.7573704314793304</v>
+        <v>-1.212550498827035</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.36166134049558</v>
+        <v>-0.3894880369344165</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.3955138033649774</v>
+        <v>-1.604211924379776</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>7.55856905283887</v>
+        <v>5.458247132821633</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>5.220740930141048</v>
+        <v>3.115138984263766</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>11.9357952086991</v>
+        <v>10.76159531784445</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>13.79200825410632</v>
+        <v>11.60141668423246</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>14.0119963607843</v>
+        <v>11.81930075905447</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>9.308299625815366</v>
+        <v>7.190156693871614</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>9.749163269365816</v>
+        <v>7.596001061694665</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>8.697065727889928</v>
+        <v>6.553413361153453</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>9.9546195373958</v>
+        <v>7.769974543640707</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>10.86276800439803</v>
+        <v>7.610760963498642</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.004309</t>
+          <t>X ≈ -0.004286</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.522258073737262</v>
+        <v>0.07194764683858068</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-3.993954249521387</v>
+        <v>-2.21893926621545</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.039224999707251</v>
+        <v>3.695871244189469</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.324923161313166</v>
+        <v>2.082892623072382</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.662574566238504</v>
+        <v>3.860211304120355</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.780301851306341</v>
+        <v>4.017109299133743</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.124984353598087</v>
+        <v>0.1529697850646841</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.805395274821343</v>
+        <v>2.924557125951338</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.77654464400905</v>
+        <v>2.026273786269449</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.07664293852519</v>
+        <v>3.285300444662091</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>2.420224108079545</v>
+        <v>4.583681952703202</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>6.425253808776958</v>
+        <v>7.388348843714638</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>2.095410996857176</v>
+        <v>4.226397076059961</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>4.019277446269875</v>
+        <v>5.008268595370602</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>2.292399932028694</v>
+        <v>3.301966347062766</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>6.10264433638352</v>
+        <v>6.946846390955585</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>5.971501566654553</v>
+        <v>6.846000244631618</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>8.014943667207888</v>
+        <v>8.773179966593034</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>2.866432787206783</v>
+        <v>3.844909364791249</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>3.054475822566516</v>
+        <v>4.06105945335549</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>1.439858277632872</v>
+        <v>2.466309287101772</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>2.439257775314012</v>
+        <v>3.422488134887203</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-1.584818103125457</v>
+        <v>0.5758750586153383</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-2.736219977891665</v>
+        <v>-0.6166437006993704</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.003514</t>
+          <t>X ≈ -0.003493</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2.689846899928447</v>
+        <v>0.5774603490900674</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>3.508581504185955</v>
+        <v>2.666939417669376</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2.065642150285406</v>
+        <v>1.419702817623786</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.350930879103842</v>
+        <v>1.997717397042031</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.1432913009197776</v>
+        <v>-0.6094874396884791</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>3.009338034410398</v>
+        <v>3.051755754712204</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.0683121667481501</v>
+        <v>-0.07594280992310587</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>4.278284830576062</v>
+        <v>4.298045969912941</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>3.163631158603224</v>
+        <v>2.085890220752873</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.075648310992193</v>
+        <v>-3.388279083819285</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>3.825526287553323</v>
+        <v>1.564629249188876</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-5.713298198155883</v>
+        <v>-6.91045544983055</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.201334640994887</v>
+        <v>-4.5081574731621</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.26352582529244</v>
+        <v>-2.412444271673742</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-3.079152309616191</v>
+        <v>-4.266092850754262</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-9.443969437209084</v>
+        <v>-10.74619422703403</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-6.101314931747147</v>
+        <v>-7.333115909417153</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-7.368466202464226</v>
+        <v>-8.642439148506618</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-7.155462096076512</v>
+        <v>-8.431263856519031</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-5.809973558727918</v>
+        <v>-7.044829720087861</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-6.353581870048423</v>
+        <v>-7.613670375126105</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-5.269610053500195</v>
+        <v>-6.515766275770652</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-3.834527891595314</v>
+        <v>-6.274258122919754</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-1.585932405998427</v>
+        <v>-4.085412651578459</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.002719</t>
+          <t>X ≈ -0.002701</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.4434427679111721</v>
+        <v>3.434663284824047</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.9027138031398252</v>
+        <v>1.207645266907633</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.333660655851048</v>
+        <v>-0.03962178279667938</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.02291311021159</v>
+        <v>4.331692813476934</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>3.718975006906852</v>
+        <v>6.048189509695092</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.890267586823015</v>
+        <v>6.205104439618516</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.930688948956927</v>
+        <v>0.4502220147527396</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-6.266099632820676</v>
+        <v>-3.830032242582107</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-2.169938496253984</v>
+        <v>-0.7222137654999941</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.939998051601222</v>
+        <v>-1.514860248124947</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-6.730626087367554</v>
+        <v>-4.230492926787321</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.94797400567424</v>
+        <v>-0.5262145582425859</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-3.051557430030215</v>
+        <v>-0.6410694202449179</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.809825699888421</v>
+        <v>4.092386914105262</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.8792505464473805</v>
+        <v>1.4209067835653</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>1.747942016162789</v>
+        <v>3.975210483469006</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>3.6503792681251</v>
+        <v>5.867763844803825</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.4929316683053884</v>
+        <v>2.744195267487271</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>1.727198270219141</v>
+        <v>3.957593079249492</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>3.952479728835996</v>
+        <v>6.17072688653262</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>3.412542568287101</v>
+        <v>5.606873632642362</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>0.279281207955087</v>
+        <v>2.536371738024975</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>0.5539958535522942</v>
+        <v>2.781215317115247</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-4.623426473393323</v>
+        <v>-3.379530298637277</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.001924</t>
+          <t>X ≈ -0.001909</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>4.747763335287225</v>
+        <v>3.015217017310803</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.9551885204520687</v>
+        <v>-1.140028390794939</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.9621157434247607</v>
+        <v>1.5262374313047</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-5.119038779003176</v>
+        <v>-4.285343727707087</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-4.112656668874557</v>
+        <v>-3.90490811015831</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-2.583683296473829</v>
+        <v>-2.445873765273554</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.3851334228586438</v>
+        <v>0.6853821718296516</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.450897232331414</v>
+        <v>2.342566534000987</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.833797057707869</v>
+        <v>4.430781795491058</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.394204313806362</v>
+        <v>2.986435767334733</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.339271016004773</v>
+        <v>3.258001230900639</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.389414416200353</v>
+        <v>2.328238236289891</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.616974079057357</v>
+        <v>2.528924338173269</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2.742823540717986</v>
+        <v>3.592600671588421</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>2.761682430010715</v>
+        <v>3.570152746269748</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>1.33492244340016</v>
+        <v>2.163899383455615</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-2.840795235813353</v>
+        <v>-1.875029317625334</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>0.4238838587746088</v>
+        <v>1.273263652783953</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.03471741581829946</v>
+        <v>1.487993505276592</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.5224637847176652</v>
+        <v>1.046418482809401</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-1.063960395099599</v>
+        <v>-0.1762475904358496</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-1.139929669212968</v>
+        <v>-0.9084449800379275</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-2.216569972678656</v>
+        <v>-1.980137329461797</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.9416835059358419</v>
+        <v>0.4888907539942977</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.001129</t>
+          <t>X ≈ -0.001117</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.9626061984746457</v>
+        <v>-0.2068882537996402</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-2.615919773233792</v>
+        <v>-0.4520249450727363</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-3.385341139762659</v>
+        <v>-1.705786931717306</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-4.756230791081428</v>
+        <v>-2.964040091706735</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-3.763710940812771</v>
+        <v>-1.908419351805399</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.594348984970772</v>
+        <v>-0.420434652204392</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.69858849057789</v>
+        <v>0.1173940322777511</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.6715785946150845</v>
+        <v>1.812700024691047</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.276817234514688</v>
+        <v>-0.7266114176789884</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.267780076176678</v>
+        <v>1.81310203984944</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.8773779385143428</v>
+        <v>2.08680022346487</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-3.379629310322223</v>
+        <v>-2.864404848322387</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.181641410206126</v>
+        <v>-0.6414925214396803</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-4.722018674952878</v>
+        <v>-4.232246344081425</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-6.043336380723858</v>
+        <v>-5.5868028071434</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-2.13132512344113</v>
+        <v>-2.349112767797799</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-3.594479411557899</v>
+        <v>-3.123754203315464</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-2.371004284877877</v>
+        <v>-1.917625125350561</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-1.491226013599658</v>
+        <v>-1.031822162093221</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-2.635981705777759</v>
+        <v>-3.496993075866179</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>0.1507420406743023</v>
+        <v>-0.717768591790005</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-1.256894063990707</v>
+        <v>-2.805775793954403</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>1.68272105105514</v>
+        <v>0.1228365101053868</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>1.607866043613704</v>
+        <v>-0.3191276140735226</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ -0.0003342</t>
+          <t>X ≈ -0.0003252</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-3.680101075141941</v>
+        <v>-2.072970371283247</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-4.022262282130157</v>
+        <v>-2.541032058804419</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-5.468831699058349</v>
+        <v>-4.775281637488391</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-4.626879658622393</v>
+        <v>-4.386716011910302</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-3.927879805652744</v>
+        <v>-4.171635022455753</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.695629660710175</v>
+        <v>-2.54457987745559</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-6.075541425049359</v>
+        <v>-6.288308884270279</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-7.094433522327861</v>
+        <v>-7.580018632479558</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-7.27417650075548</v>
+        <v>-7.948146487735684</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-7.225345173336237</v>
+        <v>-8.255148430348179</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-8.517875554379152</v>
+        <v>-8.971697775519949</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-7.757182245043339</v>
+        <v>-8.759665108062748</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-7.837587842378831</v>
+        <v>-8.893210860207262</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-7.019015388700531</v>
+        <v>-8.159242893147272</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-5.070310197452073</v>
+        <v>-6.379156486471423</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-3.437958621297341</v>
+        <v>-4.338102885993038</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-4.093969793631715</v>
+        <v>-4.444260786990206</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-3.156940214154424</v>
+        <v>-4.578205724347271</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-1.898424145585345</v>
+        <v>-3.869627902887352</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.6671351784548847</v>
+        <v>-2.666874238405221</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.3597092114445104</v>
+        <v>-1.753839489972378</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>3.945951103334679</v>
+        <v>1.634985772314259</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>3.699061619350999</v>
+        <v>1.178648299612682</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>5.195998678866765</v>
+        <v>2.006608315224099</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.0004609</t>
+          <t>X ≈ 0.0004669</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.482438061687752</v>
+        <v>2.0646955126279</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>6.039859414318101</v>
+        <v>4.154991179513267</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.7867353021886245</v>
+        <v>-1.50998255050132</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.970135098238558</v>
+        <v>-1.63429273817826</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-4.287001370727396</v>
+        <v>-2.376641428321257</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-4.587069314685891</v>
+        <v>-2.691916177089851</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.915338192789307</v>
+        <v>-1.14439288221827</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-5.641400597989943</v>
+        <v>-3.792691228527225</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-8.046262760845046</v>
+        <v>-6.479981731853826</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-8.821347437304965</v>
+        <v>-6.810052529562455</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-7.282379959432184</v>
+        <v>-7.011028810463138</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-8.742877642353633</v>
+        <v>-8.230350332783338</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-10.3556097340679</v>
+        <v>-10.28958141150628</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-11.07159598607005</v>
+        <v>-11.48333584680986</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-9.771572278275649</v>
+        <v>-11.23207863457</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-10.16741995926354</v>
+        <v>-11.61557030062323</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-4.906046259206086</v>
+        <v>-7.019058494483268</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-4.523293382882684</v>
+        <v>-6.683725576895156</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-3.819477461149212</v>
+        <v>-6.470599325698046</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-3.634675708033505</v>
+        <v>-5.786770632306833</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-4.177866066774918</v>
+        <v>-6.359828596845318</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-4.747765445392034</v>
+        <v>-5.215742770758169</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-7.921935316220825</v>
+        <v>-7.802296964725173</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-8.00132935868514</v>
+        <v>-7.02103973259954</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.001256</t>
+          <t>X ≈ 0.001259</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>4.732297347919591</v>
+        <v>2.814972297075833</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.237495186104695</v>
+        <v>1.420746125111791</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.9466084848181779</v>
+        <v>0.1763835480980731</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.975898295444793</v>
+        <v>0.9554332275679656</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.706619158829902</v>
+        <v>-2.767544178014312</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.4640837383959493</v>
+        <v>-0.70001389775787</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.509144716052809</v>
+        <v>-1.87110649289454</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-5.731921058026202</v>
+        <v>-5.251722684315254</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-4.505814851034323</v>
+        <v>-3.974075121157618</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-4.110772247474841</v>
+        <v>-4.383893539367378</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-4.616045656105349</v>
+        <v>-5.272810640683467</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-3.722671593587037</v>
+        <v>-4.394131963037353</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-4.627941265084331</v>
+        <v>-5.507449998657833</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-4.067596186570064</v>
+        <v>-4.986930280353263</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-6.708251295548727</v>
+        <v>-7.215522902521521</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-8.074096905762083</v>
+        <v>-8.594380911408173</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-6.237089527645146</v>
+        <v>-6.771350080233454</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-5.70440394318036</v>
+        <v>-5.748622961453961</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-6.430931406334373</v>
+        <v>-7.473926141078408</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-7.983206551377599</v>
+        <v>-8.813259674644087</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-8.295080407139643</v>
+        <v>-8.610669469221342</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-8.13635454086068</v>
+        <v>-8.685831991176585</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-9.446545641459913</v>
+        <v>-10.76777890124708</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-9.923095748217648</v>
+        <v>-10.92991789553651</v>
       </c>
     </row>
     <row r="23">
@@ -2016,981 +2016,981 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-2.793421238218095</v>
+        <v>-1.709511166214874</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.699497085719365</v>
+        <v>-1.953150234155586</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.718950667376966</v>
+        <v>-0.6557921639791147</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.9954072102209608</v>
+        <v>0.2073674461103181</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.0912660474802891</v>
+        <v>1.239300395874814</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-3.311841979056744</v>
+        <v>-1.887242134040811</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-3.740454258441517</v>
+        <v>-2.312704071017791</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.228696338615023</v>
+        <v>-1.523101597828564</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.543020002406067</v>
+        <v>-1.763846336563766</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-6.207642293440436</v>
+        <v>-5.114752071096703</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-6.289393496984474</v>
+        <v>-4.848416970961026</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-8.735753382818274</v>
+        <v>-7.322117302719988</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-8.431773803975929</v>
+        <v>-7.710759433862108</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-5.908934746289816</v>
+        <v>-5.404140936584255</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-5.268577489870502</v>
+        <v>-4.993049937170987</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-5.168720564097583</v>
+        <v>-5.169792667945607</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-7.244407748677133</v>
+        <v>-7.479278210228614</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-9.152476305530023</v>
+        <v>-9.453071336858926</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-11.1003015387934</v>
+        <v>-11.44948301383345</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-11.63443325113728</v>
+        <v>-11.61144910226927</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-11.81553237797274</v>
+        <v>-12.32703973825919</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-12.61261721077783</v>
+        <v>-13.13749637786149</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-11.26531004802621</v>
+        <v>-11.79092071611257</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-12.43304851715645</v>
+        <v>-13.05600088687257</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.002847</t>
+          <t>X ≈ 0.002843</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.80859700891348</v>
+        <v>-0.8578567584944423</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.206950963509122</v>
+        <v>1.213810489356327</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.105407008909232</v>
+        <v>0.9658600481251725</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.3919258528494964</v>
+        <v>0.3741790964464116</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.064010841650763</v>
+        <v>1.762582946278314</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.4295287859575794</v>
+        <v>-0.7308572967139426</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.147441603279091</v>
+        <v>1.459717363124099</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.1442680934038734</v>
+        <v>-0.8266859198072609</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.233358552483665</v>
+        <v>-0.3726493500608186</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.207459040310205</v>
+        <v>-0.5015293252779358</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.738000968769299</v>
+        <v>0.4297073952173562</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.809752048299288</v>
+        <v>3.143371638547201</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.6955197160258</v>
+        <v>4.025847410320097</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2.463929695145609</v>
+        <v>2.112516000818772</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>3.81559469317601</v>
+        <v>3.428242399826374</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>4.412090161586896</v>
+        <v>3.989442161319204</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>3.608002643131613</v>
+        <v>2.884763732767347</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>2.498082079299337</v>
+        <v>1.749830609843855</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>2.714500596840622</v>
+        <v>1.963061123757527</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>2.56573407945271</v>
+        <v>2.051146451101161</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>3.362474401208424</v>
+        <v>2.821494591860819</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>1.945760540226608</v>
+        <v>1.408539427765113</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>0.7555350220613306</v>
+        <v>-0.02006688963214032</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>2.019499153233397</v>
+        <v>1.15558675821886</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.003641</t>
+          <t>X ≈ 0.003635</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-4.679982504785855</v>
+        <v>-5.491489975622883</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-5.422388379426508</v>
+        <v>-5.734057044836653</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-2.803616860551742</v>
+        <v>-2.949641203622917</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.078671501000699</v>
+        <v>-1.532507730348726</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.4579617506893</v>
+        <v>3.027733506311328</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.206278550292758</v>
+        <v>1.006311983325723</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>3.275733280436533</v>
+        <v>3.040483761655118</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>5.836675227217349</v>
+        <v>5.575442033990846</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>4.254396171469701</v>
+        <v>4.087386796743189</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>4.694617626804558</v>
+        <v>4.519861371337335</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>4.564798230176038</v>
+        <v>4.38279651977259</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>6.31781914443124</v>
+        <v>6.132366844890711</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>5.597786108865485</v>
+        <v>5.432783781989308</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>4.97020316737823</v>
+        <v>4.780468921691259</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>2.684543594634974</v>
+        <v>2.476986502833093</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>2.470422431497106</v>
+        <v>2.218956612367549</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>1.523497164438332</v>
+        <v>1.29896342863406</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>3.045047724529702</v>
+        <v>2.793858993557762</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>2.042551921582223</v>
+        <v>1.783321319263081</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>2.228272720300104</v>
+        <v>1.997907764321994</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>3.309492789996483</v>
+        <v>3.063116324165868</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>3.232521817337279</v>
+        <v>2.987953802210484</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>4.725008709941136</v>
+        <v>4.45607808340732</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>2.876158726540581</v>
+        <v>2.253122762587203</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.004436</t>
+          <t>X ≈ 0.004427</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.085521045771983</v>
+        <v>0.5216352775888424</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>2.243281560855067</v>
+        <v>2.283211904559181</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.6872748016088224</v>
+        <v>-0.9667592591577545</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.9027163832405876</v>
+        <v>-1.061750623376803</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-4.223581482653557</v>
+        <v>-4.843597407298113</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.440996643742352</v>
+        <v>-0.1733470874508356</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-3.316026667013638</v>
+        <v>-3.673356163913212</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.599213236144863</v>
+        <v>-2.971824780072907</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.557726054230159</v>
+        <v>-3.357973332938101</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.833129292455695</v>
+        <v>-3.648825610612533</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-3.554094525915609</v>
+        <v>-4.402319859372881</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-3.335331491552722</v>
+        <v>-4.188787835285545</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-4.95600599621978</v>
+        <v>-5.818995996229191</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-5.17708487266637</v>
+        <v>-6.083202440135942</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-6.830253045868872</v>
+        <v>-7.797631550733719</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-6.733378561736764</v>
+        <v>-7.763061302125749</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-7.862320574336159</v>
+        <v>-8.905678775253364</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-8.46467371596826</v>
+        <v>-9.566740128983731</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-8.746294772854881</v>
+        <v>-9.033005211349163</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-8.559448962886883</v>
+        <v>-8.818418766290122</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-7.111945379609097</v>
+        <v>-7.855251022772961</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-5.197741589774431</v>
+        <v>-5.889597218197572</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-3.430729563859536</v>
+        <v>-4.115350488021299</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-1.51651206583908</v>
+        <v>-1.726469074147467</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.005232</t>
+          <t>X ≈ 0.005219</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.846957764616853</v>
+        <v>2.335964408026918</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3.951205356510933</v>
+        <v>3.346147503295306</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3.732698502601856</v>
+        <v>2.696446375546515</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.40998838559814</v>
+        <v>1.484743070037553</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3.293710108172817</v>
+        <v>3.076627005079075</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.870920196709221</v>
+        <v>1.988599227649843</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>5.757508098184729</v>
+        <v>6.195619844216012</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>7.308564946114586</v>
+        <v>7.526622358900056</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>5.520783835346357</v>
+        <v>7.421120906966401</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>5.357624256870807</v>
+        <v>7.257548155924113</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>6.241439996593748</v>
+        <v>7.53019120207928</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>7.182202788267702</v>
+        <v>8.518426880995506</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>6.668796818972559</v>
+        <v>8.661752365965263</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>8.886742332769828</v>
+        <v>10.31653515320799</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>10.66762342543317</v>
+        <v>12.16297810789072</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>11.87176644493721</v>
+        <v>12.7494236343219</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>11.12809321039876</v>
+        <v>11.79350302400083</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>11.63300860413855</v>
+        <v>12.09011217933946</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>8.800119497257931</v>
+        <v>9.756803705848327</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>10.20647750234799</v>
+        <v>9.97139015090724</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>7.834663041698953</v>
+        <v>8.767002974367301</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>6.539304885167944</v>
+        <v>7.417955102093536</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>4.984511304967029</v>
+        <v>6.387704237053448</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>3.079410759060863</v>
+        <v>3.677794542127046</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.006027</t>
+          <t>X ≈ 0.006011</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>6.359152886567976</v>
+        <v>2.970089404170793</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>7.135487199329269</v>
+        <v>3.956136572159991</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>7.919690372520527</v>
+        <v>8.444056202012533</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3.873403019744451</v>
+        <v>3.162213009415488</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1.315390324974985</v>
+        <v>0.4227468619298946</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.830976822260965</v>
+        <v>-2.922501838602045</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-5.936258839484616</v>
+        <v>-7.30915679023385</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-6.214470284237727</v>
+        <v>-7.688569427699861</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-2.839649768989688</v>
+        <v>-5.201021582309892</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.942990110529443</v>
+        <v>0.5364777367120652</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-2.22739469175314</v>
+        <v>-0.7720037767414354</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-4.728366317423358</v>
+        <v>-1.439752409752934</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>4.148471615720553</v>
+        <v>8.064208570559323</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.5940594059406976</v>
+        <v>5.032177792058789</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>4.38036055280454</v>
+        <v>9.868941245013623</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>4.974747474747417</v>
+        <v>11.2273923164869</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>7.063052559992187</v>
+        <v>12.31398809523819</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>4.735989633948762</v>
+        <v>8.609675418647925</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>7.174103237095458</v>
+        <v>11.20509002674596</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>5.138726824841171</v>
+        <v>9.03872409085271</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>3.485069545764098</v>
+        <v>7.280803398995744</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>4.52033469546604</v>
+        <v>8.396117067516663</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>3.683698296837051</v>
+        <v>8.639751552795012</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>4.718977154724818</v>
+        <v>9.668088748981823</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.006822</t>
+          <t>X ≈ 0.006803</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>9.594447004215091</v>
+        <v>9.005635820151923</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-1.034447441193542</v>
+        <v>-0.7469205222013926</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.4687099803637409</v>
+        <v>-2.035934658412948</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.2442440390789997</v>
+        <v>-1.04103526991959</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.831730194256032</v>
+        <v>0.2363881429625891</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>12.84222579211811</v>
+        <v>9.921421277060141</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>19.42321828469832</v>
+        <v>15.4540955925838</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>19.14500683994532</v>
+        <v>15.12772512772514</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>16.2453175512718</v>
+        <v>12.08534086709606</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>15.47240187523531</v>
+        <v>11.26354934613676</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>15.74646151739719</v>
+        <v>11.54007436503103</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>13.99712387865507</v>
+        <v>9.693350840418148</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>9.932785341210668</v>
+        <v>8.025048169556833</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>3.829353523587613</v>
+        <v>3.014909346218971</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>0.2300337554189014</v>
+        <v>0.7454533770322769</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-6.528520499108687</v>
+        <v>-5.042448953354317</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-3.721261165497928</v>
+        <v>-0.3844246031746508</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-2.355513634025037</v>
+        <v>1.06999287896538</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>2.272142452781644</v>
+        <v>6.046359868016012</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>2.458988262749671</v>
+        <v>4.673644725773265</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>1.916442094783683</v>
+        <v>4.106200224392531</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>4.781772603962771</v>
+        <v>2.443736115135707</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>3.585659081150709</v>
+        <v>1.100069013112538</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>6.451003298515666</v>
+        <v>2.52523160612462</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.007617</t>
+          <t>X ≈ 0.007595</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.4150406618190701</v>
+        <v>0.1610769755931116</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-5.58852713758823</v>
+        <v>-7.492237267518171</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.037969942413042</v>
+        <v>-1.339523962002339</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3.550822374583198</v>
+        <v>-0.08007430895871437</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.623677775383378</v>
+        <v>-4.059336152761702</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.436711589286105</v>
+        <v>-5.754254398615572</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>4.242952630049452</v>
+        <v>-0.9937808552926271</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>10.41635408852208</v>
+        <v>6.108706108706052</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>15.29655094785615</v>
+        <v>13.64404242579761</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>20.97524817504546</v>
+        <v>18.40354648613379</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>18.02350136559448</v>
+        <v>14.97207779703442</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>14.51894551053363</v>
+        <v>10.99179213885947</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>8.557073766258149</v>
+        <v>4.321344465853137</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>8.335994889811559</v>
+        <v>4.073110404420028</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>9.290754818037406</v>
+        <v>5.242807874386877</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>8.272238514173992</v>
+        <v>3.952260041354634</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>8.138321377196519</v>
+        <v>3.848379629629626</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>4.80767422176244</v>
+        <v>1.863643672616178</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>6.636468828493172</v>
+        <v>5.781809603465589</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>5.210411412654793</v>
+        <v>5.99639604852463</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>7.893671696301617</v>
+        <v>10.98450710269951</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>4.592019283279662</v>
+        <v>9.057492728892321</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>1.640687544148811</v>
+        <v>7.449275362318836</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.04804793488087</v>
+        <v>5.435284516177582</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.008412</t>
+          <t>X ≈ 0.008388</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>4.423669015600296</v>
+        <v>3.834422452217268</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>8.927601894669834</v>
+        <v>8.506548403398646</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>7.489582845638814</v>
+        <v>7.251854301507066</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-4.513693754449065</v>
+        <v>-4.81595773336673</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.602128676229434</v>
+        <v>1.465861175714217</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.1761916365204499</v>
+        <v>-0.01654948058268246</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.5957570473700216</v>
+        <v>-0.8116314928155006</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-2.486871717929482</v>
+        <v>-2.755896198519153</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>4.00622836721103</v>
+        <v>5.568754022640363</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>8.072022368593892</v>
+        <v>9.690735314306266</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>6.733178784949381</v>
+        <v>8.323626066615574</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>3.228622929888445</v>
+        <v>4.768355587554062</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>2.105460863032349</v>
+        <v>3.653463470103311</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>1.884381986585758</v>
+        <v>3.405229408670138</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>7.677851592231001</v>
+        <v>9.280452075965449</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>6.659335288367501</v>
+        <v>8.202411832490014</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>8.138321377196519</v>
+        <v>8.098531420765021</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>1.581867770149536</v>
+        <v>1.408270266423095</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>1.797759151073862</v>
+        <v>1.622732493568869</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>10.04912109007415</v>
+        <v>10.0340402501033</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>11.11947814791457</v>
+        <v>11.10594001101761</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>9.430728960699021</v>
+        <v>9.391433226767283</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>12.93101012479397</v>
+        <v>12.91375623663578</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>9.629371419957742</v>
+        <v>9.472928717756112</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.009208</t>
+          <t>X ≈ 0.00918</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>11.74376827118342</v>
+        <v>11.16325562483058</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>15.25514531898745</v>
+        <v>16.79970173030318</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>9.970972423802671</v>
+        <v>9.662654687235126</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>15.02724917359065</v>
+        <v>14.95260542960338</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>10.84530485488952</v>
+        <v>10.75547866205304</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>9.109194117909979</v>
+        <v>8.951627954325652</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>6.414168510942758</v>
+        <v>6.195761628367443</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>4.212880143112706</v>
+        <v>5.890841184958823</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-3.437940367280255</v>
+        <v>-3.785151473984513</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-11.90316373562447</v>
+        <v>-14.3851245378313</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-9.706027170385589</v>
+        <v>-10.19132089577599</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-4.215545804602819</v>
+        <v>-6.546334222796276</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-1.492554025305125</v>
+        <v>-3.739657712796152</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>2.132520944402138</v>
+        <v>-0.06632314677816709</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>3.3974545698985</v>
+        <v>1.212306785062182</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>2.068764568764571</v>
+        <v>-0.1871735098436176</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-3.834383337443668</v>
+        <v>-2.251838235294144</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-2.016147118187938</v>
+        <v>-0.4239380267302266</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-1.800255737263612</v>
+        <v>-0.2094757995844532</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-5.459563773449425</v>
+        <v>-3.916457981976507</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-9.848263787569302</v>
+        <v>-8.405471110808136</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-9.924109748978381</v>
+        <v>-8.480633632763535</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-11.57271195957327</v>
+        <v>-10.19778346121054</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-5.879313443565778</v>
+        <v>-4.477569514323534</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.01</t>
+          <t>X ≈ 0.009973</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>31</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-2.027943887625476</v>
+        <v>-1.929723502304149</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>7.314698668863379</v>
+        <v>4.275982565217795</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>9.102486071445291</v>
+        <v>9.472901366551973</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>11.61533850361545</v>
+        <v>12.10630561935669</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>8.053741579455277</v>
+        <v>8.604941027644543</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.789094862326856</v>
+        <v>2.310261730416698</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>7.468759081662263</v>
+        <v>7.96679262140978</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>7.19054763690923</v>
+        <v>4.436065726388257</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>4.00622836721103</v>
+        <v>1.338188184459511</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.007506239561642758</v>
+        <v>0.5421366892401736</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.2815658817236084</v>
+        <v>-2.411434747768347</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>6.45442938150137</v>
+        <v>6.989402652598926</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>8.557073766258206</v>
+        <v>9.100316986761193</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>5.110188438198705</v>
+        <v>5.626276473715173</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>1.2262386890052</v>
+        <v>1.71831564021722</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-4.630987292277617</v>
+        <v>-4.171993244189025</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>1.686708473970768</v>
+        <v>-1.050067204300987</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>1.581867770149536</v>
+        <v>-1.182951309462673</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>1.797759151073862</v>
+        <v>-0.9684890823168999</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>1.984604961041889</v>
+        <v>-0.7539026372579158</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>1.442058793075859</v>
+        <v>-1.321347138638693</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>1.366212831666715</v>
+        <v>-1.396509660593892</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>8.092300447374612</v>
+        <v>5.298737727910201</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>8.016468194151336</v>
+        <v>5.136598733620737</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.0108</t>
+          <t>X ≈ 0.01077</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>4.253889728673251</v>
+        <v>7.995834810350942</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-6.607202859150206</v>
+        <v>-2.506482281763191</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>2.481093881292473</v>
+        <v>6.495233872755527</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.8634390855186638</v>
+        <v>3.338729109844706</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>9.327086231407719</v>
+        <v>13.31958122615559</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.61931557539986</v>
+        <v>5.784207139846053</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>6.110524786246344</v>
+        <v>10.11733025581847</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>3.200734394124829</v>
+        <v>7.248307248307285</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>3.242221576039519</v>
+        <v>7.37623615799135</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>10.36404274210831</v>
+        <v>14.27249235507971</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>2.743365542164952</v>
+        <v>6.852419677376304</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-2.798541756019844</v>
+        <v>1.447632594699947</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-6.553282770244429</v>
+        <v>-2.231362086853416</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>1.120375195414248</v>
+        <v>5.212711544021126</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-2.169347049534693</v>
+        <v>1.96645459803355</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>1.056618819776716</v>
+        <v>5.091861180955775</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>3.554280630167625</v>
+        <v>7.552083333333293</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-1.813717968390357</v>
+        <v>2.290994099966603</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-4.229405534834449</v>
+        <v>-0.05864623699018523</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>3.852177117238831</v>
+        <v>7.848247900376478</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>0.6780520019043834</v>
+        <v>4.716700834893189</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>0.6022060404952825</v>
+        <v>4.641538312937904</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-4.386477141759499</v>
+        <v>-0.2430323299888428</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-4.462309394982775</v>
+        <v>-0.4051713242783066</v>
       </c>
     </row>
   </sheetData>
@@ -3180,2461 +3180,2461 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.01186</t>
+          <t>X &gt; -0.01181</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3355</v>
+        <v>3379</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.02924261372799464</v>
+        <v>-0.04468434127932142</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.0072010808152001</v>
+        <v>-0.01023306396148627</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.08188940631040253</v>
+        <v>-0.1020511951178094</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.1858562395147771</v>
+        <v>-0.2075627859617626</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1494058286178443</v>
+        <v>-0.172518198845502</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.2125692062251261</v>
+        <v>-0.2346783020597343</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.2858041142968233</v>
+        <v>-0.3066980127328094</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.3098590577635534</v>
+        <v>-0.3299564124306471</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.3701476258970402</v>
+        <v>-0.362155876216832</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.3247451224774522</v>
+        <v>-0.3163670613659164</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.2710737627481308</v>
+        <v>-0.2631161233009678</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.3842419732990194</v>
+        <v>-0.375443572227617</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.4207500123246319</v>
+        <v>-0.4115300015346079</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.4460594647874814</v>
+        <v>-0.4360313723523177</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.343513142531755</v>
+        <v>-0.363034095091507</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.29633984807937</v>
+        <v>-0.315692587979747</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.174702744390089</v>
+        <v>-0.1955047745619254</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.2618615346848543</v>
+        <v>-0.281440850607197</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.2961348581427288</v>
+        <v>-0.3155111215146533</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.3596027044499479</v>
+        <v>-0.3791636672656438</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.3187819531440468</v>
+        <v>-0.3379626171682517</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.4066834755199622</v>
+        <v>-0.4252375612913895</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.5018400424558251</v>
+        <v>-0.5191664522768207</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.5600425505244004</v>
+        <v>-0.5751503045561961</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.01107</t>
+          <t>X &gt; -0.01102</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3337</v>
+        <v>3358</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.009894732479587276</v>
+        <v>-0.008169466945261661</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.09053906510121834</v>
+        <v>-0.1198945105600302</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.1724279518788876</v>
+        <v>-0.2045179882866961</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.2433679066779106</v>
+        <v>-0.2774297461010136</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1453433526836037</v>
+        <v>-0.151638108255888</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.2396537555280602</v>
+        <v>-0.2743965787103164</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.3091469333029693</v>
+        <v>-0.341929003440832</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.302020405190774</v>
+        <v>-0.3338063504038686</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.2733543566322254</v>
+        <v>-0.2780623056756326</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.2533691852032405</v>
+        <v>-0.2863177553318295</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.1710099488012418</v>
+        <v>-0.2047572997057046</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.2832583249878127</v>
+        <v>-0.3160438870774556</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.3437625539329972</v>
+        <v>-0.3750705600365052</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.3679961662135653</v>
+        <v>-0.3981660977353343</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.3211072030565774</v>
+        <v>-0.3204476888687395</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.2768718575893416</v>
+        <v>-0.2763000695584097</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.1239490349041006</v>
+        <v>-0.09526684001981067</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.1810841853086629</v>
+        <v>-0.1511535264854231</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.2166807246042097</v>
+        <v>-0.1867369984440259</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.2814733813512476</v>
+        <v>-0.2520892005554884</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.2374853444555285</v>
+        <v>-0.2070474390484804</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.3254275087867313</v>
+        <v>-0.2943591229595341</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.4525110101332572</v>
+        <v>-0.4201302147378243</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.5106036397346045</v>
+        <v>-0.475420709596186</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.01027</t>
+          <t>X &gt; -0.01023</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3307</v>
+        <v>3329</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.02281655023169549</v>
+        <v>0.007492603631639838</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.004550314712659542</v>
+        <v>-0.04338286253127421</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.09513334542815954</v>
+        <v>-0.1477052776463452</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.220375158794738</v>
+        <v>-0.2758209663357079</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.001833834028239778</v>
+        <v>-0.02707808824562363</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.155120514825704</v>
+        <v>-0.1821002307039663</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.2784168820037038</v>
+        <v>-0.3030722147932465</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.2687050787674252</v>
+        <v>-0.3221193355722605</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.240144785378746</v>
+        <v>-0.2969021072521727</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.2430984170225656</v>
+        <v>-0.2983291855294539</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.1323478376701459</v>
+        <v>-0.1885046885031372</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.2732091415671789</v>
+        <v>-0.32828279989252</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.2939635862083563</v>
+        <v>-0.3482053234571296</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.3164018542342575</v>
+        <v>-0.369337434254227</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.2631188735458707</v>
+        <v>-0.3149667966293137</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.2238447826683085</v>
+        <v>-0.2753118517851334</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.03813432393454974</v>
+        <v>-0.09180155875299789</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.09481158683127688</v>
+        <v>-0.1470176633824991</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.1024668112138087</v>
+        <v>-0.1547808562201922</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.1997073508023064</v>
+        <v>-0.2525621806316067</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.1201671108321349</v>
+        <v>-0.1721777934812323</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.2081834872679167</v>
+        <v>-0.2595847809201075</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.338873246895389</v>
+        <v>-0.3885624755189951</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.3967705857583326</v>
+        <v>-0.4429126957535416</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.009478</t>
+          <t>X &gt; -0.009434</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3277</v>
+        <v>3301</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.03478650737136491</v>
+        <v>-0.02277113244273465</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.08050417852927438</v>
+        <v>-0.07201234804558254</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.1983609717284764</v>
+        <v>-0.196749640420073</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.3182863948748604</v>
+        <v>-0.3209656067605806</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.03034861785133103</v>
+        <v>-0.03769402870999983</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.1904440284656559</v>
+        <v>-0.1953511144938034</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.3078435389382008</v>
+        <v>-0.3106383999983322</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.3562525159075989</v>
+        <v>-0.3574223652607742</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.3278366192664492</v>
+        <v>-0.3330830712313784</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.3237980997410546</v>
+        <v>-0.3278093040454877</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.2145611895579407</v>
+        <v>-0.2193659097984977</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.3541897693337717</v>
+        <v>-0.3579971312437209</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.3953240047174305</v>
+        <v>-0.3988648739214185</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.446403021805061</v>
+        <v>-0.4482941169844921</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.4170966731372232</v>
+        <v>-0.4179283905790498</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.4133803791338053</v>
+        <v>-0.4129392467820949</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.1943571030203586</v>
+        <v>-0.1968082426440958</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.220181889386879</v>
+        <v>-0.2211596066231536</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.1994494746657551</v>
+        <v>-0.2005793190321654</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.2993171319470633</v>
+        <v>-0.3010208842932016</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.2141174461058881</v>
+        <v>-0.2151610884941562</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.2717767206160957</v>
+        <v>-0.2724093803013403</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.3756875075152664</v>
+        <v>-0.3742659257893735</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.4334318914895334</v>
+        <v>-0.4276975206912041</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.008683</t>
+          <t>X &gt; -0.008642</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3236</v>
+        <v>3259</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.05660609307309983</v>
+        <v>0.08321117560664248</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.01613956555711127</v>
+        <v>0.00604126093408297</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.05595183400896531</v>
+        <v>-0.07371547058409789</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.2297910834496122</v>
+        <v>-0.2223941219098222</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.004586433525929579</v>
+        <v>-0.02345157996442282</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1598711745111885</v>
+        <v>-0.1851363027961739</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.2690115122311738</v>
+        <v>-0.3222301837420147</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.2530106696415757</v>
+        <v>-0.3046385336461768</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.224727864618373</v>
+        <v>-0.2816120007731229</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.2723945048552281</v>
+        <v>-0.3271457092696366</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.2267791177303735</v>
+        <v>-0.2819292662635462</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.3646553157813273</v>
+        <v>-0.4188083117898955</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.3921299652259975</v>
+        <v>-0.4458998426755798</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.3178321529010546</v>
+        <v>-0.370427657961713</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.310617019529019</v>
+        <v>-0.3614806246385243</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.2526809401038719</v>
+        <v>-0.3024078496768894</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.001689624438725446</v>
+        <v>-0.0515092365788945</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.007769742249600142</v>
+        <v>-0.04379209393137984</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.02610364849103064</v>
+        <v>0.00498498472926201</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.04645836034401896</v>
+        <v>-0.06880184934259148</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.01589181601204359</v>
+        <v>0.02554077892627049</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.04146614181347985</v>
+        <v>-0.03140297453879981</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.1500984285260074</v>
+        <v>-0.1376367031208261</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.2384462761225947</v>
+        <v>-0.2202789945562813</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.007888</t>
+          <t>X &gt; -0.00785</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3190</v>
+        <v>3209</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.01495231106657258</v>
+        <v>-0.01539900533832395</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.009432128068780798</v>
+        <v>-0.02808788136321283</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.04148475464647561</v>
+        <v>-0.0896672941890202</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.1764412170156433</v>
+        <v>-0.1695412922008614</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.09728845869612002</v>
+        <v>0.03676738572096383</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.04100730161812294</v>
+        <v>-0.06785836514789878</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.2341488717058269</v>
+        <v>-0.2567139681948021</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.1515327365840164</v>
+        <v>-0.2341018154971692</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.02980404182726204</v>
+        <v>-0.057593453257617</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.1606303638776083</v>
+        <v>-0.1844954807477208</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.1807023547080107</v>
+        <v>-0.2048309552932821</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.3165403753038518</v>
+        <v>-0.3705636972622841</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.4219751196746628</v>
+        <v>-0.5049725343768969</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.2809405940593948</v>
+        <v>-0.3934250965982358</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.2328866424996079</v>
+        <v>-0.3426719497505459</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.1513730172266747</v>
+        <v>-0.2603143608374197</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.07733678478630424</v>
+        <v>-0.03498134328359015</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.1163261657246437</v>
+        <v>0.00603178390008452</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.1318497159686061</v>
+        <v>0.02113293426378249</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.08689352629528457</v>
+        <v>-0.02601291506080372</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>0.1893184235174488</v>
+        <v>0.07864482697416975</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>0.1322812284652031</v>
+        <v>0.02200130473693207</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>0.04951883376375577</v>
+        <v>-0.05851279967492218</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>0.02374901122082207</v>
+        <v>-0.07756707021721354</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.007093</t>
+          <t>X &gt; -0.007058</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3131</v>
+        <v>3144</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.1321395701444388</v>
+        <v>0.1359334234523928</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.2584388855540851</v>
+        <v>0.222837251093928</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.0432098310654041</v>
+        <v>0.02786238168732069</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.08089720240721476</v>
+        <v>-0.009839725449793946</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.1725331821178528</v>
+        <v>0.2380374142924921</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.1234355132247344</v>
+        <v>0.2229752029025107</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.09057198363261421</v>
+        <v>-0.01659360793776443</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.1282506041190956</v>
+        <v>-0.1137505251429332</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.0267767338004532</v>
+        <v>0.0637955122173679</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.0601895397090999</v>
+        <v>-0.0492952092664396</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.02213599794482946</v>
+        <v>-0.01226035803539816</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.2188743246351521</v>
+        <v>-0.2390204227515795</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.3051672554867793</v>
+        <v>-0.3531874353031697</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.1891306609170869</v>
+        <v>-0.265882996082567</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.0640838916399602</v>
+        <v>-0.1682644729367055</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.08772818983077002</v>
+        <v>-0.2226318556184808</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.1478199277423897</v>
+        <v>0.009504257907543945</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.1576593112767739</v>
+        <v>0.02237383134633575</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.1375386112450272</v>
+        <v>0.001608951877251741</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.1201197009708892</v>
+        <v>-0.01918115510848395</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>0.2985134938601846</v>
+        <v>0.1629133449760545</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>0.1780287763966371</v>
+        <v>0.043106441778761</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>0.08855142582804376</v>
+        <v>-0.04410036635099601</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.03207859601154439</v>
+        <v>-0.1556117235736707</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.006298</t>
+          <t>X &gt; -0.006266</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3080</v>
+        <v>3086</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.2424915910475676</v>
+        <v>0.2045588621113339</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.3441697697140285</v>
+        <v>0.3298705545896468</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.05233575573027593</v>
+        <v>0.1225270816386583</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.02982278670712901</v>
+        <v>0.1274094143009279</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.1687838927925682</v>
+        <v>0.2884899341947715</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.08351998571550467</v>
+        <v>0.2057971477762308</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.2181804123329201</v>
+        <v>-0.120074406336478</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.1873385012919897</v>
+        <v>-0.1489054680544086</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.1273898515601388</v>
+        <v>-0.06718573238313752</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.1061372327156036</v>
+        <v>-0.07076653656628906</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.05733426610869685</v>
+        <v>0.09093334183386048</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.1703671798640656</v>
+        <v>-0.1671395494460128</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.3365925490589419</v>
+        <v>-0.3271205959151189</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.150277163638691</v>
+        <v>-0.1689223259847878</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.1094060023553993</v>
+        <v>-0.1535901391355807</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.04612184016328769</v>
+        <v>-0.1225322687317885</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.09836192183220049</v>
+        <v>0.01894398642095041</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.07767610330865438</v>
+        <v>-0.06247390680024267</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.1184576401207593</v>
+        <v>-0.0553280842058399</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>0.09765462423590066</v>
+        <v>-0.08055468862028192</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.1906593392552125</v>
+        <v>0.01847470578327659</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>0.06940095835449256</v>
+        <v>-0.1022174994707612</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>0.00632082199116013</v>
+        <v>-0.1956873846847174</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.08261014686248558</v>
+        <v>-0.306296338818747</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.005503</t>
+          <t>X &gt; -0.005474</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2982</v>
+        <v>2980</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.287248758738464</v>
+        <v>0.3035271180432488</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.3852282852887967</v>
+        <v>0.3753571756925211</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.1641126169428091</v>
+        <v>0.2050229174329061</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.1305943153654354</v>
+        <v>-0.03562986451426298</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.08542994139914839</v>
+        <v>0.2075182307982004</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.07542126670540483</v>
+        <v>0.04961484754858247</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.2951192003456669</v>
+        <v>-0.1929800544918905</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.3209116154956035</v>
+        <v>-0.2788229423743473</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.3271372564771724</v>
+        <v>-0.2989489796311844</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.2799738414065303</v>
+        <v>-0.274550448476127</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.153567943468957</v>
+        <v>-0.1836559520838534</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.3128686554327089</v>
+        <v>-0.3743199625467497</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.4478085936569158</v>
+        <v>-0.4670949263976922</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.3150315031503084</v>
+        <v>-0.428314097004467</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.2513122433617951</v>
+        <v>-0.3883334710402337</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.3392621870882735</v>
+        <v>-0.5100335775654941</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.08538058375707891</v>
+        <v>-0.2260664267380932</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.1033677957700547</v>
+        <v>-0.3392289924132186</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.302740865125358</v>
+        <v>-0.5405428997913688</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.3639895553031991</v>
+        <v>-0.607963002215115</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.2502738378205578</v>
+        <v>-0.4854274647879109</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.3396593468336278</v>
+        <v>-0.6079070773525572</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.3804429479948368</v>
+        <v>-0.6464419584907262</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.4028650093708634</v>
+        <v>-0.7553692248117869</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.004707</t>
+          <t>X &gt; -0.004682</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2880</v>
+        <v>2877</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.807428748636994</v>
+        <v>0.8366836167169964</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.7140312606320194</v>
+        <v>0.7130186955853191</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.4829087633251632</v>
+        <v>0.5468344460951968</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.1147823300893194</v>
+        <v>0.2152503564039137</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.4882851929371199</v>
+        <v>0.5805247025687095</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.4188506449578142</v>
+        <v>0.5497179675330131</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.2532859002844603</v>
+        <v>0.3615136237060099</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.2711036875240893</v>
+        <v>0.3182284551105781</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.05614758276621501</v>
+        <v>0.1201450844728882</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.1440865999059966</v>
+        <v>-0.1028014391002827</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.1265382182730903</v>
+        <v>-0.08751466740228864</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.3507729564275124</v>
+        <v>-0.3443103187383159</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.4508596422063817</v>
+        <v>-0.469873344755257</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.3401966494227295</v>
+        <v>-0.3862155651241608</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.5279122059355643</v>
+        <v>-0.5976479660690117</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.5361789641568038</v>
+        <v>-0.639819039459276</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.5111305597399038</v>
+        <v>-0.6194377022653796</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.5954956975365064</v>
+        <v>-0.7667182189319846</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.8097211418763308</v>
+        <v>-0.9830399094754654</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.7065497971344854</v>
+        <v>-0.8871449030482523</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.6044205687000712</v>
+        <v>-0.7747521565597992</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.6597100265634168</v>
+        <v>-0.8642908122034854</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.7464764110190814</v>
+        <v>-0.9477596156751389</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.8018561786085172</v>
+        <v>-1.054886572533711</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.003912</t>
+          <t>X &gt; -0.003889</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2787</v>
+        <v>2780</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.8851685672522791</v>
+        <v>0.8633668501983536</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.8711330376123811</v>
+        <v>0.8153208259071576</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.4309757134566468</v>
+        <v>0.4369579822768088</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.07440088146936574</v>
+        <v>0.1500844212000132</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.4157308650874469</v>
+        <v>0.4660895945289454</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.3734200880183067</v>
+        <v>0.4287334498476625</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.2992776956239283</v>
+        <v>0.3687901533276658</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.2199055828887708</v>
+        <v>0.2272882101208182</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.03210849891419087</v>
+        <v>0.05363627725193254</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.1848213853649412</v>
+        <v>-0.2210193825265208</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.2115216758801211</v>
+        <v>-0.2505024631397816</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.5768836450403612</v>
+        <v>-0.6141189298023164</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.535826692594938</v>
+        <v>-0.6337360177117617</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.4856688743597246</v>
+        <v>-0.5744403721630036</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.6220238058030461</v>
+        <v>-0.7337136453401527</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.7577112809670936</v>
+        <v>-0.9045336246212372</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.7274508998025766</v>
+        <v>-0.8799224076067489</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.8828192931307868</v>
+        <v>-1.099585170009654</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.9323915098005244</v>
+        <v>-1.15149713235455</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.8320522666831707</v>
+        <v>-1.059798076635005</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.672636547425931</v>
+        <v>-0.8878395522558975</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.7631201469705147</v>
+        <v>-1.013865473307007</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.7185016075149946</v>
+        <v>-1.000922408267279</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.7373079786324297</v>
+        <v>-1.070177780651669</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.003117</t>
+          <t>X &gt; -0.003097</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2701</v>
+        <v>2695</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.8277075022355547</v>
+        <v>0.8723843094169936</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.7871565222013004</v>
+        <v>0.7569209816400715</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.378927837274766</v>
+        <v>0.405962319566413</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.03375609072647023</v>
+        <v>0.09181028281538062</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.4335301639680864</v>
+        <v>0.5000131744578766</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.2894923044604596</v>
+        <v>0.3460036183398714</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.3109817786168918</v>
+        <v>0.3828169814821436</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.09068654723489544</v>
+        <v>0.09889696352254873</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.06759936807331002</v>
+        <v>-0.0104607859011665</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.1564574032827721</v>
+        <v>-0.1211243641184012</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.3400615221797381</v>
+        <v>-0.3077515152911587</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.4133399014017343</v>
+        <v>-0.4155331768515254</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.4827968208576507</v>
+        <v>-0.511537196296814</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.4609018629638655</v>
+        <v>-0.5164699337739904</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.5437886886879255</v>
+        <v>-0.6223027984161504</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.4811403067216986</v>
+        <v>-0.5941287447677723</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.556346750692164</v>
+        <v>-0.6763894029114255</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.6763159113452701</v>
+        <v>-0.8616843951776545</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.7342485736954742</v>
+        <v>-0.921894100238049</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.673554957865754</v>
+        <v>-0.8710308448377901</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.4917549118296591</v>
+        <v>-0.6757075968035977</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.6196332413942329</v>
+        <v>-0.8403361344537927</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.619287146044833</v>
+        <v>-0.8346019868403971</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.7102877265948635</v>
+        <v>-0.9750776084703077</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.002322</t>
+          <t>X &gt; -0.002305</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2603</v>
+        <v>2595</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.842174633992677</v>
+        <v>0.7736452352201866</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.8507782248073141</v>
+        <v>0.7395520303773537</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.4810537198434659</v>
+        <v>0.423133190563064</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.04113341673014048</v>
+        <v>-0.07157632722937279</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.3098368890514607</v>
+        <v>0.2862106181867006</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.1915760625582266</v>
+        <v>0.1202193863060188</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.3953781410072992</v>
+        <v>0.380219485016994</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.3300123427191295</v>
+        <v>0.2503007864938169</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.0115513175055213</v>
+        <v>0.01696707458433622</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.05166025248169603</v>
+        <v>-0.06741585221063673</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.0994640087765859</v>
+        <v>-0.1565861429791653</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.3179137998962744</v>
+        <v>-0.4112679983778804</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.3860858951185477</v>
+        <v>-0.5065455884375325</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.5463921822721787</v>
+        <v>-0.6940752072953345</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.5311589299247998</v>
+        <v>-0.7010391984925022</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.5650627299420847</v>
+        <v>-0.7702111813086816</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.7147252177855492</v>
+        <v>-0.9285725723802258</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.7203367576017925</v>
+        <v>-1.000639295473022</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.8269192577921558</v>
+        <v>-1.109928288272243</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.847719921099241</v>
+        <v>-1.142389524274023</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.6387472871855735</v>
+        <v>-0.9178109197109521</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.653476351665546</v>
+        <v>-0.9704597518903526</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.6634599212889754</v>
+        <v>-0.9739398405573709</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.5629624875682637</v>
+        <v>-0.8824204720476843</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.001527</t>
+          <t>X &gt; -0.001513</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2455</v>
+        <v>2443</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.6067257021020183</v>
+        <v>0.6341778136574447</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.9596511691243705</v>
+        <v>0.8564968621490223</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.4520528320674799</v>
+        <v>0.354499607021225</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.2649887802622928</v>
+        <v>0.1905983125056281</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.576447498653522</v>
+        <v>0.5469760896187239</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.3588829404143397</v>
+        <v>0.2798780678615174</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.3959957451971192</v>
+        <v>0.361232694842812</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.2624396487628573</v>
+        <v>0.1201229749419994</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.1585881405596297</v>
+        <v>-0.2576542261024528</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.1388243892681089</v>
+        <v>-0.2574221748348293</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.2464834725923311</v>
+        <v>-0.3690369333310812</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.4208403074247116</v>
+        <v>-0.5817161963596575</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.5068406308326061</v>
+        <v>-0.6954082281611775</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.744682987568531</v>
+        <v>-0.9607861092971106</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.7296683072243724</v>
+        <v>-0.966786712042996</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.6796035876425606</v>
+        <v>-0.9527673850926277</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.5865548052934528</v>
+        <v>-0.8696853741496611</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.7893162489352861</v>
+        <v>-1.142118316404293</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.8746772507095102</v>
+        <v>-1.271567302852439</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.867328030339344</v>
+        <v>-1.278574058484701</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.6131132586840309</v>
+        <v>-0.9639499397886553</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.6241504490190977</v>
+        <v>-0.9743182231640262</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.5698304762357651</v>
+        <v>-0.911335657866637</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.5401312408397914</v>
+        <v>-0.9677415143556587</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.0007318</t>
+          <t>X &gt; -0.0007212</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2305</v>
+        <v>2294</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.7088514223130815</v>
+        <v>0.6888067779343032</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.192334744548972</v>
+        <v>0.9414880344576702</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.7017747825119542</v>
+        <v>0.4883194388747683</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.591749272974468</v>
+        <v>0.3954985401549891</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.8588873103324488</v>
+        <v>0.7064590542099225</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.4859913086606582</v>
+        <v>0.325364813846619</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.5323027453560059</v>
+        <v>0.3770705155586853</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.2358145546727073</v>
+        <v>0.0101866277699898</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.08581835136516247</v>
+        <v>-0.2271944956992655</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.2303604716180914</v>
+        <v>-0.3919069647162345</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.3196197900179243</v>
+        <v>-0.5285485882406675</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.2282943853272528</v>
+        <v>-0.4334508915896365</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.4629273480100409</v>
+        <v>-0.698910163776489</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.4858542009708486</v>
+        <v>-0.7482980644048496</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.3838764586235399</v>
+        <v>-0.6667072010709134</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.5851314703454733</v>
+        <v>-0.8620718916213619</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.3908113385083496</v>
+        <v>-0.7232789855072426</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.6863864418240553</v>
+        <v>-1.091747560287025</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.8345547715626438</v>
+        <v>-1.287139240940114</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.7522312618726517</v>
+        <v>-1.134483198157831</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.6628218464947793</v>
+        <v>-0.9799399227231831</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.5829740749428609</v>
+        <v>-0.8553613016087738</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.7164173435214991</v>
+        <v>-0.9785072590121615</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.679914144383396</v>
+        <v>-1.009870316074078</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 6.337e-05</t>
+          <t>X &gt; 7.086e-05</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2114</v>
+        <v>2092</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.10539348807179</v>
+        <v>0.9554793324954574</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.663473832579115</v>
+        <v>1.277754314973407</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.259289370014294</v>
+        <v>0.9965639022712125</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.063252643804638</v>
+        <v>0.8572611307463873</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.291371945693456</v>
+        <v>1.177479610369794</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.7734509137457195</v>
+        <v>0.6024818442687305</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.129321778727544</v>
+        <v>1.020668335236238</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.8981028151774808</v>
+        <v>0.7430840764174107</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.5636501474681239</v>
+        <v>0.5183276373749948</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.4016367270707306</v>
+        <v>0.3673544005120917</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.4210930060998592</v>
+        <v>0.2867076908369697</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.451940988942269</v>
+        <v>0.3705143434617852</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.2033735765048306</v>
+        <v>0.09231772373738778</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.1044172213831587</v>
+        <v>-0.03270970140007989</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.03954305136522152</v>
+        <v>-0.115122709841998</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.3273784023077155</v>
+        <v>-0.5264321875759208</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.05623079691488897</v>
+        <v>-0.36398724368145</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.4631717916277012</v>
+        <v>-0.7551010262812028</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.738434123294752</v>
+        <v>-1.037778481038899</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.7599196970348032</v>
+        <v>-0.9865180977132937</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.7552075759490791</v>
+        <v>-0.9052134826733038</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.9921626790351112</v>
+        <v>-1.095825024807837</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-1.11535607668548</v>
+        <v>-1.186798570122207</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-1.210803145916408</v>
+        <v>-1.301136417184132</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.0008585</t>
+          <t>X &gt; 0.0008629</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1911</v>
+        <v>1880</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.065341134097928</v>
+        <v>0.8303975079273371</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.198583056496943</v>
+        <v>0.9532999451423265</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.47663265021167</v>
+        <v>1.279217012903011</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.491707751933774</v>
+        <v>1.138223588305976</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.883946400551352</v>
+        <v>1.578263472179643</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.342883465483879</v>
+        <v>0.9739777913580951</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.558974303174388</v>
+        <v>1.264813536353444</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.592775338920539</v>
+        <v>1.254565121443079</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.478256280585633</v>
+        <v>1.307498693905053</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.381367645630782</v>
+        <v>1.176721564967302</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.23941064712708</v>
+        <v>1.109643934600598</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.428679964427914</v>
+        <v>1.340399083548995</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.325023818287285</v>
+        <v>1.263042519839331</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.291612763566832</v>
+        <v>1.258531119252517</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>1.081749441693376</v>
+        <v>1.138491468903922</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.7179007374421715</v>
+        <v>0.7240450890017556</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.4589510653797859</v>
+        <v>0.386478237791934</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-0.03187682405848591</v>
+        <v>-0.08655400248856893</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.4111438053541718</v>
+        <v>-0.4251412368539391</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.4545426848774241</v>
+        <v>-0.4452130246633814</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-0.3916284688650151</v>
+        <v>-0.2901185868198581</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.5932158650264938</v>
+        <v>-0.6312385555836428</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.3923128607641289</v>
+        <v>-0.4407955596669737</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.4894651965746775</v>
+        <v>-0.6561260433181388</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.001654</t>
+          <t>X &gt; 0.001655</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1658</v>
+        <v>1622</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.5057875019526463</v>
+        <v>0.5147253158186302</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.192645318987445</v>
+        <v>0.8789466070214118</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.557510885341074</v>
+        <v>1.454636885849787</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.265229942821414</v>
+        <v>1.167298750494879</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2.431843316427987</v>
+        <v>2.269520176094581</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.476982579448439</v>
+        <v>1.240247739441898</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.027149280173468</v>
+        <v>1.763622024359591</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.710476296958852</v>
+        <v>2.289474032593297</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.391386555796643</v>
+        <v>2.147601063995175</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.219432418221693</v>
+        <v>2.061209047654323</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>2.132915137306689</v>
+        <v>2.124855574812244</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>2.21474265693562</v>
+        <v>2.252550137814893</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.233407513156415</v>
+        <v>2.339976594914717</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.109393140155873</v>
+        <v>2.251952229670692</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>2.27045281112779</v>
+        <v>2.467305098884054</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>2.059502307846678</v>
+        <v>2.206260815330829</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>1.480723242723144</v>
+        <v>1.525023062730625</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>0.833713864203169</v>
+        <v>0.8140710230435317</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.5074365704287018</v>
+        <v>0.696058828059698</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.6942823803967286</v>
+        <v>0.8858326200314508</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>0.8143868148403399</v>
+        <v>1.033372244043015</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>0.5578179618649699</v>
+        <v>0.649948316415724</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>0.9893040834554228</v>
+        <v>1.201844207366108</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>0.9500453761428602</v>
+        <v>0.9780529319422513</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.002449</t>
+          <t>X &gt; 0.002447</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1381</v>
+        <v>1350</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.167540449836288</v>
+        <v>0.9628677773839058</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.772749190170494</v>
+        <v>1.449561674280773</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2.21470121850755</v>
+        <v>1.879849257370871</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.718666938761118</v>
+        <v>1.360707131822721</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.901314644088025</v>
+        <v>2.477090383664788</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2.437521611096471</v>
+        <v>1.870379032469529</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>3.184011105080309</v>
+        <v>2.584926245057851</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3.701172039213709</v>
+        <v>3.05763741887089</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>3.381126321634554</v>
+        <v>2.93568528099668</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>3.909729083775943</v>
+        <v>3.507032324913794</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.822255826444021</v>
+        <v>3.529840858108791</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>4.411185381781266</v>
+        <v>4.181668318426368</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.372622013406712</v>
+        <v>4.365013779971974</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.717703657567498</v>
+        <v>3.794513223167982</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>3.782626158974651</v>
+        <v>3.970428483926263</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>3.50933412213238</v>
+        <v>3.692398998628008</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>3.230803825357377</v>
+        <v>3.339223022912044</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>2.836736801941107</v>
+        <v>2.882710076297961</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>2.835708443169118</v>
+        <v>3.143160591759646</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>3.167167412934688</v>
+        <v>3.403803455932042</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>3.34768704395637</v>
+        <v>3.725247843440194</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>3.199534502648497</v>
+        <v>3.427863099262694</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>3.447325889697574</v>
+        <v>3.819645732689217</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>3.634416852206513</v>
+        <v>3.805654886547906</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.003244</t>
+          <t>X &gt; 0.003239</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1083</v>
+        <v>1051</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.986459159630762</v>
+        <v>1.480847450293155</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.928435128808623</v>
+        <v>1.516630755434356</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.519936374980588</v>
+        <v>2.139870925843248</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>2.083735123065523</v>
+        <v>1.641365440650056</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.131708488156626</v>
+        <v>2.680361291161041</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>3.226423751744775</v>
+        <v>2.610407255519817</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>3.469235215455903</v>
+        <v>2.905038001193148</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>4.759289453359649</v>
+        <v>4.162692298285513</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>4.24727110021901</v>
+        <v>3.876876579461175</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>5.042621106839341</v>
+        <v>4.647431880962628</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>4.670924291436691</v>
+        <v>4.411800806162582</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>4.576676733007147</v>
+        <v>4.477054338677434</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.283772968734048</v>
+        <v>4.461503546409574</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>4.062694092287458</v>
+        <v>4.273026229335848</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>3.773554484743805</v>
+        <v>4.124675524026991</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>3.260930336576102</v>
+        <v>3.607892903818623</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>3.127013199598629</v>
+        <v>3.468512583095922</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>2.929921573268217</v>
+        <v>3.205004044394798</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>2.869060186664861</v>
+        <v>3.478888223474812</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>3.33265876416057</v>
+        <v>3.788622147125608</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>3.34361813124989</v>
+        <v>3.982357474479429</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>3.544524937368458</v>
+        <v>4.002342431115956</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>4.188003339887416</v>
+        <v>4.912009266537062</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>4.078780171037536</v>
+        <v>4.55957531506396</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.004039</t>
+          <t>X &gt; 0.004031</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>837</v>
+        <v>806</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.945771763509484</v>
+        <v>3.600230414746541</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>4.088892217250482</v>
+        <v>3.720623945343036</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>4.084564924491879</v>
+        <v>3.686931064452686</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3.013187965981047</v>
+        <v>2.606128377243977</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>3.035820432501865</v>
+        <v>2.574770481344885</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>3.820158183712749</v>
+        <v>3.098004453643334</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>3.526106751913211</v>
+        <v>2.863866523137091</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>4.442638437387124</v>
+        <v>3.733258445620741</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>4.245176993256429</v>
+        <v>3.812887741701751</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>5.144901699537741</v>
+        <v>4.686209517263123</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>4.702115463563473</v>
+        <v>4.420617245573922</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>4.064943121047371</v>
+        <v>3.973888626491011</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>3.89757555837285</v>
+        <v>4.166263276289186</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3.795970994948959</v>
+        <v>4.118778760815886</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>4.093622201549998</v>
+        <v>4.625523923769542</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>3.493265993265993</v>
+        <v>4.030088178515278</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>3.598297482333919</v>
+        <v>4.127990924092408</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>2.896085213399239</v>
+        <v>3.329979897316719</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>3.111976594323565</v>
+        <v>3.994290074010635</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>3.657245343359691</v>
+        <v>4.332945997977816</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>3.35364780143906</v>
+        <v>4.261779412229828</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>3.636224779098065</v>
+        <v>4.31068636918274</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>4.030173804602811</v>
+        <v>5.050598770093863</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>4.432238803470334</v>
+        <v>5.260668212528977</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.004834</t>
+          <t>X &gt; 0.004823</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>636</v>
+        <v>610</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4.849718924303879</v>
+        <v>4.589418360456236</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>4.672174830356589</v>
+        <v>4.182480928939157</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>5.592646347363328</v>
+        <v>5.182215168432442</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>4.250761510310525</v>
+        <v>3.78465999055819</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>5.330065377385893</v>
+        <v>4.958377212777705</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>4.88810074587321</v>
+        <v>4.149127243896551</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>5.688479106008018</v>
+        <v>4.964351189795877</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>6.668129296475065</v>
+        <v>5.887678629614108</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>6.395151069584742</v>
+        <v>6.116967693553256</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>7.666260550780947</v>
+        <v>7.364351951793665</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>7.311389375332816</v>
+        <v>7.255528184212565</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>6.40370915427475</v>
+        <v>6.596650243717576</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>6.695641427041274</v>
+        <v>7.374641665491801</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>6.631795254997201</v>
+        <v>7.396792392597128</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>7.5459790014418</v>
+        <v>8.617226338527963</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>6.725271583762151</v>
+        <v>7.81936243786879</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>7.220285264394747</v>
+        <v>8.315858565193672</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>6.486513742963496</v>
+        <v>7.473844036914898</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>6.859637828290339</v>
+        <v>8.180109542749193</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>7.518181751465917</v>
+        <v>8.55863041403768</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>6.661170174694853</v>
+        <v>8.155120338886462</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>6.428091508883234</v>
+        <v>7.588154538242655</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>6.388100812560253</v>
+        <v>7.995723449750535</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>6.312268559336978</v>
+        <v>7.505715603002066</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.005629</t>
+          <t>X &gt; 0.005615</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>472</v>
+        <v>453</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>5.893051191652773</v>
+        <v>5.370416750150277</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>4.922681172963976</v>
+        <v>4.472336001402923</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>6.238899412068584</v>
+        <v>6.043728856033084</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>4.89035217228686</v>
+        <v>4.581761439833549</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>6.037612547197213</v>
+        <v>5.610551125821175</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>5.58898551295561</v>
+        <v>4.897919514427961</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>5.664494456183903</v>
+        <v>4.537620110890892</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>6.445605045329131</v>
+        <v>5.319656189221398</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>6.698956634023496</v>
+        <v>5.664976403253327</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>8.468413839342944</v>
+        <v>7.401367836896355</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>7.683151447606555</v>
+        <v>7.160335924157224</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>6.133215603480593</v>
+        <v>5.930604036095865</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>6.704968790861763</v>
+        <v>6.928556941486669</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>5.848296694076197</v>
+        <v>6.384872716182336</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>6.461339837173604</v>
+        <v>7.388345482479501</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>4.937082691319972</v>
+        <v>6.110709881923682</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>5.862487588240811</v>
+        <v>7.110582229580579</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>4.698324850521317</v>
+        <v>5.873945365037073</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>6.185402672123622</v>
+        <v>7.633661455317494</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>6.584112888871303</v>
+        <v>8.06899845225287</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>6.253431127684941</v>
+        <v>7.943055054624892</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>6.389449573055494</v>
+        <v>7.647141980793229</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>6.875788692317215</v>
+        <v>8.553028121700741</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>7.435549659432915</v>
+        <v>8.832390231164048</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.006424</t>
+          <t>X &gt; 0.006407</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>382</v>
+        <v>369</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>5.783236656201538</v>
+        <v>5.916832731348862</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>4.401339439003557</v>
+        <v>4.589844814563911</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.842901541805034</v>
+        <v>5.497312874834499</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5.129947522362293</v>
+        <v>4.904910676026276</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>7.150177992223391</v>
+        <v>6.791514698089102</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>7.33714417832077</v>
+        <v>6.678178033816906</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>8.397656227414707</v>
+        <v>7.234447372935549</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>9.428345306221843</v>
+        <v>8.280878280878269</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>8.94627227871247</v>
+        <v>8.138536920292118</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>10.00581733566027</v>
+        <v>8.964107046694394</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>10.01809687311015</v>
+        <v>8.966071791028455</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>8.692227050813983</v>
+        <v>7.608408755476077</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>7.30728487924582</v>
+        <v>6.670034619421337</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>7.08620600279923</v>
+        <v>6.692803268015332</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>6.951622914642762</v>
+        <v>6.823657016211577</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>4.92820878946533</v>
+        <v>4.945936644787338</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>5.579631966623992</v>
+        <v>5.926067073170721</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>4.689450948666675</v>
+        <v>5.251177547954924</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>5.952462748439167</v>
+        <v>6.820653325236208</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>6.92464887254333</v>
+        <v>7.848247900376478</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>6.905662914001375</v>
+        <v>8.093811529077058</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>6.829816952592275</v>
+        <v>7.476643587067564</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>7.627851874498418</v>
+        <v>8.533286202427256</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>8.075579830699219</v>
+        <v>8.642149918164883</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.00722</t>
+          <t>X &gt; 0.007199</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>4.957879001217712</v>
+        <v>5.280902683654112</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>5.578516215606754</v>
+        <v>5.68859061919207</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>7.006739204792318</v>
+        <v>7.048275602267807</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>6.293785185349577</v>
+        <v>6.129076017838671</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>7.868822738280016</v>
+        <v>8.14109957708574</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>6.144960898899683</v>
+        <v>6.01045148373742</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>6.009954890168572</v>
+        <v>5.542166857125615</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>7.324100133313578</v>
+        <v>6.871233341821565</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>7.365587315228282</v>
+        <v>7.325959637126594</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>8.821971002249114</v>
+        <v>8.49069245563274</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>8.777559306831428</v>
+        <v>8.436130084616167</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>7.543395890644575</v>
+        <v>7.179155973282121</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>6.738705161368081</v>
+        <v>6.39106124145227</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>7.791511635239956</v>
+        <v>7.450016722502816</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>8.407253687977864</v>
+        <v>8.07505188310143</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>7.409283922022766</v>
+        <v>7.002368973816502</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>7.593838122624916</v>
+        <v>7.225285947712415</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>6.215112068485269</v>
+        <v>6.112009685688065</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>6.749474786989204</v>
+        <v>6.980066684075666</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>7.891734609696087</v>
+        <v>8.50184267161832</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>7.98613111688929</v>
+        <v>8.914790327100334</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>7.273342480320956</v>
+        <v>8.512830419524128</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>8.503231205541866</v>
+        <v>10.06365444728616</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>8.42739895231859</v>
+        <v>9.901515452996698</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.008015</t>
+          <t>X &gt; 0.007992</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>252</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>6.27978780720295</v>
+        <v>6.378008192524319</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>8.325963389805523</v>
+        <v>8.513053737772836</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>8.475245928076113</v>
+        <v>8.845661223182837</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>6.968641114982582</v>
+        <v>7.459608230723823</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>10.20427921386387</v>
+        <v>10.75547866205305</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>8.010293019008884</v>
+        <v>8.531459887098769</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>6.444693541467728</v>
+        <v>6.942727081215246</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>6.563307493540051</v>
+        <v>7.034632034632025</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>5.414318484978565</v>
+        <v>5.972084753839944</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>5.831878999418265</v>
+        <v>6.366509449096796</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>6.502764038405594</v>
+        <v>7.035569860526536</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>5.827189238132192</v>
+        <v>6.362162509229833</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>6.29132875857767</v>
+        <v>6.834571979080657</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>7.657551469432661</v>
+        <v>8.173639504949129</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>8.189884362328293</v>
+        <v>8.681961313540263</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>7.196969696969688</v>
+        <v>7.65596374505833</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>7.459877956817621</v>
+        <v>7.948908730158728</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>6.561386459345641</v>
+        <v>7.022373831346329</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>6.777277840269967</v>
+        <v>7.236836058492102</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>8.55142523753959</v>
+        <v>9.038724090852682</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>8.00887906957356</v>
+        <v>8.471279589471948</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>7.933033108164459</v>
+        <v>8.396117067516663</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>10.19163480477349</v>
+        <v>10.62387853692201</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>10.5126279483756</v>
+        <v>10.85856493945794</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.00881</t>
+          <t>X &gt; 0.008784</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>6.885468676041718</v>
+        <v>7.190357565083119</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>8.129639246112959</v>
+        <v>8.515131357651505</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>8.796883354976707</v>
+        <v>9.354678093456251</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>10.71550828290238</v>
+        <v>11.38007694176845</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>13.01129675772353</v>
+        <v>13.72231984878954</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>10.56668399645248</v>
+        <v>11.2614524076672</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>8.742103733614776</v>
+        <v>9.419249976586315</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>9.516523867809056</v>
+        <v>10.16144995202586</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>5.873800523407972</v>
+        <v>6.100897186317297</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>5.100884847371482</v>
+        <v>5.30484569109796</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>6.427576068480782</v>
+        <v>6.624201124550467</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>6.675142454506471</v>
+        <v>6.871179379503246</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>7.657243545545079</v>
+        <v>7.850528099748807</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>9.541427826993228</v>
+        <v>9.696534876012045</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>8.356968739938985</v>
+        <v>8.490820284702899</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>7.372408293460921</v>
+        <v>7.481443675250304</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>7.238491156483448</v>
+        <v>7.901123472949386</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>8.186282031609636</v>
+        <v>8.815359786635952</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>8.402173412533962</v>
+        <v>9.029822013781725</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>8.062703433028304</v>
+        <v>8.720848249416619</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>6.993841475588589</v>
+        <v>7.629843538611809</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>7.444311303653173</v>
+        <v>8.0782412260806</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>9.297733384556281</v>
+        <v>9.892556339631234</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>10.80084849975406</v>
+        <v>11.30109797361403</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.009605</t>
+          <t>X &gt; 0.009576</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>5.05480506048108</v>
+        <v>5.743087557603687</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>5.44466594329068</v>
+        <v>5.497180721899817</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>8.354472981216205</v>
+        <v>9.242486620008243</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>9.090794324092315</v>
+        <v>10.07865584977144</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>13.82746761966098</v>
+        <v>14.80309770967212</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>11.11588308112069</v>
+        <v>12.10288845852734</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>9.619296716070899</v>
+        <v>10.5935207320089</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>11.51499831479609</v>
+        <v>11.71717171717171</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>9.382572453232527</v>
+        <v>9.702243483998679</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>11.50820750183372</v>
+        <v>12.47762056020791</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>12.50690482515507</v>
+        <v>12.74985557481224</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>10.77888005938823</v>
+        <v>11.75898790605522</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>11.10499335485095</v>
+        <v>12.0726672171759</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>12.33318984072321</v>
+        <v>13.2530045843142</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>10.22577118082381</v>
+        <v>11.14227877385773</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>9.370882740447954</v>
+        <v>10.27501136410595</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>11.41087864694875</v>
+        <v>11.59970238095239</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>12.03067562428699</v>
+        <v>12.18110399007649</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>12.24656700521131</v>
+        <v>12.39556621722227</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>13.15805049633876</v>
+        <v>13.32443837656696</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>13.34014200953215</v>
+        <v>13.47127958947193</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>13.98893372928246</v>
+        <v>14.11040278180239</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>17.1619591664022</v>
+        <v>17.2111801242236</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>17.08612691317892</v>
+        <v>17.04904112993413</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.0104</t>
+          <t>X &gt; 0.01037</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>7.106816437969897</v>
+        <v>7.925263180146281</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>4.902880761115412</v>
+        <v>5.844493959121309</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>8.1377589083461</v>
+        <v>9.176955820532491</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>8.359384328155699</v>
+        <v>9.501984814384812</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>15.50022936962712</v>
+        <v>16.56587621556987</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>13.81803667721982</v>
+        <v>14.88794743624687</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>10.24234967557246</v>
+        <v>11.3405718460325</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>12.7678765485764</v>
+        <v>13.78794498060553</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>10.94020485198642</v>
+        <v>12.08101150496854</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>14.84018637221162</v>
+        <v>15.87211597305195</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>16.04882545362587</v>
+        <v>17.06178218031683</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>12.03175829316854</v>
+        <v>13.11547545520334</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>11.84317566556475</v>
+        <v>12.91801453041311</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>14.42583510687517</v>
+        <v>15.42207404696165</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>12.83311237004228</v>
+        <v>13.82248847241605</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>13.42749929198527</v>
+        <v>14.38379249123571</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>14.22816159426013</v>
+        <v>15.19734327217125</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>15.05790032969129</v>
+        <v>15.9818903596702</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>15.27379171061562</v>
+        <v>16.19635258681598</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>16.39521695983598</v>
+        <v>17.3283702245355</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>16.78725023112228</v>
+        <v>17.67835691581533</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>17.64598370896552</v>
+        <v>18.52062558652059</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>19.78961729995224</v>
+        <v>20.59912245712007</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>19.71378504672897</v>
+        <v>20.4369834628306</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.0112</t>
+          <t>X &gt; 0.01116</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>8.677993466278174</v>
+        <v>7.885944700460833</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>11.24176739256605</v>
+        <v>10.49718072189982</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>11.25302370585388</v>
+        <v>10.67105804857966</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>13.43862041104883</v>
+        <v>12.9357987069143</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>18.89993138777693</v>
+        <v>18.37452628110069</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>20.53617293619314</v>
+        <v>19.96003131567019</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>12.51784744070859</v>
+        <v>12.02209216058033</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>18.03673744523088</v>
+        <v>17.43145743145743</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>15.1796739025079</v>
+        <v>14.70224348399868</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>17.3053089511091</v>
+        <v>16.7633348459222</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>23.37647004254638</v>
+        <v>22.74985557481224</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>20.1991699144607</v>
+        <v>19.6161307631981</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>21.97455857224227</v>
+        <v>21.35838150289018</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>21.75347969579568</v>
+        <v>21.11014744145707</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>21.09533639821512</v>
+        <v>20.42799305957201</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>20.24044795783927</v>
+        <v>19.56072564982024</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>20.10653082086179</v>
+        <v>19.45684523809523</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>24.34951620399713</v>
+        <v>23.60967541864792</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>26.0146829472403</v>
+        <v>25.25270907436513</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>23.30297803257064</v>
+        <v>22.61015266228125</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>25.65898258924229</v>
+        <v>24.89985101804338</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>27.03241199015203</v>
+        <v>26.25325992465951</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>33.10398815190945</v>
+        <v>32.21118012422361</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>33.02815589868617</v>
+        <v>32.04904112993415</v>
       </c>
     </row>
   </sheetData>
@@ -5824,2461 +5824,2461 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.01186</t>
+          <t>X &lt; -0.01181</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1.431616654683978</v>
+        <v>2.171658986175117</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.3524355059846727</v>
+        <v>0.4971807218998165</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4.006646894259688</v>
+        <v>4.956772334293952</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>9.090794324092315</v>
+        <v>10.07865584977144</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>7.30572848922619</v>
+        <v>8.374526281100685</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>10.39124539996125</v>
+        <v>11.38860274424162</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>13.96712280302743</v>
+        <v>14.87923501772319</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>15.1381867205932</v>
+        <v>16.00288600288599</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>18.07822462714559</v>
+        <v>17.55938634114154</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>15.85603358879024</v>
+        <v>15.33476341735076</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>13.23154250631449</v>
+        <v>12.74985557481224</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>18.74989455214185</v>
+        <v>18.18755933462666</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>20.52528320992342</v>
+        <v>19.92981007431874</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>21.75347969579568</v>
+        <v>21.11014744145707</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>16.74751031125859</v>
+        <v>17.57085020242916</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>14.44334650856389</v>
+        <v>15.27501136410596</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>8.512327922311073</v>
+        <v>9.456845238095234</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>12.75531330544641</v>
+        <v>13.60967541864791</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>14.42048004868956</v>
+        <v>15.25270907436513</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>17.50587658329528</v>
+        <v>18.32443837656697</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>15.51405505301042</v>
+        <v>16.32842244661479</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>19.78603517855783</v>
+        <v>20.5389742103738</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>24.4083359779964</v>
+        <v>25.06832298136647</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>27.23105444941081</v>
+        <v>27.76332684421985</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.01107</t>
+          <t>X &lt; -0.01102</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.3821413923151624</v>
+        <v>0.3035271180432488</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3.495640456034309</v>
+        <v>4.45322467794378</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>6.655322556428608</v>
+        <v>7.594134971656587</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>9.390644399054835</v>
+        <v>10.29843606955166</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>5.606578064438594</v>
+        <v>5.627273533847934</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>9.241820112604941</v>
+        <v>10.1798115354504</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>11.91814729078356</v>
+        <v>12.68143281992099</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>11.63993584603048</v>
+        <v>12.37651237651237</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>10.53199774058885</v>
+        <v>10.30663908839427</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>9.759082064552359</v>
+        <v>10.60948869207604</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>6.584865844645329</v>
+        <v>7.585020409977076</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>10.90381759062262</v>
+        <v>11.70404285111017</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>13.22893138583546</v>
+        <v>13.8858540303627</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>14.15727779674519</v>
+        <v>14.7365210678307</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>12.34970921180831</v>
+        <v>11.85656448814344</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>10.64524555903867</v>
+        <v>10.2200663091609</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>4.764201985279584</v>
+        <v>3.522779304029299</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>6.958211856171033</v>
+        <v>5.587697396669896</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>8.323528524451682</v>
+        <v>6.901060722716764</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>10.80922490913237</v>
+        <v>9.313449365577952</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>9.117253453810015</v>
+        <v>7.647103765296109</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>12.48968335446987</v>
+        <v>10.86864454004414</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>17.36185921637721</v>
+        <v>15.50788342092691</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>19.58487753786658</v>
+        <v>17.54354662443965</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.01027</t>
+          <t>X &lt; -0.01023</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.6493941219789718</v>
+        <v>-0.2092933947772622</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.1294700656279346</v>
+        <v>1.211466436185539</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2.706015158845354</v>
+        <v>4.123439000960616</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>6.266565412906878</v>
+        <v>7.697703468819057</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.05213104254637813</v>
+        <v>0.7554786620530578</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4.408339417055274</v>
+        <v>5.079078934717806</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>7.909895006669196</v>
+        <v>8.450663589151759</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>7.63168356191612</v>
+        <v>8.979076479076468</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>6.818469889129972</v>
+        <v>8.273672055427248</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>6.900255067794333</v>
+        <v>8.310953893541239</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>3.755511291152843</v>
+        <v>5.249855574812244</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>7.750266161209112</v>
+        <v>9.139940287007605</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>8.336505803754712</v>
+        <v>9.691714836223504</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>8.970127782008973</v>
+        <v>10.27681410812374</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>7.457283629727563</v>
+        <v>8.761326392905339</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>6.342268842268837</v>
+        <v>7.65596374505833</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>1.080146577086239</v>
+        <v>2.552083333333336</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>2.684707582666768</v>
+        <v>4.085865894838392</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>2.900598963591094</v>
+        <v>4.300328121984165</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>5.651547337661682</v>
+        <v>7.014914567043149</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>3.399599460293942</v>
+        <v>4.780803398995758</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>5.887856062987403</v>
+        <v>7.205640877040459</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>9.581134194272877</v>
+        <v>10.78260869565218</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>11.21470365045132</v>
+        <v>12.28713636802939</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.009478</t>
+          <t>X &lt; -0.009434</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.7809215940510299</v>
+        <v>0.5114273259434583</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1.806689013388279</v>
+        <v>1.616871841590935</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4.450302617418522</v>
+        <v>4.416231793753411</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>7.13870914219347</v>
+        <v>7.202207973323567</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.6804696900543519</v>
+        <v>0.8455687521431514</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>4.268796420369426</v>
+        <v>4.380880736519607</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>6.898208280696764</v>
+        <v>6.964177102665268</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>7.980541053630759</v>
+        <v>8.01060801060801</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>7.341756126701924</v>
+        <v>7.462861244616441</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>7.249112559508973</v>
+        <v>7.34248542507278</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>4.802083766296747</v>
+        <v>4.912017736974406</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>7.924694907066424</v>
+        <v>8.013814160881481</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>8.842349166740924</v>
+        <v>8.92594907045774</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>9.981814507981412</v>
+        <v>10.02906636037599</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>9.323671210400853</v>
+        <v>9.34691197849093</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>9.237786023500306</v>
+        <v>9.232540321634914</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>4.34196412461808</v>
+        <v>4.398930180180173</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>4.91739552964043</v>
+        <v>4.941721750694256</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>4.453014801721224</v>
+        <v>4.480508302164345</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>6.680676938219847</v>
+        <v>6.722121774250354</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>4.777586552566753</v>
+        <v>4.80332592151828</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>6.062284808844716</v>
+        <v>6.079514750914335</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>8.377575847857386</v>
+        <v>8.350176263219744</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>9.662287812321189</v>
+        <v>9.539388620281635</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.008683</t>
+          <t>X &lt; -0.008642</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.9812726453468628</v>
+        <v>-1.437363570215865</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.2796952371543853</v>
+        <v>-0.1043230374986805</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.9693357625914771</v>
+        <v>1.272561807978157</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3.979785998467889</v>
+        <v>3.838054346012044</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.07940872939853705</v>
+        <v>0.4046014690705988</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2.767131924783961</v>
+        <v>3.193114022437101</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4.654757708978707</v>
+        <v>5.555926747046499</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>4.376546264225631</v>
+        <v>5.25100630363788</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>3.886118552523314</v>
+        <v>4.852619423848303</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>4.708947557337886</v>
+        <v>5.635515297050013</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>3.919177412265768</v>
+        <v>4.855118732706984</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>6.300002476902876</v>
+        <v>7.210115725604112</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>6.772585090897827</v>
+        <v>7.674170976574381</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>5.487676427217195</v>
+        <v>6.373305336193916</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>5.361448023253665</v>
+        <v>6.217466743782545</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>4.360090264345587</v>
+        <v>5.199823394181152</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.02914602156806012</v>
+        <v>0.8854166666666643</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.1339867253892422</v>
+        <v>0.7525325615050633</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.45001023808193</v>
+        <v>-0.08563679029654025</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.8006653591201314</v>
+        <v>1.181581233709821</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.2737957024629196</v>
+        <v>-0.4384948466182905</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>0.7141881233620282</v>
+        <v>0.5389742103738016</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>2.584407516695144</v>
+        <v>2.361556064073234</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>4.104319944322931</v>
+        <v>3.778364438204818</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.007888</t>
+          <t>X &lt; -0.00785</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.2053067327218798</v>
+        <v>0.2073732718894021</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.1294700656279346</v>
+        <v>0.3781331028521961</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.5692630220932102</v>
+        <v>1.206772334293952</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2.420411566753039</v>
+        <v>2.2810368021524</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.334182324597656</v>
+        <v>-0.4945213379469351</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.562185570901427</v>
+        <v>0.912412268051142</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.209040305814497</v>
+        <v>3.450663589151759</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2.07612800636057</v>
+        <v>3.14574314574314</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.4082134788735559</v>
+        <v>0.7736720554272409</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2.199400366939635</v>
+        <v>2.47762056020791</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>2.473460009101558</v>
+        <v>2.749855574812244</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>4.331462742405698</v>
+        <v>4.973273620340947</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>5.772403239652142</v>
+        <v>6.775048169556847</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>3.841922653803842</v>
+        <v>5.276814108123737</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>3.183779356223283</v>
+        <v>4.594659726238682</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>2.068764568764571</v>
+        <v>3.489297078391672</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-1.05660555966589</v>
+        <v>0.46875</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-1.588796690837498</v>
+        <v>-0.08080077182827239</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-1.800255737263612</v>
+        <v>-0.2830052113491632</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-1.186059499945145</v>
+        <v>0.3482479003764851</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-2.583306522612041</v>
+        <v>-1.052529934337578</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-1.804451629320276</v>
+        <v>-0.2943591229595341</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.675276062137371</v>
+        <v>0.7826086956521792</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.3237578880102205</v>
+        <v>1.03713636802938</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.007093</t>
+          <t>X &lt; -0.007058</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.422417079302271</v>
+        <v>-1.411479187126993</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.781084662635031</v>
+        <v>-2.313123727748888</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.4648375000619254</v>
+        <v>-0.2891293050503165</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.8699900504612117</v>
+        <v>0.1020750535185115</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.854878920379576</v>
+        <v>-2.468565053793931</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.32661580595456</v>
+        <v>-2.311631447795847</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.9731078651038985</v>
+        <v>0.1719750645616003</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.37749027700611</v>
+        <v>1.178530030989045</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.2875071827174054</v>
+        <v>-0.6607541740809495</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.646061782884324</v>
+        <v>0.510407445453815</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.2375275683909592</v>
+        <v>0.1269047551401101</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.347856663236477</v>
+        <v>2.473273620340947</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>3.27247616634623</v>
+        <v>3.65346347010329</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>2.027506504916708</v>
+        <v>2.749491703752149</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.6867693506808621</v>
+        <v>1.739468469408081</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.9398593442962024</v>
+        <v>2.300772488227743</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-1.583136290974785</v>
+        <v>-0.09818989071038686</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-1.687976994795967</v>
+        <v>-0.2310739958719878</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-1.472085613871641</v>
+        <v>-0.01661176872621439</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-1.285239803903615</v>
+        <v>0.1979746763327697</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-3.192973685180228</v>
+        <v>-1.680945234884021</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-1.903631933278746</v>
+        <v>-0.4446323470032496</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.9465633641414044</v>
+        <v>0.4547398431931668</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>0.3427920959459101</v>
+        <v>1.604076258739759</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.006298</t>
+          <t>X &lt; -0.006266</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-2.18735874133894</v>
+        <v>-1.751993119295172</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-3.103530888525967</v>
+        <v>-2.824346235990774</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.4717824956964947</v>
+        <v>-1.048737307579323</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.2687518569537914</v>
+        <v>-1.090175319059732</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.520526987686509</v>
+        <v>-2.467661833814709</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.7521654527519175</v>
+        <v>-1.759764040488797</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.96425795638099</v>
+        <v>1.026421164909337</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.686046511627914</v>
+        <v>1.272464908828539</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1.146138344705406</v>
+        <v>0.5739475375209153</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.9546180175061281</v>
+        <v>0.6043423232933094</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.5155083868435781</v>
+        <v>-0.7763152240858204</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>1.531323605057253</v>
+        <v>1.426441664418078</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>3.024440607968586</v>
+        <v>2.790888389942516</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>1.349873359428969</v>
+        <v>1.440725953853757</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.9824277362670131</v>
+        <v>1.30953575929653</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.4140239605355873</v>
+        <v>1.044393497124453</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.8826838741162959</v>
+        <v>-0.1614152892562046</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.6968269035188754</v>
+        <v>0.5321468865739405</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-1.062330871431762</v>
+        <v>0.4711270200557962</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.8754850614637348</v>
+        <v>0.6857134651147803</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-1.708728903848368</v>
+        <v>-0.1572131299298647</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.6217841675830513</v>
+        <v>0.8695527227704929</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.05661178068240247</v>
+        <v>1.664151395376699</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>0.7396489893501368</v>
+        <v>2.603940775742885</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.005503</t>
+          <t>X &lt; -0.005474</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>442</v>
+        <v>469</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.947844856095628</v>
+        <v>-1.943479606575416</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.61815784843337</v>
+        <v>-2.402606058483983</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.115000426876122</v>
+        <v>-1.311884382123957</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.8869776803779672</v>
+        <v>0.2279095811147229</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.5800345116263159</v>
+        <v>-1.326966256212756</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.511909050036671</v>
+        <v>-0.317154185395907</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.002403805060354</v>
+        <v>1.233179580622974</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>2.176681048090082</v>
+        <v>1.78113760203312</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2.218168230004785</v>
+        <v>1.909066511717228</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.897741241751099</v>
+        <v>1.752673865111959</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.040579164456013</v>
+        <v>1.172030414897527</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>2.119295824356428</v>
+        <v>2.387985773859072</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>3.032332852522934</v>
+        <v>2.978850586045823</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>2.132520944402138</v>
+        <v>2.730616524612714</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>1.700621990712982</v>
+        <v>2.474901375137044</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>2.295008912655973</v>
+        <v>3.249425010161396</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.5773813684386795</v>
+        <v>1.439787668798864</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.6987850085088994</v>
+        <v>2.159782028456029</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>2.045898108890242</v>
+        <v>3.44034233662525</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>2.458988262749671</v>
+        <v>3.86814839788893</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>1.690197750892239</v>
+        <v>3.087484280303499</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>2.293084821157343</v>
+        <v>3.865200223166973</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>2.567559533639397</v>
+        <v>4.10883470844535</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>2.717971624307523</v>
+        <v>4.799574178974659</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.004707</t>
+          <t>X &lt; -0.004682</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>544</v>
+        <v>572</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-4.280700861146777</v>
+        <v>-4.241927427411298</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-3.792473728631599</v>
+        <v>-3.613708388989288</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.569606263565063</v>
+        <v>-2.770500392978775</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.6118910979025713</v>
+        <v>-1.090175319059732</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.602093335155729</v>
+        <v>-2.93916003258564</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-2.231303619646589</v>
+        <v>-2.782226426587556</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.348840538831048</v>
+        <v>-1.829056690568521</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.443228454172363</v>
+        <v>-1.609501609501621</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.2988000957870725</v>
+        <v>-0.607446825691639</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.7665195222940895</v>
+        <v>0.5195786021659501</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.6729321056324835</v>
+        <v>0.4421632671199305</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.864770937478596</v>
+        <v>1.739007886075221</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>2.39602063532837</v>
+        <v>2.372367516876189</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.80729470005825</v>
+        <v>1.949308280617913</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>2.803563167183569</v>
+        <v>3.015405646984597</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>2.84647950089127</v>
+        <v>3.227059316153913</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>2.712562363913797</v>
+        <v>3.123178904428904</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>3.159192248327905</v>
+        <v>3.864420673393177</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>4.29420127631105</v>
+        <v>4.953008774664823</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>3.745752968632019</v>
+        <v>4.468294520423115</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>3.203206800665988</v>
+        <v>3.90085001904238</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>3.495007898080416</v>
+        <v>4.350163021562615</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>3.953306139974238</v>
+        <v>4.768622681666166</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>4.245120945574492</v>
+        <v>5.305784386677409</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.003912</t>
+          <t>X &lt; -0.003889</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>637</v>
+        <v>669</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-3.874856473806382</v>
+        <v>-3.617365143656187</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-3.819373911781781</v>
+        <v>-3.414841486086516</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.892516200249396</v>
+        <v>-1.829475797245657</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.3272239395031562</v>
+        <v>-0.6281560229597147</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.831304250291012</v>
+        <v>-1.950051980697317</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.644338064193633</v>
+        <v>-1.793118374699233</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.317385649182889</v>
+        <v>-1.541862569293684</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.9676536088496164</v>
+        <v>-0.949922026155221</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.1412370705769916</v>
+        <v>-0.2240857921063864</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.8126918373739613</v>
+        <v>0.9230615168596259</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.9297656082642973</v>
+        <v>1.045819700372782</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2.534846660075331</v>
+        <v>2.56295971899565</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>2.353599820848729</v>
+        <v>2.643882250274331</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2.132520944402138</v>
+        <v>2.395648188841221</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>2.730264616994262</v>
+        <v>3.058785286776789</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>3.324651538937253</v>
+        <v>3.769566136687644</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>3.19073440195978</v>
+        <v>3.665685724962636</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>3.870823054496519</v>
+        <v>4.579139437439295</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>4.086714435420845</v>
+        <v>4.793601664585069</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>3.645616760302538</v>
+        <v>4.410280785279333</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>2.946084721064921</v>
+        <v>3.693359452807407</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>3.341196373470581</v>
+        <v>4.216104255216848</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>3.144713472137873</v>
+        <v>4.16078507831287</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>3.225867090186185</v>
+        <v>4.447076577296947</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.003117</t>
+          <t>X &lt; -0.003097</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>723</v>
+        <v>754</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-3.091396563981419</v>
+        <v>-3.144748744025712</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.943987047957847</v>
+        <v>-2.727525606254787</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.419152602686047</v>
+        <v>-1.462325808942118</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.1265969802555063</v>
+        <v>-0.3305900767158647</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.628133309156375</v>
+        <v>-1.799782169069836</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.08869927500416</v>
+        <v>-1.244970578986873</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.16908502666768</v>
+        <v>-1.376922617744796</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.3407957798578281</v>
+        <v>-0.3555831142038102</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.2539417478383399</v>
+        <v>0.03759778487021492</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.5875267633647923</v>
+        <v>0.4351802419055204</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.276524164862813</v>
+        <v>1.10529324059474</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.551025107196281</v>
+        <v>1.491841259598239</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.810988904793831</v>
+        <v>1.835835083792027</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.728222614792607</v>
+        <v>1.852853011748842</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>2.038267422329611</v>
+        <v>2.231706587423467</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>1.802778825600406</v>
+        <v>2.129880632768334</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>2.083799447959031</v>
+        <v>2.423878205128204</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>2.532209089919313</v>
+        <v>3.086750068136361</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>2.748100470843639</v>
+        <v>3.301212295282134</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>2.520008521475567</v>
+        <v>3.117920756256247</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>1.839149767064171</v>
+        <v>2.417850260180543</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>2.316554151436534</v>
+        <v>3.005817711700068</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>2.314403691027856</v>
+        <v>2.984200207588515</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>2.653509197140679</v>
+        <v>3.485191186773861</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.002322</t>
+          <t>X &lt; -0.002305</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>821</v>
+        <v>854</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.67232411101066</v>
+        <v>-2.371666540756969</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.702896639054515</v>
+        <v>-2.266285320254745</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.530147815181707</v>
+        <v>-1.296155066174428</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.1309971874237092</v>
+        <v>0.2191710722538716</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.9879348980582634</v>
+        <v>-0.8760591989930049</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.6115966625641178</v>
+        <v>-0.3678375367888265</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.261742666795513</v>
+        <v>-1.162919549021545</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.052743392912781</v>
+        <v>-0.7652638800179901</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.03683477372645427</v>
+        <v>-0.05185487665706745</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.1646709875086785</v>
+        <v>0.2059577967418633</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.316927950011646</v>
+        <v>0.4781928113461973</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.012599983835273</v>
+        <v>1.255475025493169</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.22926739322763</v>
+        <v>1.54573513286676</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.739004594734752</v>
+        <v>2.117173202581192</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>1.689874695448957</v>
+        <v>2.137594933108311</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>1.79705089875614</v>
+        <v>2.347610895721886</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>2.272147160073423</v>
+        <v>2.829210577673692</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>2.289109135911197</v>
+        <v>3.047614528718178</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>2.626803196494478</v>
+        <v>3.379172774599319</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>2.69184632680355</v>
+        <v>3.476663200922935</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>2.027497479178564</v>
+        <v>2.792122680806841</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>2.073454197428418</v>
+        <v>2.951152196322283</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>2.104323550592568</v>
+        <v>2.960594644129934</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>1.784885938051382</v>
+        <v>2.681359631105103</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.001527</t>
+          <t>X &lt; -0.001513</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>969</v>
+        <v>1006</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.538283010867872</v>
+        <v>-1.554555157534054</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-2.435582844019969</v>
+        <v>-2.098672728824404</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.148483659682242</v>
+        <v>-0.8682773674953168</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.6739220831361763</v>
+        <v>-0.4666437810152644</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.467536783389811</v>
+        <v>-1.338623392287559</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.9145965244373642</v>
+        <v>-0.6846718936453371</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.010218247809377</v>
+        <v>-0.8833324347050961</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.6692346461228311</v>
+        <v>-0.293620671354283</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.4042442798579273</v>
+        <v>0.629536866560457</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.3537228246676705</v>
+        <v>0.6287139995717297</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.6277824668295935</v>
+        <v>0.9009490141760637</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.071427284227831</v>
+        <v>1.419595687935384</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.289854484657575</v>
+        <v>1.69635366988819</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.894369003463815</v>
+        <v>2.342751815214527</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>1.855420752322892</v>
+        <v>2.356422483031253</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>1.727413453419651</v>
+        <v>2.321305030677955</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>1.490297142035566</v>
+        <v>2.118021040424125</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>2.004651484654012</v>
+        <v>2.780365563493142</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>2.220542865578338</v>
+        <v>3.094231369167737</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>2.200990326733155</v>
+        <v>3.110010657169063</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>1.555244984360527</v>
+        <v>2.343758998730685</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>1.582598197358024</v>
+        <v>2.368000055304222</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>1.444276212213659</v>
+        <v>2.214020226467284</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>1.368443958990383</v>
+        <v>2.350091967764314</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.0007318</t>
+          <t>X &lt; -0.0007212</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1119</v>
+        <v>1155</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.46306933565419</v>
+        <v>-1.379996970325124</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.463168395767546</v>
+        <v>-1.885419376963263</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.451042782718382</v>
+        <v>-0.977483721069369</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.224636195941784</v>
+        <v>-0.7913392070748273</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.779068987147127</v>
+        <v>-1.412918108419831</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.007564123848262</v>
+        <v>-0.6504481702418232</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.104563873741427</v>
+        <v>-0.7534886599831836</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.4891202693434664</v>
+        <v>-0.02034681965478313</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.1779254469769498</v>
+        <v>0.4536028512750008</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.4773958299216901</v>
+        <v>0.7821188301041104</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.6620899671685052</v>
+        <v>1.054353844708444</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.4727060686356168</v>
+        <v>0.8642770805485611</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.9581230902513553</v>
+        <v>1.392983579014739</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.005140728550067</v>
+        <v>1.490770278827313</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.7938249555450199</v>
+        <v>1.327647038810767</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>1.20948086765781</v>
+        <v>1.715940677007588</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.8074672159350271</v>
+        <v>1.439049884659738</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>1.417550551434665</v>
+        <v>2.17121768261233</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>1.722807437274099</v>
+        <v>2.558690290380937</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>1.552191227581709</v>
+        <v>2.254245593571419</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>1.367107079276096</v>
+        <v>1.946316663124932</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>1.201895612951887</v>
+        <v>1.698143760546813</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>1.47637032543394</v>
+        <v>1.941778245825191</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>1.400538072210665</v>
+        <v>2.005751086644104</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 6.337e-05</t>
+          <t>X &lt; 7.086e-05</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1310</v>
+        <v>1357</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.783379334811798</v>
+        <v>-1.48380319869883</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.685790831356897</v>
+        <v>-1.985737390157361</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.034751540919082</v>
+        <v>-1.548010594330037</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.719302147428763</v>
+        <v>-1.330994102924869</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.089763878658303</v>
+        <v>-1.827302794900582</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.252590216477088</v>
+        <v>-0.9345340159812352</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.830309783040541</v>
+        <v>-1.582448993629697</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.456678956324438</v>
+        <v>-1.151534264117053</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.9149103842960713</v>
+        <v>-0.8028548025565598</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.6524297367988652</v>
+        <v>-0.5687370556861282</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.6837136060873235</v>
+        <v>-0.443669075666044</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.7334553759475355</v>
+        <v>-0.5730839955530911</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.3298998855517397</v>
+        <v>-0.1427222498692089</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.1692993726853587</v>
+        <v>0.05054479245044519</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.0640838916399602</v>
+        <v>0.1778091007787808</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.5303030303030312</v>
+        <v>0.8126966368905642</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.09104238187516955</v>
+        <v>0.5616491905813064</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.7495604566799443</v>
+        <v>1.164600258340975</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>1.194459471192054</v>
+        <v>1.59981303736312</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>1.228633525434894</v>
+        <v>1.520065413253604</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>1.220438502507037</v>
+        <v>1.394122015625634</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>1.602607808273504</v>
+        <v>1.686877080130976</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>1.80074664289296</v>
+        <v>1.828264071204465</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>1.953922023257469</v>
+        <v>2.005878691782762</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.0008585</t>
+          <t>X &lt; 0.0008629</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1513</v>
+        <v>1569</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.344259186922784</v>
+        <v>-1.00133066711949</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.513378343823803</v>
+        <v>-1.150262743725463</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.86567975450528</v>
+        <v>-1.544499930337089</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.885965816547426</v>
+        <v>-1.373543350519363</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.383440084381739</v>
+        <v>-1.90355441682734</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.700042728193232</v>
+        <v>-1.174101726859803</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.974906182479813</v>
+        <v>-1.523891118227375</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.019055357115484</v>
+        <v>-1.510745403875184</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.87512323718083</v>
+        <v>-1.573656188847558</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.753379526434315</v>
+        <v>-1.415509210784457</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.574231621152826</v>
+        <v>-1.334113890836612</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.815830516586168</v>
+        <v>-1.610695845307909</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.683209371281023</v>
+        <v>-1.516936563267585</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.639912834641031</v>
+        <v>-1.510717698492037</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-1.372742186418549</v>
+        <v>-1.365900070198975</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-0.9105429710188417</v>
+        <v>-0.8682092829314882</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-0.5818031350947948</v>
+        <v>-0.4631838422391894</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>0.04038854707212636</v>
+        <v>0.1036775996730057</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.5206553410830352</v>
+        <v>0.5089795214752613</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.5753134445077634</v>
+        <v>0.5327262718777632</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.4954242494432535</v>
+        <v>0.3469611598100002</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>0.7500475543923883</v>
+        <v>0.7553968710994567</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>0.4957714407012688</v>
+        <v>0.5278316255884832</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>0.6182207472929306</v>
+        <v>0.7861803450848299</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.001654</t>
+          <t>X &lt; 0.001655</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1766</v>
+        <v>1827</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.4720305121980957</v>
+        <v>-0.4602481138170873</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.113671049828916</v>
+        <v>-0.7863501577009373</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.4551926519975</v>
+        <v>-1.302102597437347</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.182776755536416</v>
+        <v>-1.045465930088042</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.274641528125997</v>
+        <v>-2.031406583848579</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.382282909000125</v>
+        <v>-1.109445655446116</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.898242207208028</v>
+        <v>-1.576658815219822</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.539545359312797</v>
+        <v>-2.045513684857951</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.24184069230737</v>
+        <v>-1.917584775173843</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.081812595220342</v>
+        <v>-1.83931933050247</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.001788374776275</v>
+        <v>-1.894953168357148</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.079758341501616</v>
+        <v>-2.007600696598942</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.098469848612247</v>
+        <v>-2.0842414479295</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.980757081919371</v>
+        <v>-2.004606656903583</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-2.13071291479072</v>
+        <v>-2.194957760100124</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-1.931582909843783</v>
+        <v>-1.961522593739474</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-1.387916760542311</v>
+        <v>-1.35502049180328</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-0.7819011381792365</v>
+        <v>-0.7228772745605028</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.4761699869483493</v>
+        <v>-0.6177046649010762</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.6518714657571181</v>
+        <v>-0.7856318810442744</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.7650719369750689</v>
+        <v>-0.9159179124796566</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.5243362495446533</v>
+        <v>-0.576389376285583</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.9293632358168438</v>
+        <v>-1.066406621634471</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.8919452059144106</v>
+        <v>-0.8683097184511865</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.002449</t>
+          <t>X &lt; 0.002447</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2043</v>
+        <v>2099</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.7823199816490174</v>
+        <v>-0.6237847727237877</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.188420809503548</v>
+        <v>-0.9395307148116245</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.485417936564474</v>
+        <v>-1.218999637202486</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.153283054976527</v>
+        <v>-0.8827781534876564</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.947824346006669</v>
+        <v>-1.607811875274564</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.637247395894342</v>
+        <v>-1.213122682020185</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.139692593938811</v>
+        <v>-1.675346872094075</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.488439927191322</v>
+        <v>-1.980267315502694</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.274366586974985</v>
+        <v>-1.899889523269849</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.63121913521271</v>
+        <v>-2.267980961427845</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.573602632897789</v>
+        <v>-2.28105265153107</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.971587619582806</v>
+        <v>-2.700287958356149</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.947044953480258</v>
+        <v>-2.816606609330464</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.506866971436295</v>
+        <v>-2.446676143897186</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-2.551888769688745</v>
+        <v>-2.558217116367125</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-2.368672079506638</v>
+        <v>-2.377322037157548</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-2.181739106674442</v>
+        <v>-2.148344626723727</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-1.916564238927478</v>
+        <v>-1.853268674823994</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-1.91680585381372</v>
+        <v>-2.019215387288298</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-2.141903438674177</v>
+        <v>-2.185037881839399</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-2.265093533166173</v>
+        <v>-2.392523591172335</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-2.165911021616679</v>
+        <v>-2.2025774317014</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-2.331964943495855</v>
+        <v>-2.455486542443062</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-2.456744822759269</v>
+        <v>-2.447657978484827</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.003244</t>
+          <t>X &lt; 0.003239</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2341</v>
+        <v>2398</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.9112660723824533</v>
+        <v>-0.655215012281765</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.88502272634571</v>
+        <v>-0.6713265812708258</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.156972058652677</v>
+        <v>-0.9475935700719518</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.9571054548317832</v>
+        <v>-0.7271440076091196</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.439072488835002</v>
+        <v>-1.187925416182473</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.483224489775807</v>
+        <v>-1.155835755253058</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.595524384197795</v>
+        <v>-1.285083393786238</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.189757965807239</v>
+        <v>-1.839691727332188</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.955007164601859</v>
+        <v>-1.711762817648079</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.322090603149462</v>
+        <v>-2.050053180948979</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.151841025039246</v>
+        <v>-1.944276759769529</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.109318698375738</v>
+        <v>-1.971170824103496</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.975163716762104</v>
+        <v>-1.962467435936283</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.874025700442381</v>
+        <v>-1.87778431051963</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-1.741393385041413</v>
+        <v>-1.810875021992693</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-1.505472097465287</v>
+        <v>-1.582488190022815</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-1.444261741953525</v>
+        <v>-1.519910008322931</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-1.353808604187009</v>
+        <v>-1.403106223347201</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-1.326252128931635</v>
+        <v>-1.521561183051197</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-1.541212500149349</v>
+        <v>-1.657719349137807</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-1.546940697513826</v>
+        <v>-1.743214371377697</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-1.640591388602651</v>
+        <v>-1.75269245629287</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-1.939254857085842</v>
+        <v>-2.151947369374916</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-1.886936747216417</v>
+        <v>-1.998379339504673</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.004039</t>
+          <t>X &lt; 0.004031</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2587</v>
+        <v>2643</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.265368186228898</v>
+        <v>-1.111416777111728</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.311768028301522</v>
+        <v>-1.149016218414765</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.310882224616449</v>
+        <v>-1.139040566498203</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.96741017549909</v>
+        <v>-0.8054411852689896</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.9750505379908176</v>
+        <v>-0.7960502167691388</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.227436621791782</v>
+        <v>-0.9581818910626509</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.133391455972109</v>
+        <v>-0.8846838428724126</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.428539520588942</v>
+        <v>-1.151839935827859</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.365570001289626</v>
+        <v>-1.174968427956436</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.65562580642564</v>
+        <v>-1.44231901683137</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.513719478077924</v>
+        <v>-1.358905754492888</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.309102498005636</v>
+        <v>-1.220079853979293</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.255685428159389</v>
+        <v>-1.277570158741248</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.223422303724398</v>
+        <v>-1.261453767002152</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-1.319862011824867</v>
+        <v>-1.414907242542796</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-1.12672972499562</v>
+        <v>-1.231246728254852</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-1.161054353397653</v>
+        <v>-1.259598439073514</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.9348335224123261</v>
+        <v>-1.014839039703396</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-1.004909108583639</v>
+        <v>-1.215784667542515</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-1.181441278422255</v>
+        <v>-1.319363231722747</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-1.083785023090535</v>
+        <v>-1.29818375141997</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.175558184667857</v>
+        <v>-1.313577774503329</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-1.30342174437888</v>
+        <v>-1.539630336117867</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-1.434010003287469</v>
+        <v>-1.604274907036832</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.004834</t>
+          <t>X &lt; 0.004823</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2788</v>
+        <v>2839</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.097268315851032</v>
+        <v>-0.9996593482438882</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.057474445589612</v>
+        <v>-0.9113405813583242</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.266259550346419</v>
+        <v>-1.129573752052131</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.9627793164378531</v>
+        <v>-0.8252366060873015</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.207667110800649</v>
+        <v>-1.081542764009463</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.10792304860135</v>
+        <v>-0.9053436466829865</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.289794193019993</v>
+        <v>-1.083607061111863</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.512457286932289</v>
+        <v>-1.283079349863186</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.451058180612151</v>
+        <v>-1.3308973646079</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.740093401247918</v>
+        <v>-1.599708086540772</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.66013696633761</v>
+        <v>-1.573518766136786</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.45455679361384</v>
+        <v>-1.428308101978914</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.521410485029747</v>
+        <v>-1.594166827514044</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.507441666253825</v>
+        <v>-1.596355194746806</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-1.715853644947067</v>
+        <v>-1.856716958002679</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-1.529782806606832</v>
+        <v>-1.68205617292643</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-1.642970099518806</v>
+        <v>-1.785936584651438</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-1.476529255735421</v>
+        <v>-1.602476225841166</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-1.56202279226374</v>
+        <v>-1.75452419869093</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-1.712594410434221</v>
+        <v>-1.836357563335554</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-1.517916241886752</v>
+        <v>-1.750395287375348</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-1.46532838697123</v>
+        <v>-1.629276405606483</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-1.456734355248585</v>
+        <v>-1.717391304347828</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-1.439957964038129</v>
+        <v>-1.612710996065957</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.005629</t>
+          <t>X &lt; 0.005615</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2952</v>
+        <v>2996</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.9349647604907858</v>
+        <v>-0.820183169013653</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.7812728694146003</v>
+        <v>-0.6832529261525551</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.9905013530092148</v>
+        <v>-0.9236263368023927</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.7766642750065174</v>
+        <v>-0.7004354477645194</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.9591898762292388</v>
+        <v>-0.8579965152519122</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.8882158795000237</v>
+        <v>-0.7492660381233449</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.9005191590834656</v>
+        <v>-0.6943796576878967</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.025042311790877</v>
+        <v>-0.8143234099972858</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.065691786740501</v>
+        <v>-0.8674730843863401</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.347636996685729</v>
+        <v>-1.130901410497813</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.223085154559961</v>
+        <v>-1.091689032378163</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.976679407841722</v>
+        <v>-0.9022257138800853</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.068088177282064</v>
+        <v>-1.051738337322867</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.9319365427427257</v>
+        <v>-0.9670829180635678</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-1.029973793700073</v>
+        <v>-1.116614130840773</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.7872645372645408</v>
+        <v>-0.9214885407827538</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.9351450292834329</v>
+        <v>-1.072625291375296</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.7496988943360563</v>
+        <v>-0.8863748335648935</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.9873216304505661</v>
+        <v>-1.152298780159562</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-1.051319784691231</v>
+        <v>-1.218418766290185</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.9988560041513637</v>
+        <v>-1.199801246997353</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-1.020927623047463</v>
+        <v>-1.15548876494308</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-1.099008554952164</v>
+        <v>-1.292800046423224</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-1.188881923865971</v>
+        <v>-1.335471553643963</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.006424</t>
+          <t>X &lt; 0.006407</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3042</v>
+        <v>3080</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.720781860577155</v>
+        <v>-0.7057472954864821</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.5487309613901346</v>
+        <v>-0.5476435283420358</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.7286935647957904</v>
+        <v>-0.6561308915125039</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.6399869214704026</v>
+        <v>-0.5856137302774229</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.8923123139592732</v>
+        <v>-0.8111234468343937</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.9159441425223989</v>
+        <v>-0.797844970136353</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.048677567464019</v>
+        <v>-0.8645818888844232</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.177772369841968</v>
+        <v>-0.9899596006219653</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.11791822390191</v>
+        <v>-0.9732574856199392</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.250727166957532</v>
+        <v>-1.072330943186849</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.252672014902799</v>
+        <v>-1.072912859857865</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.087239925805804</v>
+        <v>-0.9107444967732476</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.914308163731377</v>
+        <v>-0.7962610076242171</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.8869366622114327</v>
+        <v>-0.7992376718115395</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.8703769103223635</v>
+        <v>-0.8151276914801073</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.6172379533035226</v>
+        <v>-0.5910138024373452</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.6990552349132031</v>
+        <v>-0.7083637026239131</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.5877199023591402</v>
+        <v>-0.6278951766673231</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.7462555857905357</v>
+        <v>-0.8158253085938938</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.868422806733939</v>
+        <v>-0.9390413343835604</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.8663261849420465</v>
+        <v>-0.9687370918681211</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.8570926661925924</v>
+        <v>-0.8951594690551374</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.9575548524674318</v>
+        <v>-1.02200019756431</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-1.014093193730147</v>
+        <v>-1.035374454481442</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.00722</t>
+          <t>X &lt; 0.007199</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3110</v>
+        <v>3143</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.496895629231517</v>
+        <v>-0.5104094192034623</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.559276529917156</v>
+        <v>-0.5499869603389556</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.7026879943483877</v>
+        <v>-0.6816600298021314</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.6313893125238863</v>
+        <v>-0.5929488654627448</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.7896485585873876</v>
+        <v>-0.7878483461695822</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.6168534917693478</v>
+        <v>-0.5818406055120775</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.6034940311841765</v>
+        <v>-0.5366781830001415</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.7356901605439674</v>
+        <v>-0.6655895544784585</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.7400942134341264</v>
+        <v>-0.709861826776681</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.8867153952324571</v>
+        <v>-0.8229812769792915</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.8825339808981951</v>
+        <v>-0.817951776265069</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.7586887603018511</v>
+        <v>-0.6962984874245066</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.6779728999261678</v>
+        <v>-0.6200585732036714</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.7841457222645261</v>
+        <v>-0.7230273127452875</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.8463859115181265</v>
+        <v>-0.7839358744381428</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.7461562384589939</v>
+        <v>-0.6800142513449217</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.7649872218492888</v>
+        <v>-0.7018849206349174</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.6262981994558317</v>
+        <v>-0.5939266318896586</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.6803643926531677</v>
+        <v>-0.6784944108408979</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.7957625778563155</v>
+        <v>-0.8266806029600247</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.805539727177397</v>
+        <v>-0.8671092943714811</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.7338783865105327</v>
+        <v>-0.8282753921699211</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.8582496298746847</v>
+        <v>-0.9794778183427297</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.8508692189800797</v>
+        <v>-0.9640037316630554</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.008015</t>
+          <t>X &lt; 0.007992</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3172</v>
+        <v>3197</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.4953072073286791</v>
+        <v>-0.499148467241028</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.6569013068976233</v>
+        <v>-0.6664459589682465</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.6688888111102926</v>
+        <v>-0.692699387272242</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.550155877498625</v>
+        <v>-0.5843398427548721</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.8058534509224984</v>
+        <v>-0.842780044414603</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.6327880378652893</v>
+        <v>-0.6687178511816256</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.5092702328158936</v>
+        <v>-0.5443581905619936</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.5188059875696567</v>
+        <v>-0.5517358458535</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.4281168052132358</v>
+        <v>-0.4685446319949165</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.4612785649257347</v>
+        <v>-0.4996450891225237</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.5145044074342806</v>
+        <v>-0.5523251105460147</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.4611971381938815</v>
+        <v>-0.499615130048582</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.4980882334783416</v>
+        <v>-0.5368803424963602</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.606443422469205</v>
+        <v>-0.6422691472551278</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.6488056772419668</v>
+        <v>-0.6824249067411543</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.5703259005145753</v>
+        <v>-0.6019665721543461</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.5913460978666407</v>
+        <v>-0.6251950686641763</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.5202861509613257</v>
+        <v>-0.5524939761159189</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.5375744462537071</v>
+        <v>-0.5695448740599645</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.6785135893765712</v>
+        <v>-0.7115771542939271</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.6356653623724497</v>
+        <v>-0.6671132676709135</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.6298438384554004</v>
+        <v>-0.6614009068503321</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.8094207282706947</v>
+        <v>-0.8371536558174881</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.8351772518886094</v>
+        <v>-0.8559144087405102</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.00881</t>
+          <t>X &lt; 0.008784</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3234</v>
+        <v>3258</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.4016699565391164</v>
+        <v>-0.4185791816308608</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.4743954105532779</v>
+        <v>-0.495850636985196</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.5134893509817502</v>
+        <v>-0.5449050063586824</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.6256750380305576</v>
+        <v>-0.6630856302250692</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.7599589252897161</v>
+        <v>-0.7998056426972227</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.6173646861396023</v>
+        <v>-0.6565743009354179</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.5109196276182075</v>
+        <v>-0.5493364108482339</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.5563506261180606</v>
+        <v>-0.5928029752098212</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.3434971066320358</v>
+        <v>-0.3560254697789844</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.2983891998154462</v>
+        <v>-0.3096655033617779</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.3761131669268067</v>
+        <v>-0.3867998822345342</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.3907199834738861</v>
+        <v>-0.4013441166621163</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.4483439980442441</v>
+        <v>-0.4586879373055979</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.5588382512727179</v>
+        <v>-0.5667191436102499</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.4896158065335783</v>
+        <v>-0.4964024102780087</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.4320658777783919</v>
+        <v>-0.4375247219757483</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.4243484479271373</v>
+        <v>-0.4622096733027021</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.4800597487672249</v>
+        <v>-0.5158497914361178</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.4928721668358875</v>
+        <v>-0.5285614479412573</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.4731048956996275</v>
+        <v>-0.5106321323232805</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.4105127835532443</v>
+        <v>-0.4468874933685498</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.4370887353813728</v>
+        <v>-0.4732957282765042</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.5460801678719278</v>
+        <v>-0.5797724028442914</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.6345581988105309</v>
+        <v>-0.6625260015224868</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.009605</t>
+          <t>X &lt; 0.009576</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3286</v>
+        <v>3309</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.2108078266383728</v>
+        <v>-0.2413061998993129</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.2271353990852916</v>
+        <v>-0.2310433206442539</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.3486293533135267</v>
+        <v>-0.3885730110513919</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.3794705434739001</v>
+        <v>-0.4238545566140033</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.5773647599132232</v>
+        <v>-0.6227264661520664</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.4642832521775588</v>
+        <v>-0.5092889642902989</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.4018961389094144</v>
+        <v>-0.4459088702589398</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.4812446297522328</v>
+        <v>-0.4933545986177563</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.392243259177846</v>
+        <v>-0.4086384138868269</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.4812523137130427</v>
+        <v>-0.525689701603703</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.5231745577057865</v>
+        <v>-0.5373208249469457</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.4510265155232247</v>
+        <v>-0.4957116250670595</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.464813188647085</v>
+        <v>-0.5090883766278935</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.5163774872632843</v>
+        <v>-0.5590300216342214</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.4282720555246371</v>
+        <v>-0.4701383448885039</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.3925870729149352</v>
+        <v>-0.4336754871796273</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.4781965542905979</v>
+        <v>-0.489734117410535</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.5043235832781292</v>
+        <v>-0.5144357642867874</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.5135297012212519</v>
+        <v>-0.5236509566720358</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.5519182275060075</v>
+        <v>-0.563061084430835</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.5597262381621846</v>
+        <v>-0.5694381468979728</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.5871267806085712</v>
+        <v>-0.5966343670952412</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.7205203422462745</v>
+        <v>-0.7279653224747094</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.7175549342722647</v>
+        <v>-0.7213254028983869</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.0104</t>
+          <t>X &lt; 0.01037</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3317</v>
+        <v>3340</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.2276734607373569</v>
+        <v>-0.2568699633172642</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.1571153762921114</v>
+        <v>-0.1894853782106622</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2608568613520106</v>
+        <v>-0.297616240534964</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.2680413914032442</v>
+        <v>-0.3082489121333154</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.4971596350569882</v>
+        <v>-0.5375649024998808</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.4433373086844128</v>
+        <v>-0.4832597589490533</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.3287136818495071</v>
+        <v>-0.3682223208869715</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.4098898261919217</v>
+        <v>-0.4478206206454161</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.3513211041904327</v>
+        <v>-0.3924978402508472</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.4767036751205822</v>
+        <v>-0.5158201076513649</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.5156829800414329</v>
+        <v>-0.5546478549521439</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.3867221800447638</v>
+        <v>-0.4264877161745702</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.3807751791512715</v>
+        <v>-0.4201920572411311</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.4639508134762949</v>
+        <v>-0.5017928570503969</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.4128511796736305</v>
+        <v>-0.4498809326644775</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.4321029847345557</v>
+        <v>-0.4682895404852658</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.458006405110055</v>
+        <v>-0.494923936858882</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.4848616717655574</v>
+        <v>-0.5206294229539878</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.4919613826116347</v>
+        <v>-0.5277735222609721</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.5282409559477443</v>
+        <v>-0.5648302495437676</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.5410348719066533</v>
+        <v>-0.5764106801746536</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.5688822708223356</v>
+        <v>-0.6040539164963405</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.6381823541575855</v>
+        <v>-0.6720455994690369</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.63592854989448</v>
+        <v>-0.6669554483378803</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.0112</t>
+          <t>X &lt; 0.01116</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3355</v>
+        <v>3379</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.1772591915847244</v>
+        <v>-0.1622622366349944</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.229695573019562</v>
+        <v>-0.2160548810741005</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.2299936717132525</v>
+        <v>-0.2196982539413455</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.2747451284036586</v>
+        <v>-0.2664036215016239</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.3865131196670433</v>
+        <v>-0.3785217303346187</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.4200995946034212</v>
+        <v>-0.4113047371495213</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.256148123786744</v>
+        <v>-0.2478051976562483</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.36918863355708</v>
+        <v>-0.3594114934321198</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.3108004448881374</v>
+        <v>-0.303228357065386</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.3544275208152357</v>
+        <v>-0.3458395046314706</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.4789122425581098</v>
+        <v>-0.4694840478292619</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.4139420029990504</v>
+        <v>-0.4049333982376453</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.4504588655628936</v>
+        <v>-0.4410285266083562</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.4460594647874814</v>
+        <v>-0.4360313723523177</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.4326926906887181</v>
+        <v>-0.4220659723052052</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.4152812694293573</v>
+        <v>-0.4042665472357214</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.4126563434382717</v>
+        <v>-0.402238383540066</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.4998859321855917</v>
+        <v>-0.4882355330296448</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.5342300962379625</v>
+        <v>-0.522366913476823</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.4786857648846023</v>
+        <v>-0.467842354821066</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.5272393682721059</v>
+        <v>-0.5153724338447745</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.5556259837117921</v>
+        <v>-0.5435457541337456</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.6806243094403328</v>
+        <v>-0.667095446359653</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.6792675877822134</v>
+        <v>-0.663933968362052</v>
       </c>
     </row>
   </sheetData>
